--- a/Översikt NORDMALING.xlsx
+++ b/Översikt NORDMALING.xlsx
@@ -601,7 +601,7 @@
         <v>46205</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45168</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45183</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>45265</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>46139</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>45158</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>45154</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>46044</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>45920</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>45273</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>45219</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>45567</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>44694</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>44859</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>44806</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>45239</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>44728</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>45873</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>45574</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>44964</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>45575</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>45077</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>46043</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>46042</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>44820</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>44904</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>44721</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>45400</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>45713</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>45265</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>46032</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>45283</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>45283</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>45238</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>44648</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         <v>44802</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>44495</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>44495</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         <v>44859</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>44859</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>45275</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         <v>45158</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         <v>45343</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>45570</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>45693</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>45618</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>44788</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>45999</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
         <v>45999</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>46002</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>45166</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         <v>44908</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>46072</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>45651</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>46129</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>46205</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>45145</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>44547</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>45824</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>44519</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         <v>46183</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>44858</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
         <v>44487</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>44463</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>44510</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>44818</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>44859</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>44462</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>44851</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>44651</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>44867</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>44867</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>44866</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>44859</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8308,7 +8308,7 @@
         <v>44744</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>44859</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>44859</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         <v>44833</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>44565</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>44651</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>44487</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>44657</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>44687</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>44759</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         <v>44859</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>44859</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>44854</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>44832</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9375,7 +9375,7 @@
         <v>44868</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>44830</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>44473</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         <v>44469</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>44620</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>44861</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>44621</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>44655</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>45736</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>44922</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>45096</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>45062</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>45167</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10349,7 +10349,7 @@
         <v>44968</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
         <v>44756</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>45664</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         <v>44964</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>45182</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         <v>45141</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>45590</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         <v>45204</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10943,7 +10943,7 @@
         <v>45204</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11016,7 +11016,7 @@
         <v>45447</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
         <v>45665</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>44991</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>45158</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11318,7 +11318,7 @@
         <v>45407</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>44921</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11464,7 +11464,7 @@
         <v>45021</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11537,7 +11537,7 @@
         <v>45622</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11610,7 +11610,7 @@
         <v>44735</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>45757</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
         <v>45469</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11829,7 +11829,7 @@
         <v>45343</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>44763</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11985,7 +11985,7 @@
         <v>44896</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>45232</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         <v>45505</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         <v>44816</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12287,7 +12287,7 @@
         <v>44981</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         <v>45264</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>45491</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>44977</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>45180</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>45678</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         <v>45343</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12813,7 +12813,7 @@
         <v>45187</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>45245</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12959,7 +12959,7 @@
         <v>44753</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>45673</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>45587</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>45247</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         <v>44949</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13329,7 +13329,7 @@
         <v>45589</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>45419</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>44905</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>45443</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13626,7 +13626,7 @@
         <v>44916</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>44515</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13777,7 +13777,7 @@
         <v>45608</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13855,7 +13855,7 @@
         <v>44949</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13928,7 +13928,7 @@
         <v>45049</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14006,7 +14006,7 @@
         <v>44922</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>45470</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14152,7 +14152,7 @@
         <v>45096</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>45887</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14303,7 +14303,7 @@
         <v>45173</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>45981</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>44687</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>45800</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14595,7 +14595,7 @@
         <v>45562</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>46139</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>45126</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>44547</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14887,7 +14887,7 @@
         <v>45552</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14960,7 +14960,7 @@
         <v>44908</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15038,7 +15038,7 @@
         <v>45770</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
         <v>45996</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15184,7 +15184,7 @@
         <v>44540</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15257,7 +15257,7 @@
         <v>45799</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>45888</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
         <v>45141</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>45051</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>45712</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15622,7 +15622,7 @@
         <v>45713</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15695,7 +15695,7 @@
         <v>45891</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15773,7 +15773,7 @@
         <v>45343</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15851,7 +15851,7 @@
         <v>45926</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15924,7 +15924,7 @@
         <v>45894</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         <v>45796</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         <v>45896</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16143,7 +16143,7 @@
         <v>45901</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         <v>44886</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>45900</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         <v>45835</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16435,7 +16435,7 @@
         <v>45900</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16508,7 +16508,7 @@
         <v>45929</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
         <v>45898</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>44834</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>45903</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>45673</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
         <v>46050</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         <v>45638</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>45536</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>45911</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>46141</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         <v>45965</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17321,7 +17321,7 @@
         <v>45489</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17399,7 +17399,7 @@
         <v>45917</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17472,7 +17472,7 @@
         <v>45917</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17545,7 +17545,7 @@
         <v>44531</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>45917</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>45126</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>45265</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>45917</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17915,7 +17915,7 @@
         <v>45923</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17988,7 +17988,7 @@
         <v>45923</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18061,7 +18061,7 @@
         <v>45265</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>45102</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18212,7 +18212,7 @@
         <v>44943</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>45929</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18358,7 +18358,7 @@
         <v>45929</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>45961</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>45926</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>45929</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18650,7 +18650,7 @@
         <v>44938</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18723,7 +18723,7 @@
         <v>45239</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18796,7 +18796,7 @@
         <v>45932</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>45936</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18952,7 +18952,7 @@
         <v>45938</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19025,7 +19025,7 @@
         <v>45938</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19098,7 +19098,7 @@
         <v>45940</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         <v>44972</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19244,7 +19244,7 @@
         <v>45940</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19317,7 +19317,7 @@
         <v>44893</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19395,7 +19395,7 @@
         <v>45078</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19468,7 +19468,7 @@
         <v>45944</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
         <v>45946</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         <v>45946</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19687,7 +19687,7 @@
         <v>45946</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>45525</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19833,7 +19833,7 @@
         <v>45021</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>45092</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19979,7 +19979,7 @@
         <v>45951</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20052,7 +20052,7 @@
         <v>45950</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20125,7 +20125,7 @@
         <v>45950</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20198,7 +20198,7 @@
         <v>45951</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20271,7 +20271,7 @@
         <v>45953</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20344,7 +20344,7 @@
         <v>46151</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20417,7 +20417,7 @@
         <v>46151</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20490,7 +20490,7 @@
         <v>45959</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20563,7 +20563,7 @@
         <v>45607</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20636,7 +20636,7 @@
         <v>45607</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20709,7 +20709,7 @@
         <v>45961</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20782,7 +20782,7 @@
         <v>45960</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20855,7 +20855,7 @@
         <v>45960</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20928,7 +20928,7 @@
         <v>45964</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21001,7 +21001,7 @@
         <v>45962</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21079,7 +21079,7 @@
         <v>45965</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21152,7 +21152,7 @@
         <v>45964</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21225,7 +21225,7 @@
         <v>45965</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         <v>45965</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21371,7 +21371,7 @@
         <v>45158</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21444,7 +21444,7 @@
         <v>46155</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21517,7 +21517,7 @@
         <v>45966</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21590,7 +21590,7 @@
         <v>45433</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>46155</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>45167</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21809,7 +21809,7 @@
         <v>45378</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21882,7 +21882,7 @@
         <v>44859</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21960,7 +21960,7 @@
         <v>45972</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22033,7 +22033,7 @@
         <v>45972</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22106,7 +22106,7 @@
         <v>45435</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22179,7 +22179,7 @@
         <v>45974</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22252,7 +22252,7 @@
         <v>45979</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22325,7 +22325,7 @@
         <v>45979</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22398,7 +22398,7 @@
         <v>45979</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22471,7 +22471,7 @@
         <v>45981</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22544,7 +22544,7 @@
         <v>45981</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22617,7 +22617,7 @@
         <v>45980</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>45707</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>45981</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22841,7 +22841,7 @@
         <v>44977</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22914,7 +22914,7 @@
         <v>45638</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22987,7 +22987,7 @@
         <v>45538</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23060,7 +23060,7 @@
         <v>45982</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23138,7 +23138,7 @@
         <v>44993</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23211,7 +23211,7 @@
         <v>45986</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23289,7 +23289,7 @@
         <v>45986</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>45344</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23435,7 +23435,7 @@
         <v>45986</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>46161</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>45986</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>45988</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>46160</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>46160</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>44881</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>44473</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24024,7 +24024,7 @@
         <v>46161</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24097,7 +24097,7 @@
         <v>45993</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24175,7 +24175,7 @@
         <v>45988</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24248,7 +24248,7 @@
         <v>45988</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>46161</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24394,7 +24394,7 @@
         <v>45419</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24467,7 +24467,7 @@
         <v>46161</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24540,7 +24540,7 @@
         <v>45754</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24613,7 +24613,7 @@
         <v>45503</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>45993</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>45988</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>46161</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24905,7 +24905,7 @@
         <v>45586</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>46162</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25056,7 +25056,7 @@
         <v>45021</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25129,7 +25129,7 @@
         <v>45034</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25202,7 +25202,7 @@
         <v>45994</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25275,7 +25275,7 @@
         <v>45994</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25348,7 +25348,7 @@
         <v>45280</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>45457</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25499,7 +25499,7 @@
         <v>46000</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25577,7 +25577,7 @@
         <v>46000</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25650,7 +25650,7 @@
         <v>46000</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25728,7 +25728,7 @@
         <v>45327</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25801,7 +25801,7 @@
         <v>46003</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25879,7 +25879,7 @@
         <v>46003</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>45691</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26030,7 +26030,7 @@
         <v>45615</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26103,7 +26103,7 @@
         <v>46006</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26176,7 +26176,7 @@
         <v>46006</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26249,7 +26249,7 @@
         <v>46006</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26322,7 +26322,7 @@
         <v>46006</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26395,7 +26395,7 @@
         <v>46006</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>46006</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26546,7 +26546,7 @@
         <v>46006</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26619,7 +26619,7 @@
         <v>46006</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26692,7 +26692,7 @@
         <v>45022</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26770,7 +26770,7 @@
         <v>46009</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26843,7 +26843,7 @@
         <v>46009</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26916,7 +26916,7 @@
         <v>46009</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26989,7 +26989,7 @@
         <v>45147</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27062,7 +27062,7 @@
         <v>45147</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27135,7 +27135,7 @@
         <v>45147</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27208,7 +27208,7 @@
         <v>45147</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27281,7 +27281,7 @@
         <v>46010</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27354,7 +27354,7 @@
         <v>46010</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27427,7 +27427,7 @@
         <v>46010</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27500,7 +27500,7 @@
         <v>45330</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>46169</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27651,7 +27651,7 @@
         <v>44859</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>45147</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>46020</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27875,7 +27875,7 @@
         <v>46018</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27948,7 +27948,7 @@
         <v>44609</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>46020</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28094,7 +28094,7 @@
         <v>46018</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28167,7 +28167,7 @@
         <v>46018</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>46022</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28313,7 +28313,7 @@
         <v>46029</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28386,7 +28386,7 @@
         <v>46028</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28459,7 +28459,7 @@
         <v>46029</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28532,7 +28532,7 @@
         <v>45775</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>45775</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28678,7 +28678,7 @@
         <v>46171</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28751,7 +28751,7 @@
         <v>45349</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28824,7 +28824,7 @@
         <v>46032</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28902,7 +28902,7 @@
         <v>46174</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28975,7 +28975,7 @@
         <v>46174</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29048,7 +29048,7 @@
         <v>44812</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
         <v>45453</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29199,7 +29199,7 @@
         <v>46041</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29272,7 +29272,7 @@
         <v>46037</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29345,7 +29345,7 @@
         <v>46038</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29418,7 +29418,7 @@
         <v>46174</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>45568</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29564,7 +29564,7 @@
         <v>45568</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29637,7 +29637,7 @@
         <v>46042</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29710,7 +29710,7 @@
         <v>46042</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29783,7 +29783,7 @@
         <v>46043</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29856,7 +29856,7 @@
         <v>46045</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>44789</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30002,7 +30002,7 @@
         <v>46176</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30075,7 +30075,7 @@
         <v>45139</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30153,7 +30153,7 @@
         <v>46048</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>45188</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30304,7 +30304,7 @@
         <v>46050</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30377,7 +30377,7 @@
         <v>46050</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30450,7 +30450,7 @@
         <v>45344</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30523,7 +30523,7 @@
         <v>45593</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>44533</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30669,7 +30669,7 @@
         <v>44812</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30742,7 +30742,7 @@
         <v>46056</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30820,7 +30820,7 @@
         <v>46058</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30898,7 +30898,7 @@
         <v>46058</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30971,7 +30971,7 @@
         <v>46058</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>45525</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>45075</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31190,7 +31190,7 @@
         <v>46062</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>45524</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31336,7 +31336,7 @@
         <v>44977</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31414,7 +31414,7 @@
         <v>46065</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31487,7 +31487,7 @@
         <v>45482</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>46065</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31633,7 +31633,7 @@
         <v>46178</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         <v>46066</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31779,7 +31779,7 @@
         <v>46181</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31852,7 +31852,7 @@
         <v>45586</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31925,7 +31925,7 @@
         <v>46072</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31998,7 +31998,7 @@
         <v>46072</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32071,7 +32071,7 @@
         <v>46072</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32149,7 +32149,7 @@
         <v>44907</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>46076</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>46185</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32368,7 +32368,7 @@
         <v>44480</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32441,7 +32441,7 @@
         <v>46188</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32514,7 +32514,7 @@
         <v>44902</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32587,7 +32587,7 @@
         <v>45231</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         <v>44909</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32738,7 +32738,7 @@
         <v>45105</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>44742</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>45922</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32962,7 +32962,7 @@
         <v>46094</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33035,7 +33035,7 @@
         <v>45517</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33113,7 +33113,7 @@
         <v>46094</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33186,7 +33186,7 @@
         <v>46094</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33259,7 +33259,7 @@
         <v>46195</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>46196</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33405,7 +33405,7 @@
         <v>45569</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33478,7 +33478,7 @@
         <v>46197</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33551,7 +33551,7 @@
         <v>46108</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33629,7 +33629,7 @@
         <v>45574</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33702,7 +33702,7 @@
         <v>44888</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33775,7 +33775,7 @@
         <v>46108</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33848,7 +33848,7 @@
         <v>46197</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33921,7 +33921,7 @@
         <v>46244</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33994,7 +33994,7 @@
         <v>46111</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34067,7 +34067,7 @@
         <v>46199</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34140,7 +34140,7 @@
         <v>46113</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34213,7 +34213,7 @@
         <v>46113</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34286,7 +34286,7 @@
         <v>45378</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34359,7 +34359,7 @@
         <v>46244</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34432,7 +34432,7 @@
         <v>46245</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34505,7 +34505,7 @@
         <v>46245</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34578,7 +34578,7 @@
         <v>44706</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34651,7 +34651,7 @@
         <v>46244</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34724,7 +34724,7 @@
         <v>45028</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34797,7 +34797,7 @@
         <v>46245</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34870,7 +34870,7 @@
         <v>46245</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34943,7 +34943,7 @@
         <v>46245</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35016,7 +35016,7 @@
         <v>46245</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35089,7 +35089,7 @@
         <v>46245</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35162,7 +35162,7 @@
         <v>46125</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35235,7 +35235,7 @@
         <v>46245</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35308,7 +35308,7 @@
         <v>46245</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35381,7 +35381,7 @@
         <v>46245</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35454,7 +35454,7 @@
         <v>46202</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35527,7 +35527,7 @@
         <v>44788</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35600,7 +35600,7 @@
         <v>46244</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35673,7 +35673,7 @@
         <v>46125</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35746,7 +35746,7 @@
         <v>46244</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35819,7 +35819,7 @@
         <v>46127</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35892,7 +35892,7 @@
         <v>46245</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35965,7 +35965,7 @@
         <v>46245</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>44462</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36111,7 +36111,7 @@
         <v>46245</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36184,7 +36184,7 @@
         <v>46244</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36257,7 +36257,7 @@
         <v>46244</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36330,7 +36330,7 @@
         <v>46244</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36403,7 +36403,7 @@
         <v>46245</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36476,7 +36476,7 @@
         <v>46129</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36549,7 +36549,7 @@
         <v>46244</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36622,7 +36622,7 @@
         <v>46245</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36695,7 +36695,7 @@
         <v>46132</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>46132</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36841,7 +36841,7 @@
         <v>45525</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36914,7 +36914,7 @@
         <v>45524</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36987,7 +36987,7 @@
         <v>46135</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37065,7 +37065,7 @@
         <v>46205</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37138,7 +37138,7 @@
         <v>46205</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37211,7 +37211,7 @@
         <v>46205</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37284,7 +37284,7 @@
         <v>46205</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>45736</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37430,7 +37430,7 @@
         <v>46135</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37503,7 +37503,7 @@
         <v>46029</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>45618</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37649,7 +37649,7 @@
         <v>45877</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37722,7 +37722,7 @@
         <v>45890</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37795,7 +37795,7 @@
         <v>45866</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37868,7 +37868,7 @@
         <v>46205</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37941,7 +37941,7 @@
         <v>46205</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38014,7 +38014,7 @@
         <v>46246</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38087,7 +38087,7 @@
         <v>45462</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38160,7 +38160,7 @@
         <v>45462</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38233,7 +38233,7 @@
         <v>45245</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38306,7 +38306,7 @@
         <v>44722</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38384,7 +38384,7 @@
         <v>45348</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38457,7 +38457,7 @@
         <v>45096</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38535,7 +38535,7 @@
         <v>44854</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38608,7 +38608,7 @@
         <v>45139</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38686,7 +38686,7 @@
         <v>45569</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38759,7 +38759,7 @@
         <v>44859</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38832,7 +38832,7 @@
         <v>45241</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38905,7 +38905,7 @@
         <v>45147</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38978,7 +38978,7 @@
         <v>45742</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39051,7 +39051,7 @@
         <v>45575</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>46253</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39197,7 +39197,7 @@
         <v>46253</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39270,7 +39270,7 @@
         <v>45119</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39343,7 +39343,7 @@
         <v>45034</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39416,7 +39416,7 @@
         <v>45566</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39489,7 +39489,7 @@
         <v>44812</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39562,7 +39562,7 @@
         <v>45251</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39635,7 +39635,7 @@
         <v>45141</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39708,7 +39708,7 @@
         <v>45775</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>46212</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39854,7 +39854,7 @@
         <v>45439</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39927,7 +39927,7 @@
         <v>46254</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40000,7 +40000,7 @@
         <v>45429</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40073,7 +40073,7 @@
         <v>46254</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40146,7 +40146,7 @@
         <v>44816</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40219,7 +40219,7 @@
         <v>46258</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40292,7 +40292,7 @@
         <v>46258</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40365,7 +40365,7 @@
         <v>46134</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40438,7 +40438,7 @@
         <v>46258</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40511,7 +40511,7 @@
         <v>46258</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40584,7 +40584,7 @@
         <v>45238</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40657,7 +40657,7 @@
         <v>46258</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40735,7 +40735,7 @@
         <v>44620</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40808,7 +40808,7 @@
         <v>45764</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40881,7 +40881,7 @@
         <v>45764</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40954,7 +40954,7 @@
         <v>45420</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41032,7 +41032,7 @@
         <v>46258</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41105,7 +41105,7 @@
         <v>45187</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41178,7 +41178,7 @@
         <v>45763</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41256,7 +41256,7 @@
         <v>45491</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41329,7 +41329,7 @@
         <v>45140</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41407,7 +41407,7 @@
         <v>45216</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41485,7 +41485,7 @@
         <v>45988</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41558,7 +41558,7 @@
         <v>45237</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41631,7 +41631,7 @@
         <v>45145</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41709,7 +41709,7 @@
         <v>46265</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41782,7 +41782,7 @@
         <v>44531</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41855,7 +41855,7 @@
         <v>45147</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41928,7 +41928,7 @@
         <v>46265</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42001,7 +42001,7 @@
         <v>46265</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42074,7 +42074,7 @@
         <v>46262</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42152,7 +42152,7 @@
         <v>46136</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42225,7 +42225,7 @@
         <v>45676</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42298,7 +42298,7 @@
         <v>45187</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42371,7 +42371,7 @@
         <v>45187</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42444,7 +42444,7 @@
         <v>46262</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42522,7 +42522,7 @@
         <v>46267</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42595,7 +42595,7 @@
         <v>46267</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42668,7 +42668,7 @@
         <v>46266</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>46263</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42814,7 +42814,7 @@
         <v>45772</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42887,7 +42887,7 @@
         <v>45187</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42960,7 +42960,7 @@
         <v>45616</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43033,7 +43033,7 @@
         <v>45665</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43106,7 +43106,7 @@
         <v>45638</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43179,7 +43179,7 @@
         <v>45030</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43257,7 +43257,7 @@
         <v>45783</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43330,7 +43330,7 @@
         <v>45783</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43403,7 +43403,7 @@
         <v>46272</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43476,7 +43476,7 @@
         <v>45936</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43549,7 +43549,7 @@
         <v>46275</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43622,7 +43622,7 @@
         <v>46275</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43695,7 +43695,7 @@
         <v>46274</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43768,7 +43768,7 @@
         <v>46279</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43841,7 +43841,7 @@
         <v>46237</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43914,7 +43914,7 @@
         <v>45603</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43987,7 +43987,7 @@
         <v>45261</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44060,7 +44060,7 @@
         <v>45789</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44133,7 +44133,7 @@
         <v>46274</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44206,7 +44206,7 @@
         <v>46280</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44279,7 +44279,7 @@
         <v>45790</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44352,7 +44352,7 @@
         <v>45790</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44425,7 +44425,7 @@
         <v>45790</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44498,7 +44498,7 @@
         <v>45790</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44571,7 +44571,7 @@
         <v>45036</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44644,7 +44644,7 @@
         <v>46239</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44722,7 +44722,7 @@
         <v>46239</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44800,7 +44800,7 @@
         <v>45796</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44873,7 +44873,7 @@
         <v>45699</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44946,7 +44946,7 @@
         <v>45799</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45019,7 +45019,7 @@
         <v>45238</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45092,7 +45092,7 @@
         <v>45607</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45165,7 +45165,7 @@
         <v>45688</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45238,7 +45238,7 @@
         <v>45825</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45311,7 +45311,7 @@
         <v>45825</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45384,7 +45384,7 @@
         <v>45825</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45457,7 +45457,7 @@
         <v>45825</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45530,7 +45530,7 @@
         <v>45825</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45603,7 +45603,7 @@
         <v>45835</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45676,7 +45676,7 @@
         <v>45838</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45749,7 +45749,7 @@
         <v>45841</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45822,7 +45822,7 @@
         <v>45842</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45900,7 +45900,7 @@
         <v>45846</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45973,7 +45973,7 @@
         <v>45849</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46046,7 +46046,7 @@
         <v>45852</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46119,7 +46119,7 @@
         <v>45470</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46192,7 +46192,7 @@
         <v>45867</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46265,7 +46265,7 @@
         <v>45866</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46338,7 +46338,7 @@
         <v>45775</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46411,7 +46411,7 @@
         <v>45883</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46484,7 +46484,7 @@
         <v>45883</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46557,7 +46557,7 @@
         <v>44603</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46635,7 +46635,7 @@
         <v>45567</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46713,7 +46713,7 @@
         <v>44489</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46786,7 +46786,7 @@
         <v>44559</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46864,7 +46864,7 @@
         <v>45667</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46942,7 +46942,7 @@
         <v>44517</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47015,7 +47015,7 @@
         <v>45250</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47093,7 +47093,7 @@
         <v>45638</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47166,7 +47166,7 @@
         <v>45762</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47239,7 +47239,7 @@
         <v>45762</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47312,7 +47312,7 @@
         <v>46071</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         <v>46070</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47463,7 +47463,7 @@
         <v>46071</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47536,7 +47536,7 @@
         <v>46071</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47609,7 +47609,7 @@
         <v>46135</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47682,7 +47682,7 @@
         <v>46148</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>

--- a/Översikt NORDMALING.xlsx
+++ b/Översikt NORDMALING.xlsx
@@ -601,7 +601,7 @@
         <v>46205</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45168</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45183</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>45265</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>46139</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>45154</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>45158</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>46044</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>45920</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>45273</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>45219</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>45567</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>44694</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>44859</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>45239</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>45873</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>44806</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>44728</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>46042</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>46043</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>45575</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>44721</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>45077</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>44820</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>44904</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>44964</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>45574</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>45400</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>45238</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>46032</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>45283</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>45283</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>45265</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>45713</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>44648</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         <v>44802</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>44495</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>44495</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         <v>44859</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>44859</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>44788</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>44547</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>44908</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>45570</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>46072</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>46129</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>45999</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>45999</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>46002</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>45824</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
         <v>45651</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>45275</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>46181</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         <v>45145</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>46205</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>45166</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>45158</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         <v>45618</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         <v>45693</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         <v>45343</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         <v>44519</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>46183</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>44858</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>44487</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>44510</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>44818</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>44859</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>44851</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
         <v>44651</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>44867</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>44867</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8116,7 +8116,7 @@
         <v>44866</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8189,7 +8189,7 @@
         <v>44859</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>44744</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>44859</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         <v>44859</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>44833</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8579,7 +8579,7 @@
         <v>44565</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>44651</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>44487</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8803,7 +8803,7 @@
         <v>44657</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>44687</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>44759</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         <v>44859</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>44859</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>44854</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         <v>44832</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>44830</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>44868</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9490,7 +9490,7 @@
         <v>44473</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>44469</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>44620</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>44861</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         <v>44621</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>44655</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         <v>45772</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>44763</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>45378</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>45092</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>45096</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         <v>45126</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         <v>44812</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>45419</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>44886</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         <v>44480</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>45216</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10751,7 +10751,7 @@
         <v>45245</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>45265</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         <v>44909</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>45489</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>46018</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>46018</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         <v>46018</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>46020</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>45443</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>46020</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>45525</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>45453</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>46022</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>44964</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>46028</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>45021</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>45796</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>44515</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
         <v>45699</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>44921</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12231,7 +12231,7 @@
         <v>46029</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>46029</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         <v>45883</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12450,7 +12450,7 @@
         <v>44922</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>46032</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>45887</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>45888</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>45482</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
         <v>44977</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12893,7 +12893,7 @@
         <v>45470</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         <v>46037</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13039,7 +13039,7 @@
         <v>46038</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>45894</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>45796</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>45891</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>45327</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>46042</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>46042</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>45896</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13628,7 +13628,7 @@
         <v>46041</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13701,7 +13701,7 @@
         <v>45898</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>46043</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13847,7 +13847,7 @@
         <v>45901</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>46048</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>46045</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14066,7 +14066,7 @@
         <v>45900</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14139,7 +14139,7 @@
         <v>45638</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>45538</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>45590</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         <v>45835</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>45900</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>45589</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>46050</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>45903</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>45126</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14801,7 +14801,7 @@
         <v>46050</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>45799</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         <v>45491</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         <v>46056</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>45911</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
         <v>46058</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15244,7 +15244,7 @@
         <v>46058</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>46058</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15395,7 +15395,7 @@
         <v>45343</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15473,7 +15473,7 @@
         <v>45349</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
         <v>46062</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15619,7 +15619,7 @@
         <v>45917</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15692,7 +15692,7 @@
         <v>45917</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>44991</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15843,7 +15843,7 @@
         <v>45917</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15916,7 +15916,7 @@
         <v>45917</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>46065</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>46065</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         <v>46066</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16208,7 +16208,7 @@
         <v>45923</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>45923</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>46072</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16427,7 +16427,7 @@
         <v>44609</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16500,7 +16500,7 @@
         <v>46072</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>44908</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16651,7 +16651,7 @@
         <v>46076</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16724,7 +16724,7 @@
         <v>46072</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>45926</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16875,7 +16875,7 @@
         <v>45232</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16948,7 +16948,7 @@
         <v>45929</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>45929</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17094,7 +17094,7 @@
         <v>45929</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17167,7 +17167,7 @@
         <v>45238</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>45586</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17313,7 +17313,7 @@
         <v>45932</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17391,7 +17391,7 @@
         <v>45936</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         <v>44473</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>45688</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17620,7 +17620,7 @@
         <v>45938</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17693,7 +17693,7 @@
         <v>45938</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>44905</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17844,7 +17844,7 @@
         <v>46094</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17917,7 +17917,7 @@
         <v>46094</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17990,7 +17990,7 @@
         <v>46094</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18063,7 +18063,7 @@
         <v>45344</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18136,7 +18136,7 @@
         <v>45940</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18209,7 +18209,7 @@
         <v>45940</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18282,7 +18282,7 @@
         <v>44977</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18360,7 +18360,7 @@
         <v>45607</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18433,7 +18433,7 @@
         <v>45141</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18506,7 +18506,7 @@
         <v>45944</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>45946</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18652,7 +18652,7 @@
         <v>44753</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18730,7 +18730,7 @@
         <v>45946</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18803,7 +18803,7 @@
         <v>45049</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         <v>45569</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18954,7 +18954,7 @@
         <v>44722</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19032,7 +19032,7 @@
         <v>45950</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19105,7 +19105,7 @@
         <v>45950</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19178,7 +19178,7 @@
         <v>45951</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19251,7 +19251,7 @@
         <v>45951</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19324,7 +19324,7 @@
         <v>46108</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19402,7 +19402,7 @@
         <v>45953</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19475,7 +19475,7 @@
         <v>46111</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>46108</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19621,7 +19621,7 @@
         <v>46113</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19694,7 +19694,7 @@
         <v>46113</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19767,7 +19767,7 @@
         <v>45960</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         <v>45959</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
         <v>45960</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19986,7 +19986,7 @@
         <v>45962</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>45964</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20137,7 +20137,7 @@
         <v>44812</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20210,7 +20210,7 @@
         <v>45964</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20283,7 +20283,7 @@
         <v>45961</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20356,7 +20356,7 @@
         <v>46125</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20429,7 +20429,7 @@
         <v>45965</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20502,7 +20502,7 @@
         <v>45966</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20575,7 +20575,7 @@
         <v>45965</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20648,7 +20648,7 @@
         <v>46125</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20721,7 +20721,7 @@
         <v>46127</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20794,7 +20794,7 @@
         <v>45965</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20867,7 +20867,7 @@
         <v>45034</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20940,7 +20940,7 @@
         <v>45525</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21013,7 +21013,7 @@
         <v>45972</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21086,7 +21086,7 @@
         <v>45972</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21159,7 +21159,7 @@
         <v>45974</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21232,7 +21232,7 @@
         <v>46129</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21305,7 +21305,7 @@
         <v>45075</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>44977</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21456,7 +21456,7 @@
         <v>46132</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21529,7 +21529,7 @@
         <v>46132</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21602,7 +21602,7 @@
         <v>45979</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         <v>45979</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21748,7 +21748,7 @@
         <v>45979</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21821,7 +21821,7 @@
         <v>45980</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21899,7 +21899,7 @@
         <v>45119</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21972,7 +21972,7 @@
         <v>45469</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>45981</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22118,7 +22118,7 @@
         <v>45982</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>45981</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22269,7 +22269,7 @@
         <v>45981</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22342,7 +22342,7 @@
         <v>45986</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22415,7 +22415,7 @@
         <v>45986</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22488,7 +22488,7 @@
         <v>45986</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22566,7 +22566,7 @@
         <v>45986</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>46135</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22712,7 +22712,7 @@
         <v>45800</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22785,7 +22785,7 @@
         <v>45988</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>46135</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22936,7 +22936,7 @@
         <v>45187</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         <v>45147</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23082,7 +23082,7 @@
         <v>45147</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23155,7 +23155,7 @@
         <v>45866</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23228,7 +23228,7 @@
         <v>45993</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>45988</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23374,7 +23374,7 @@
         <v>45994</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23447,7 +23447,7 @@
         <v>45993</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23525,7 +23525,7 @@
         <v>46050</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23598,7 +23598,7 @@
         <v>45877</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23671,7 +23671,7 @@
         <v>45994</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>45988</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>44742</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
         <v>45799</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23963,7 +23963,7 @@
         <v>45926</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24036,7 +24036,7 @@
         <v>46000</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24109,7 +24109,7 @@
         <v>46139</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24182,7 +24182,7 @@
         <v>46000</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24260,7 +24260,7 @@
         <v>45929</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24333,7 +24333,7 @@
         <v>46000</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>46003</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24489,7 +24489,7 @@
         <v>46003</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24567,7 +24567,7 @@
         <v>46006</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24645,7 +24645,7 @@
         <v>45187</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24718,7 +24718,7 @@
         <v>46006</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24791,7 +24791,7 @@
         <v>46006</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24864,7 +24864,7 @@
         <v>46006</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24937,7 +24937,7 @@
         <v>46006</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25010,7 +25010,7 @@
         <v>46006</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25083,7 +25083,7 @@
         <v>46006</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25156,7 +25156,7 @@
         <v>45021</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25229,7 +25229,7 @@
         <v>45763</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25307,7 +25307,7 @@
         <v>45147</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25380,7 +25380,7 @@
         <v>45618</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>46009</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25526,7 +25526,7 @@
         <v>46010</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>46010</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25672,7 +25672,7 @@
         <v>45552</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25745,7 +25745,7 @@
         <v>45051</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25818,7 +25818,7 @@
         <v>45147</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25891,7 +25891,7 @@
         <v>46010</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25964,7 +25964,7 @@
         <v>45147</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26037,7 +26037,7 @@
         <v>45147</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26110,7 +26110,7 @@
         <v>45147</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26183,7 +26183,7 @@
         <v>46009</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26256,7 +26256,7 @@
         <v>46009</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26329,7 +26329,7 @@
         <v>46029</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26402,7 +26402,7 @@
         <v>45965</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26475,7 +26475,7 @@
         <v>45961</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>45890</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>45028</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>45825</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26767,7 +26767,7 @@
         <v>44907</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26840,7 +26840,7 @@
         <v>45586</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26913,7 +26913,7 @@
         <v>44533</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>45996</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27059,7 +27059,7 @@
         <v>45825</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27132,7 +27132,7 @@
         <v>45825</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27205,7 +27205,7 @@
         <v>45981</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27278,7 +27278,7 @@
         <v>45173</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27351,7 +27351,7 @@
         <v>46141</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27424,7 +27424,7 @@
         <v>45503</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27497,7 +27497,7 @@
         <v>45825</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
         <v>45825</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27643,7 +27643,7 @@
         <v>45524</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>45736</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27789,7 +27789,7 @@
         <v>45280</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27867,7 +27867,7 @@
         <v>44943</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27940,7 +27940,7 @@
         <v>44531</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28013,7 +28013,7 @@
         <v>44834</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28091,7 +28091,7 @@
         <v>45102</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28164,7 +28164,7 @@
         <v>45145</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28242,7 +28242,7 @@
         <v>46151</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28315,7 +28315,7 @@
         <v>45343</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>45757</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28461,7 +28461,7 @@
         <v>46151</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28534,7 +28534,7 @@
         <v>44812</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28607,7 +28607,7 @@
         <v>45378</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28680,7 +28680,7 @@
         <v>46155</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28753,7 +28753,7 @@
         <v>45419</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28826,7 +28826,7 @@
         <v>45096</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28904,7 +28904,7 @@
         <v>45838</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28977,7 +28977,7 @@
         <v>45835</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29050,7 +29050,7 @@
         <v>44859</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29128,7 +29128,7 @@
         <v>46155</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29201,7 +29201,7 @@
         <v>46160</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29274,7 +29274,7 @@
         <v>45105</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29352,7 +29352,7 @@
         <v>45491</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29425,7 +29425,7 @@
         <v>46161</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>46161</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29571,7 +29571,7 @@
         <v>45231</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29644,7 +29644,7 @@
         <v>44893</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29722,7 +29722,7 @@
         <v>46160</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29795,7 +29795,7 @@
         <v>45841</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29868,7 +29868,7 @@
         <v>46161</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29941,7 +29941,7 @@
         <v>46161</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30014,7 +30014,7 @@
         <v>46161</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30087,7 +30087,7 @@
         <v>44949</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30160,7 +30160,7 @@
         <v>45842</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30238,7 +30238,7 @@
         <v>45846</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30311,7 +30311,7 @@
         <v>45245</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30384,7 +30384,7 @@
         <v>46162</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30462,7 +30462,7 @@
         <v>45139</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30540,7 +30540,7 @@
         <v>45187</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30613,7 +30613,7 @@
         <v>45187</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30686,7 +30686,7 @@
         <v>45562</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30759,7 +30759,7 @@
         <v>44896</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30837,7 +30837,7 @@
         <v>45691</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30910,7 +30910,7 @@
         <v>45622</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30983,7 +30983,7 @@
         <v>45849</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31056,7 +31056,7 @@
         <v>45852</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31129,7 +31129,7 @@
         <v>45569</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31202,7 +31202,7 @@
         <v>45575</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31275,7 +31275,7 @@
         <v>46171</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31348,7 +31348,7 @@
         <v>45344</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31421,7 +31421,7 @@
         <v>45470</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>45764</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31567,7 +31567,7 @@
         <v>46174</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31640,7 +31640,7 @@
         <v>45866</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31713,7 +31713,7 @@
         <v>45867</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31786,7 +31786,7 @@
         <v>45447</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31864,7 +31864,7 @@
         <v>44531</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31937,7 +31937,7 @@
         <v>46174</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32010,7 +32010,7 @@
         <v>46174</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32083,7 +32083,7 @@
         <v>46176</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32156,7 +32156,7 @@
         <v>45141</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32229,7 +32229,7 @@
         <v>44540</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>45457</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32375,7 +32375,7 @@
         <v>45180</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32453,7 +32453,7 @@
         <v>46178</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32526,7 +32526,7 @@
         <v>45673</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32599,7 +32599,7 @@
         <v>45022</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32677,7 +32677,7 @@
         <v>45593</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32750,7 +32750,7 @@
         <v>44981</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32823,7 +32823,7 @@
         <v>45615</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32896,7 +32896,7 @@
         <v>45141</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32969,7 +32969,7 @@
         <v>45587</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33042,7 +33042,7 @@
         <v>45158</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33115,7 +33115,7 @@
         <v>46185</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33188,7 +33188,7 @@
         <v>45678</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33261,7 +33261,7 @@
         <v>46188</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33334,7 +33334,7 @@
         <v>45922</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>44993</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33480,7 +33480,7 @@
         <v>45524</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33553,7 +33553,7 @@
         <v>45574</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33626,7 +33626,7 @@
         <v>45330</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33704,7 +33704,7 @@
         <v>45525</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33777,7 +33777,7 @@
         <v>46195</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33850,7 +33850,7 @@
         <v>45182</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33923,7 +33923,7 @@
         <v>46197</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33996,7 +33996,7 @@
         <v>46197</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>45187</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34142,7 +34142,7 @@
         <v>45462</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34215,7 +34215,7 @@
         <v>45462</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34288,7 +34288,7 @@
         <v>45775</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34361,7 +34361,7 @@
         <v>46196</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34434,7 +34434,7 @@
         <v>45638</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34507,7 +34507,7 @@
         <v>46199</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34580,7 +34580,7 @@
         <v>45712</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34653,7 +34653,7 @@
         <v>46202</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>45883</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34799,7 +34799,7 @@
         <v>45420</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34877,7 +34877,7 @@
         <v>46205</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34950,7 +34950,7 @@
         <v>46205</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35023,7 +35023,7 @@
         <v>46205</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35096,7 +35096,7 @@
         <v>46205</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35169,7 +35169,7 @@
         <v>46205</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35242,7 +35242,7 @@
         <v>46205</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>45062</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>44854</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35461,7 +35461,7 @@
         <v>44859</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35539,7 +35539,7 @@
         <v>45607</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35612,7 +35612,7 @@
         <v>44547</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35685,7 +35685,7 @@
         <v>45638</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35758,7 +35758,7 @@
         <v>44789</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35831,7 +35831,7 @@
         <v>46253</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35904,7 +35904,7 @@
         <v>46253</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35977,7 +35977,7 @@
         <v>45204</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36050,7 +36050,7 @@
         <v>45140</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36128,7 +36128,7 @@
         <v>45139</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36206,7 +36206,7 @@
         <v>46258</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36279,7 +36279,7 @@
         <v>46254</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36352,7 +36352,7 @@
         <v>46254</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36425,7 +36425,7 @@
         <v>45775</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36498,7 +36498,7 @@
         <v>45775</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36571,7 +36571,7 @@
         <v>46258</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>46258</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36722,7 +36722,7 @@
         <v>46258</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36795,7 +36795,7 @@
         <v>46134</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36868,7 +36868,7 @@
         <v>46258</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36941,7 +36941,7 @@
         <v>46212</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37014,7 +37014,7 @@
         <v>46258</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37087,7 +37087,7 @@
         <v>45237</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37160,7 +37160,7 @@
         <v>45167</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37238,7 +37238,7 @@
         <v>44687</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37311,7 +37311,7 @@
         <v>45988</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37384,7 +37384,7 @@
         <v>45665</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37457,7 +37457,7 @@
         <v>46262</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37535,7 +37535,7 @@
         <v>45239</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37608,7 +37608,7 @@
         <v>45158</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37681,7 +37681,7 @@
         <v>46262</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37759,7 +37759,7 @@
         <v>45770</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37832,7 +37832,7 @@
         <v>46136</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37905,7 +37905,7 @@
         <v>44756</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37983,7 +37983,7 @@
         <v>45265</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38061,7 +38061,7 @@
         <v>46265</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38134,7 +38134,7 @@
         <v>46265</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38207,7 +38207,7 @@
         <v>46265</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38280,7 +38280,7 @@
         <v>46263</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38353,7 +38353,7 @@
         <v>46266</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38426,7 +38426,7 @@
         <v>46267</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38499,7 +38499,7 @@
         <v>46267</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38572,7 +38572,7 @@
         <v>46272</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38645,7 +38645,7 @@
         <v>45936</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38718,7 +38718,7 @@
         <v>44816</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38791,7 +38791,7 @@
         <v>44902</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38864,7 +38864,7 @@
         <v>46274</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38937,7 +38937,7 @@
         <v>44938</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         <v>45736</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39083,7 +39083,7 @@
         <v>46275</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39156,7 +39156,7 @@
         <v>46275</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39229,7 +39229,7 @@
         <v>45566</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39302,7 +39302,7 @@
         <v>45616</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39375,7 +39375,7 @@
         <v>46237</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39448,7 +39448,7 @@
         <v>45167</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39521,7 +39521,7 @@
         <v>46279</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39594,7 +39594,7 @@
         <v>45707</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39667,7 +39667,7 @@
         <v>46280</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39740,7 +39740,7 @@
         <v>46239</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>45505</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39896,7 +39896,7 @@
         <v>46239</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39974,7 +39974,7 @@
         <v>45536</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40047,7 +40047,7 @@
         <v>44922</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40120,7 +40120,7 @@
         <v>45433</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40193,7 +40193,7 @@
         <v>46274</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40266,7 +40266,7 @@
         <v>46286</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40339,7 +40339,7 @@
         <v>45775</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40412,7 +40412,7 @@
         <v>46245</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40485,7 +40485,7 @@
         <v>46245</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40558,7 +40558,7 @@
         <v>46245</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40631,7 +40631,7 @@
         <v>46245</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40704,7 +40704,7 @@
         <v>46245</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40777,7 +40777,7 @@
         <v>46244</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40850,7 +40850,7 @@
         <v>44916</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40928,7 +40928,7 @@
         <v>46245</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41001,7 +41001,7 @@
         <v>46245</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41074,7 +41074,7 @@
         <v>46245</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41147,7 +41147,7 @@
         <v>46245</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41220,7 +41220,7 @@
         <v>46245</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41293,7 +41293,7 @@
         <v>46245</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41366,7 +41366,7 @@
         <v>46244</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41439,7 +41439,7 @@
         <v>46266</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41512,7 +41512,7 @@
         <v>46245</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41585,7 +41585,7 @@
         <v>46287</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41658,7 +41658,7 @@
         <v>46245</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41731,7 +41731,7 @@
         <v>46245</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41804,7 +41804,7 @@
         <v>46244</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>46244</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41950,7 +41950,7 @@
         <v>46244</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42023,7 +42023,7 @@
         <v>46244</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42096,7 +42096,7 @@
         <v>46244</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42169,7 +42169,7 @@
         <v>46245</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42242,7 +42242,7 @@
         <v>46287</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42315,7 +42315,7 @@
         <v>46006</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42388,7 +42388,7 @@
         <v>44949</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42461,7 +42461,7 @@
         <v>46244</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42534,7 +42534,7 @@
         <v>46244</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42607,7 +42607,7 @@
         <v>46287</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42680,7 +42680,7 @@
         <v>44816</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42753,7 +42753,7 @@
         <v>44706</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42826,7 +42826,7 @@
         <v>45247</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42899,7 +42899,7 @@
         <v>45251</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42972,7 +42972,7 @@
         <v>45348</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43045,7 +43045,7 @@
         <v>45343</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43123,7 +43123,7 @@
         <v>46246</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43196,7 +43196,7 @@
         <v>46289</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43269,7 +43269,7 @@
         <v>44620</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43342,7 +43342,7 @@
         <v>45034</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43415,7 +43415,7 @@
         <v>45439</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43488,7 +43488,7 @@
         <v>44881</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43561,7 +43561,7 @@
         <v>45673</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43634,7 +43634,7 @@
         <v>44735</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43707,7 +43707,7 @@
         <v>45238</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43780,7 +43780,7 @@
         <v>44859</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43853,7 +43853,7 @@
         <v>45742</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43926,7 +43926,7 @@
         <v>45021</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43999,7 +43999,7 @@
         <v>45096</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44077,7 +44077,7 @@
         <v>44888</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44150,7 +44150,7 @@
         <v>44972</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44223,7 +44223,7 @@
         <v>45608</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44301,7 +44301,7 @@
         <v>45517</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44379,7 +44379,7 @@
         <v>45435</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44452,7 +44452,7 @@
         <v>45407</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44525,7 +44525,7 @@
         <v>45754</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44598,7 +44598,7 @@
         <v>45188</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44676,7 +44676,7 @@
         <v>44788</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44749,7 +44749,7 @@
         <v>45607</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44822,7 +44822,7 @@
         <v>44968</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44895,7 +44895,7 @@
         <v>45078</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44968,7 +44968,7 @@
         <v>45665</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>45676</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45114,7 +45114,7 @@
         <v>45713</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45187,7 +45187,7 @@
         <v>45264</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45265,7 +45265,7 @@
         <v>45241</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45338,7 +45338,7 @@
         <v>45568</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45411,7 +45411,7 @@
         <v>45568</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45484,7 +45484,7 @@
         <v>45664</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45562,7 +45562,7 @@
         <v>45429</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45635,7 +45635,7 @@
         <v>45764</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45708,7 +45708,7 @@
         <v>45204</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45781,7 +45781,7 @@
         <v>45030</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45859,7 +45859,7 @@
         <v>45783</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45932,7 +45932,7 @@
         <v>45783</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46005,7 +46005,7 @@
         <v>45261</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46078,7 +46078,7 @@
         <v>45603</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46151,7 +46151,7 @@
         <v>45790</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46224,7 +46224,7 @@
         <v>45790</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46297,7 +46297,7 @@
         <v>45036</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46370,7 +46370,7 @@
         <v>45789</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46443,7 +46443,7 @@
         <v>45790</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46516,7 +46516,7 @@
         <v>45790</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46589,7 +46589,7 @@
         <v>44603</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46667,7 +46667,7 @@
         <v>44559</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46745,7 +46745,7 @@
         <v>45567</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46823,7 +46823,7 @@
         <v>44489</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46896,7 +46896,7 @@
         <v>45667</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46974,7 +46974,7 @@
         <v>44517</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47047,7 +47047,7 @@
         <v>45250</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47125,7 +47125,7 @@
         <v>45638</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47198,7 +47198,7 @@
         <v>45762</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47271,7 +47271,7 @@
         <v>45762</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47344,7 +47344,7 @@
         <v>46070</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47422,7 +47422,7 @@
         <v>46071</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47495,7 +47495,7 @@
         <v>46071</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47568,7 +47568,7 @@
         <v>46071</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47641,7 +47641,7 @@
         <v>46135</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47714,7 +47714,7 @@
         <v>46148</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>

--- a/Översikt NORDMALING.xlsx
+++ b/Översikt NORDMALING.xlsx
@@ -601,7 +601,7 @@
         <v>46205</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45168</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45183</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>45265</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>46139</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>45158</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>45154</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>46044</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>45920</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>45273</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>45219</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>45567</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>44694</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>44859</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>44806</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>45873</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>45239</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>44728</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>45574</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>44964</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>46043</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>46042</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>45575</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>45077</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>44820</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>44904</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>46295</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>44721</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>45400</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>46032</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>45283</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v>45283</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>45713</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>45265</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>46294</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>45238</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>44648</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>44802</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>44495</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>44495</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
         <v>44859</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>44859</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         <v>45275</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>45158</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>46002</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>46072</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>45824</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>46129</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>45999</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         <v>45999</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>45343</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>45570</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>45693</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         <v>45618</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>44788</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         <v>46181</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         <v>45166</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6908,7 +6908,7 @@
         <v>46205</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7013,7 +7013,7 @@
         <v>44908</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         <v>45651</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>45145</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>44547</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>44519</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         <v>46183</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
         <v>44858</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>44487</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>44818</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>44859</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         <v>44851</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         <v>44510</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>44651</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         <v>44867</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>44867</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>44866</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>44859</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>44744</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>44859</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
         <v>44859</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>44833</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         <v>44565</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>44651</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         <v>44487</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>44657</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>44687</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         <v>44759</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>44859</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>44859</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>44854</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>44832</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>44830</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>44868</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9708,7 +9708,7 @@
         <v>44473</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9781,7 +9781,7 @@
         <v>44620</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>44861</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9932,7 +9932,7 @@
         <v>44621</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>44655</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>45736</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>44964</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>45447</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>45182</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>45062</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>45167</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>44968</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>44922</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>44756</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>45096</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>45141</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
         <v>45204</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         <v>45664</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>45590</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         <v>45665</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>45204</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11271,7 +11271,7 @@
         <v>44991</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>45158</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>44921</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         <v>44735</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>45603</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>45407</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         <v>46000</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>45261</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11865,7 +11865,7 @@
         <v>45021</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>45789</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12011,7 +12011,7 @@
         <v>45622</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>46003</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>46003</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12240,7 +12240,7 @@
         <v>45757</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>45887</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>46006</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
         <v>46006</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>46006</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>46006</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>46006</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12756,7 +12756,7 @@
         <v>46006</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>46006</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
         <v>46009</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>46009</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>46009</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>45469</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>45147</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>45147</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>45790</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>45147</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>45147</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13559,7 +13559,7 @@
         <v>46010</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>46010</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>46010</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
         <v>45790</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         <v>45790</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>45147</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13997,7 +13997,7 @@
         <v>45790</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14070,7 +14070,7 @@
         <v>46020</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14143,7 +14143,7 @@
         <v>46018</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>45888</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
         <v>46020</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>46018</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14435,7 +14435,7 @@
         <v>46018</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14508,7 +14508,7 @@
         <v>46022</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14581,7 +14581,7 @@
         <v>45891</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>45894</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>46029</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14805,7 +14805,7 @@
         <v>45036</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>45796</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>46028</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>45343</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15102,7 +15102,7 @@
         <v>44763</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15180,7 +15180,7 @@
         <v>44896</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15258,7 +15258,7 @@
         <v>46029</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>45896</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15404,7 +15404,7 @@
         <v>45901</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15477,7 +15477,7 @@
         <v>45900</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15550,7 +15550,7 @@
         <v>45835</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15623,7 +15623,7 @@
         <v>45900</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15696,7 +15696,7 @@
         <v>45898</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>46032</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>45903</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>44816</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>44981</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>46041</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16139,7 +16139,7 @@
         <v>46037</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16212,7 +16212,7 @@
         <v>46038</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16285,7 +16285,7 @@
         <v>45232</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>45505</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16436,7 +16436,7 @@
         <v>46042</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16509,7 +16509,7 @@
         <v>46042</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>45911</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16655,7 +16655,7 @@
         <v>45264</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16733,7 +16733,7 @@
         <v>46043</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>46045</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         <v>45796</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16952,7 +16952,7 @@
         <v>45917</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17025,7 +17025,7 @@
         <v>45699</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17098,7 +17098,7 @@
         <v>46048</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>45917</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17244,7 +17244,7 @@
         <v>45917</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17317,7 +17317,7 @@
         <v>45343</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17390,7 +17390,7 @@
         <v>45587</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17463,7 +17463,7 @@
         <v>45799</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>46050</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17609,7 +17609,7 @@
         <v>46050</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17682,7 +17682,7 @@
         <v>45917</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17755,7 +17755,7 @@
         <v>45491</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17828,7 +17828,7 @@
         <v>45238</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>45923</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17974,7 +17974,7 @@
         <v>45923</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18047,7 +18047,7 @@
         <v>46056</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         <v>45180</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18203,7 +18203,7 @@
         <v>45929</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18276,7 +18276,7 @@
         <v>45929</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
         <v>44977</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>45926</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18500,7 +18500,7 @@
         <v>45929</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18573,7 +18573,7 @@
         <v>46058</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>46058</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18724,7 +18724,7 @@
         <v>46058</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18797,7 +18797,7 @@
         <v>46062</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18870,7 +18870,7 @@
         <v>45607</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>45678</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>46065</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>46065</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>45932</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>46066</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>45936</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>45938</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>45938</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>46072</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>45940</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>46072</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>45940</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19829,7 +19829,7 @@
         <v>45688</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19902,7 +19902,7 @@
         <v>45187</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>46072</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20053,7 +20053,7 @@
         <v>44753</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>45944</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20204,7 +20204,7 @@
         <v>46076</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20277,7 +20277,7 @@
         <v>45245</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>45946</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>45673</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20496,7 +20496,7 @@
         <v>45946</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20569,7 +20569,7 @@
         <v>45951</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>45950</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         <v>45950</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20788,7 +20788,7 @@
         <v>45951</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20861,7 +20861,7 @@
         <v>44949</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20934,7 +20934,7 @@
         <v>45953</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>45419</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21080,7 +21080,7 @@
         <v>45247</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21153,7 +21153,7 @@
         <v>45589</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>45959</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21299,7 +21299,7 @@
         <v>44905</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21377,7 +21377,7 @@
         <v>45443</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21450,7 +21450,7 @@
         <v>45961</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>45960</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21596,7 +21596,7 @@
         <v>45960</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21669,7 +21669,7 @@
         <v>45964</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21742,7 +21742,7 @@
         <v>45962</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21820,7 +21820,7 @@
         <v>45965</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>45964</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>45965</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22039,7 +22039,7 @@
         <v>45965</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22112,7 +22112,7 @@
         <v>45966</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
         <v>46094</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>44916</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22336,7 +22336,7 @@
         <v>46094</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22409,7 +22409,7 @@
         <v>44515</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22482,7 +22482,7 @@
         <v>46094</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22555,7 +22555,7 @@
         <v>45972</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22628,7 +22628,7 @@
         <v>45608</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22706,7 +22706,7 @@
         <v>45096</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22784,7 +22784,7 @@
         <v>44949</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22857,7 +22857,7 @@
         <v>45049</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22935,7 +22935,7 @@
         <v>45974</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23008,7 +23008,7 @@
         <v>44922</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23081,7 +23081,7 @@
         <v>45470</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23154,7 +23154,7 @@
         <v>45979</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23227,7 +23227,7 @@
         <v>45979</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>45979</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23373,7 +23373,7 @@
         <v>45981</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23446,7 +23446,7 @@
         <v>46108</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23524,7 +23524,7 @@
         <v>45980</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23602,7 +23602,7 @@
         <v>45981</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23675,7 +23675,7 @@
         <v>46108</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>45982</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>46111</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23899,7 +23899,7 @@
         <v>45986</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23977,7 +23977,7 @@
         <v>46113</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24050,7 +24050,7 @@
         <v>46113</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24123,7 +24123,7 @@
         <v>45986</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24196,7 +24196,7 @@
         <v>45825</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24269,7 +24269,7 @@
         <v>45986</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>45825</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24415,7 +24415,7 @@
         <v>45986</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>45988</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24561,7 +24561,7 @@
         <v>45825</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24634,7 +24634,7 @@
         <v>45825</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24707,7 +24707,7 @@
         <v>45993</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24785,7 +24785,7 @@
         <v>45173</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         <v>45825</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>45988</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>45993</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25077,7 +25077,7 @@
         <v>45988</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>46125</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25223,7 +25223,7 @@
         <v>45994</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25296,7 +25296,7 @@
         <v>45994</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>46125</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25442,7 +25442,7 @@
         <v>46127</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>44687</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>45562</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25661,7 +25661,7 @@
         <v>45126</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25734,7 +25734,7 @@
         <v>46129</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25807,7 +25807,7 @@
         <v>44547</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25880,7 +25880,7 @@
         <v>46000</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25958,7 +25958,7 @@
         <v>46000</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26031,7 +26031,7 @@
         <v>44908</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26109,7 +26109,7 @@
         <v>45770</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26182,7 +26182,7 @@
         <v>46132</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>46132</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>44540</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>45141</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26474,7 +26474,7 @@
         <v>45051</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26547,7 +26547,7 @@
         <v>46135</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26625,7 +26625,7 @@
         <v>45712</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26698,7 +26698,7 @@
         <v>45713</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26771,7 +26771,7 @@
         <v>46135</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26844,7 +26844,7 @@
         <v>45343</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
         <v>46029</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26995,7 +26995,7 @@
         <v>45835</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27068,7 +27068,7 @@
         <v>45618</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27141,7 +27141,7 @@
         <v>45838</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         <v>45877</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27287,7 +27287,7 @@
         <v>45890</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27360,7 +27360,7 @@
         <v>44886</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27433,7 +27433,7 @@
         <v>45866</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27506,7 +27506,7 @@
         <v>45841</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27579,7 +27579,7 @@
         <v>44834</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27657,7 +27657,7 @@
         <v>45842</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         <v>45673</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27808,7 +27808,7 @@
         <v>45981</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27881,7 +27881,7 @@
         <v>45800</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>45638</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28032,7 +28032,7 @@
         <v>46139</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28105,7 +28105,7 @@
         <v>45846</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28178,7 +28178,7 @@
         <v>45536</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>45849</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28324,7 +28324,7 @@
         <v>45552</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28397,7 +28397,7 @@
         <v>45852</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28470,7 +28470,7 @@
         <v>45489</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         <v>45996</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28621,7 +28621,7 @@
         <v>45799</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28694,7 +28694,7 @@
         <v>44531</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28767,7 +28767,7 @@
         <v>45126</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28840,7 +28840,7 @@
         <v>45265</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>45926</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28991,7 +28991,7 @@
         <v>45265</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29069,7 +29069,7 @@
         <v>45102</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29142,7 +29142,7 @@
         <v>45929</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>44943</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29288,7 +29288,7 @@
         <v>46050</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29361,7 +29361,7 @@
         <v>45470</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29434,7 +29434,7 @@
         <v>44938</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29507,7 +29507,7 @@
         <v>45239</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29580,7 +29580,7 @@
         <v>45867</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29653,7 +29653,7 @@
         <v>45866</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         <v>46141</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29799,7 +29799,7 @@
         <v>45965</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44972</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29945,7 +29945,7 @@
         <v>44893</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30023,7 +30023,7 @@
         <v>45078</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30096,7 +30096,7 @@
         <v>45961</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>45525</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30242,7 +30242,7 @@
         <v>45021</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30315,7 +30315,7 @@
         <v>45092</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30388,7 +30388,7 @@
         <v>46151</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30461,7 +30461,7 @@
         <v>46151</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         <v>45607</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30607,7 +30607,7 @@
         <v>45607</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30680,7 +30680,7 @@
         <v>46155</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>46155</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30826,7 +30826,7 @@
         <v>45158</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30899,7 +30899,7 @@
         <v>45433</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30972,7 +30972,7 @@
         <v>45167</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31045,7 +31045,7 @@
         <v>46161</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31118,7 +31118,7 @@
         <v>45378</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31191,7 +31191,7 @@
         <v>46160</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31264,7 +31264,7 @@
         <v>46160</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31337,7 +31337,7 @@
         <v>44859</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31415,7 +31415,7 @@
         <v>46161</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31488,7 +31488,7 @@
         <v>46161</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31561,7 +31561,7 @@
         <v>46161</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31634,7 +31634,7 @@
         <v>46161</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31707,7 +31707,7 @@
         <v>46162</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         <v>45435</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31858,7 +31858,7 @@
         <v>45691</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31931,7 +31931,7 @@
         <v>45707</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32004,7 +32004,7 @@
         <v>44977</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32077,7 +32077,7 @@
         <v>45638</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32150,7 +32150,7 @@
         <v>45538</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32223,7 +32223,7 @@
         <v>44993</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32296,7 +32296,7 @@
         <v>45344</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32369,7 +32369,7 @@
         <v>45775</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32442,7 +32442,7 @@
         <v>46171</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32515,7 +32515,7 @@
         <v>46174</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32588,7 +32588,7 @@
         <v>46174</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32661,7 +32661,7 @@
         <v>44881</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32734,7 +32734,7 @@
         <v>46174</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32807,7 +32807,7 @@
         <v>44473</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32885,7 +32885,7 @@
         <v>45883</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32958,7 +32958,7 @@
         <v>45419</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33031,7 +33031,7 @@
         <v>45754</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33104,7 +33104,7 @@
         <v>45503</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33177,7 +33177,7 @@
         <v>46176</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33250,7 +33250,7 @@
         <v>45883</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33323,7 +33323,7 @@
         <v>45586</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>46178</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>45021</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33542,7 +33542,7 @@
         <v>45034</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33615,7 +33615,7 @@
         <v>45280</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33693,7 +33693,7 @@
         <v>46185</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33766,7 +33766,7 @@
         <v>45457</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33839,7 +33839,7 @@
         <v>46188</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33912,7 +33912,7 @@
         <v>45327</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33985,7 +33985,7 @@
         <v>45922</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>45615</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>45022</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34209,7 +34209,7 @@
         <v>46195</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34282,7 +34282,7 @@
         <v>46196</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34355,7 +34355,7 @@
         <v>45330</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34433,7 +34433,7 @@
         <v>44859</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34511,7 +34511,7 @@
         <v>46197</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34584,7 +34584,7 @@
         <v>46197</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34657,7 +34657,7 @@
         <v>44609</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34730,7 +34730,7 @@
         <v>46199</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34803,7 +34803,7 @@
         <v>46202</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34876,7 +34876,7 @@
         <v>46205</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34949,7 +34949,7 @@
         <v>46205</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35022,7 +35022,7 @@
         <v>46205</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35095,7 +35095,7 @@
         <v>46205</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35168,7 +35168,7 @@
         <v>45775</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35241,7 +35241,7 @@
         <v>45775</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35314,7 +35314,7 @@
         <v>46205</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35387,7 +35387,7 @@
         <v>46205</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35460,7 +35460,7 @@
         <v>45349</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35533,7 +35533,7 @@
         <v>44812</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35606,7 +35606,7 @@
         <v>45453</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>45568</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>45568</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35830,7 +35830,7 @@
         <v>46212</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35903,7 +35903,7 @@
         <v>46258</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>46258</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36049,7 +36049,7 @@
         <v>46134</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>46258</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36195,7 +36195,7 @@
         <v>46258</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36268,7 +36268,7 @@
         <v>44789</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36341,7 +36341,7 @@
         <v>46258</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36419,7 +36419,7 @@
         <v>45139</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36497,7 +36497,7 @@
         <v>46258</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36570,7 +36570,7 @@
         <v>45188</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36648,7 +36648,7 @@
         <v>45344</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>45593</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36794,7 +36794,7 @@
         <v>45988</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36867,7 +36867,7 @@
         <v>44533</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36940,7 +36940,7 @@
         <v>44812</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37013,7 +37013,7 @@
         <v>46265</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37086,7 +37086,7 @@
         <v>46265</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37159,7 +37159,7 @@
         <v>46265</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37232,7 +37232,7 @@
         <v>46262</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37310,7 +37310,7 @@
         <v>46136</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37383,7 +37383,7 @@
         <v>46262</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37461,7 +37461,7 @@
         <v>45525</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37534,7 +37534,7 @@
         <v>45075</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37607,7 +37607,7 @@
         <v>46267</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>46267</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37753,7 +37753,7 @@
         <v>46266</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37826,7 +37826,7 @@
         <v>45524</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37899,7 +37899,7 @@
         <v>44977</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>45482</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38050,7 +38050,7 @@
         <v>46263</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38123,7 +38123,7 @@
         <v>45586</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>44907</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38269,7 +38269,7 @@
         <v>46272</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38342,7 +38342,7 @@
         <v>45936</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38415,7 +38415,7 @@
         <v>46275</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38488,7 +38488,7 @@
         <v>46275</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38561,7 +38561,7 @@
         <v>44480</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38634,7 +38634,7 @@
         <v>46274</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38707,7 +38707,7 @@
         <v>46279</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38780,7 +38780,7 @@
         <v>46237</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38853,7 +38853,7 @@
         <v>46280</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38926,7 +38926,7 @@
         <v>44902</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>45231</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39072,7 +39072,7 @@
         <v>44909</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39150,7 +39150,7 @@
         <v>45105</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>46239</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39306,7 +39306,7 @@
         <v>44742</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39379,7 +39379,7 @@
         <v>45517</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39457,7 +39457,7 @@
         <v>46239</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39535,7 +39535,7 @@
         <v>45569</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39608,7 +39608,7 @@
         <v>46286</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>46287</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39754,7 +39754,7 @@
         <v>46244</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39827,7 +39827,7 @@
         <v>46287</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39900,7 +39900,7 @@
         <v>46244</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39973,7 +39973,7 @@
         <v>46244</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40046,7 +40046,7 @@
         <v>46244</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40119,7 +40119,7 @@
         <v>45574</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40192,7 +40192,7 @@
         <v>44888</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40265,7 +40265,7 @@
         <v>46244</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40338,7 +40338,7 @@
         <v>46006</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40411,7 +40411,7 @@
         <v>46244</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40484,7 +40484,7 @@
         <v>46287</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40557,7 +40557,7 @@
         <v>46244</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40630,7 +40630,7 @@
         <v>46244</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40703,7 +40703,7 @@
         <v>46244</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>46245</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40849,7 +40849,7 @@
         <v>46245</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40922,7 +40922,7 @@
         <v>46245</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40995,7 +40995,7 @@
         <v>46245</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41068,7 +41068,7 @@
         <v>46289</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41141,7 +41141,7 @@
         <v>45378</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41214,7 +41214,7 @@
         <v>46245</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41287,7 +41287,7 @@
         <v>46245</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41360,7 +41360,7 @@
         <v>46245</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41433,7 +41433,7 @@
         <v>46245</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>44706</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41579,7 +41579,7 @@
         <v>46245</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41652,7 +41652,7 @@
         <v>46245</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41725,7 +41725,7 @@
         <v>46245</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41798,7 +41798,7 @@
         <v>46266</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41871,7 +41871,7 @@
         <v>46245</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41944,7 +41944,7 @@
         <v>45028</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42017,7 +42017,7 @@
         <v>46245</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42090,7 +42090,7 @@
         <v>46246</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42163,7 +42163,7 @@
         <v>46245</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42236,7 +42236,7 @@
         <v>44788</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42309,7 +42309,7 @@
         <v>46293</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42382,7 +42382,7 @@
         <v>45525</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42455,7 +42455,7 @@
         <v>46293</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42528,7 +42528,7 @@
         <v>45524</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42601,7 +42601,7 @@
         <v>46295</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42679,7 +42679,7 @@
         <v>45736</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>46295</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42830,7 +42830,7 @@
         <v>46253</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42903,7 +42903,7 @@
         <v>46293</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42976,7 +42976,7 @@
         <v>46295</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43054,7 +43054,7 @@
         <v>45462</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43127,7 +43127,7 @@
         <v>45462</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43200,7 +43200,7 @@
         <v>45245</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43273,7 +43273,7 @@
         <v>46254</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43346,7 +43346,7 @@
         <v>44722</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43424,7 +43424,7 @@
         <v>45348</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43497,7 +43497,7 @@
         <v>45096</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43575,7 +43575,7 @@
         <v>44854</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43648,7 +43648,7 @@
         <v>45139</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43726,7 +43726,7 @@
         <v>45569</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43799,7 +43799,7 @@
         <v>44859</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43872,7 +43872,7 @@
         <v>46245</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43945,7 +43945,7 @@
         <v>46253</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44018,7 +44018,7 @@
         <v>46274</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44091,7 +44091,7 @@
         <v>46254</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44164,7 +44164,7 @@
         <v>45241</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44237,7 +44237,7 @@
         <v>45147</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44310,7 +44310,7 @@
         <v>45742</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44383,7 +44383,7 @@
         <v>45575</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44456,7 +44456,7 @@
         <v>45119</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44529,7 +44529,7 @@
         <v>45034</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44602,7 +44602,7 @@
         <v>45566</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44675,7 +44675,7 @@
         <v>44812</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44748,7 +44748,7 @@
         <v>45251</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44821,7 +44821,7 @@
         <v>45141</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44894,7 +44894,7 @@
         <v>45775</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44967,7 +44967,7 @@
         <v>45439</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45040,7 +45040,7 @@
         <v>45429</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45113,7 +45113,7 @@
         <v>44816</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45186,7 +45186,7 @@
         <v>45238</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45259,7 +45259,7 @@
         <v>44620</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45332,7 +45332,7 @@
         <v>45764</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45405,7 +45405,7 @@
         <v>45764</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45478,7 +45478,7 @@
         <v>45420</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45556,7 +45556,7 @@
         <v>45187</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45629,7 +45629,7 @@
         <v>45763</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45707,7 +45707,7 @@
         <v>45491</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45780,7 +45780,7 @@
         <v>45140</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45858,7 +45858,7 @@
         <v>45216</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45936,7 +45936,7 @@
         <v>45237</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46009,7 +46009,7 @@
         <v>45145</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46087,7 +46087,7 @@
         <v>44531</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>45147</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46233,7 +46233,7 @@
         <v>45676</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46306,7 +46306,7 @@
         <v>45187</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46379,7 +46379,7 @@
         <v>45187</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46452,7 +46452,7 @@
         <v>45772</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46525,7 +46525,7 @@
         <v>45187</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45616</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46671,7 +46671,7 @@
         <v>45665</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46744,7 +46744,7 @@
         <v>45638</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45030</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46895,7 +46895,7 @@
         <v>45783</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46968,7 +46968,7 @@
         <v>45783</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47041,7 +47041,7 @@
         <v>44603</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47119,7 +47119,7 @@
         <v>45567</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47197,7 +47197,7 @@
         <v>44489</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>44559</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47348,7 +47348,7 @@
         <v>45667</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47426,7 +47426,7 @@
         <v>44517</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47499,7 +47499,7 @@
         <v>45250</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47577,7 +47577,7 @@
         <v>45638</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47650,7 +47650,7 @@
         <v>45762</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47723,7 +47723,7 @@
         <v>45762</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47796,7 +47796,7 @@
         <v>46071</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47869,7 +47869,7 @@
         <v>46070</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47947,7 +47947,7 @@
         <v>46071</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>46071</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48093,7 +48093,7 @@
         <v>46135</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48166,7 +48166,7 @@
         <v>46148</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>

--- a/Översikt NORDMALING.xlsx
+++ b/Översikt NORDMALING.xlsx
@@ -601,7 +601,7 @@
         <v>46205</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45168</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45183</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>45265</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>46139</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>45158</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>45154</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>46044</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>45920</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>45273</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>45219</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>45567</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>44694</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>44859</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>44806</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>45873</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>45239</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>44728</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>45574</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>44964</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>46043</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>46042</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>45575</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>45077</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>44820</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>44904</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>46295</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>44721</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>45400</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>46032</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>45283</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v>45283</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>45713</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>45265</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>46294</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>45238</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>44648</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>44802</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>44495</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>44495</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
         <v>44859</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>44859</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         <v>45275</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>45158</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>46002</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>46072</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>45824</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>46129</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>45999</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         <v>45999</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>45343</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>45570</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>45693</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         <v>45618</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>44788</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         <v>46181</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         <v>45166</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6908,7 +6908,7 @@
         <v>46205</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7013,7 +7013,7 @@
         <v>44908</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         <v>45651</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>45145</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>44547</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>44519</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         <v>46183</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
         <v>44858</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>44487</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>44818</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>44859</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         <v>44851</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         <v>44510</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>44651</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         <v>44867</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>44867</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>44866</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>44859</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>44744</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>44859</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
         <v>44859</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>44833</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         <v>44565</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>44651</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         <v>44487</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>44657</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>44687</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         <v>44759</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>44859</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>44859</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>44854</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>44832</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>44830</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>44868</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9708,7 +9708,7 @@
         <v>44473</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9781,7 +9781,7 @@
         <v>44620</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>44861</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9932,7 +9932,7 @@
         <v>44621</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>44655</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>45736</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>44964</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>45447</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>45182</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>45062</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>45167</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>44968</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>44922</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>44756</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>45096</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>45141</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
         <v>45204</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         <v>45664</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>45590</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         <v>45665</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>45204</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11271,7 +11271,7 @@
         <v>44991</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>45158</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>44921</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         <v>44735</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>45603</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>45407</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         <v>46000</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>45261</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11865,7 +11865,7 @@
         <v>45021</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>45789</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12011,7 +12011,7 @@
         <v>45622</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>46003</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>46003</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12240,7 +12240,7 @@
         <v>45757</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>45887</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>46006</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
         <v>46006</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>46006</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>46006</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>46006</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12756,7 +12756,7 @@
         <v>46006</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>46006</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
         <v>46009</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>46009</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>46009</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>45469</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>45147</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>45147</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>45790</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>45147</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>45147</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13559,7 +13559,7 @@
         <v>46010</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>46010</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>46010</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
         <v>45790</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         <v>45790</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>45147</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13997,7 +13997,7 @@
         <v>45790</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14070,7 +14070,7 @@
         <v>46020</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14143,7 +14143,7 @@
         <v>46018</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>45888</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
         <v>46020</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>46018</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14435,7 +14435,7 @@
         <v>46018</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14508,7 +14508,7 @@
         <v>46022</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14581,7 +14581,7 @@
         <v>45891</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>45894</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>46029</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14805,7 +14805,7 @@
         <v>45036</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>45796</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>46028</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>45343</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15102,7 +15102,7 @@
         <v>44763</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15180,7 +15180,7 @@
         <v>44896</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15258,7 +15258,7 @@
         <v>46029</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>45896</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15404,7 +15404,7 @@
         <v>45901</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15477,7 +15477,7 @@
         <v>45900</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15550,7 +15550,7 @@
         <v>45835</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15623,7 +15623,7 @@
         <v>45900</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15696,7 +15696,7 @@
         <v>45898</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>46032</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>45903</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>44816</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>44981</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>46041</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16139,7 +16139,7 @@
         <v>46037</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16212,7 +16212,7 @@
         <v>46038</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16285,7 +16285,7 @@
         <v>45232</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>45505</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16436,7 +16436,7 @@
         <v>46042</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16509,7 +16509,7 @@
         <v>46042</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>45911</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16655,7 +16655,7 @@
         <v>45264</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16733,7 +16733,7 @@
         <v>46043</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>46045</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         <v>45796</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16952,7 +16952,7 @@
         <v>45917</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17025,7 +17025,7 @@
         <v>45699</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17098,7 +17098,7 @@
         <v>46048</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>45917</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17244,7 +17244,7 @@
         <v>45917</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17317,7 +17317,7 @@
         <v>45343</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17390,7 +17390,7 @@
         <v>45587</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17463,7 +17463,7 @@
         <v>45799</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>46050</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17609,7 +17609,7 @@
         <v>46050</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17682,7 +17682,7 @@
         <v>45917</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17755,7 +17755,7 @@
         <v>45491</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17828,7 +17828,7 @@
         <v>45238</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>45923</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17974,7 +17974,7 @@
         <v>45923</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18047,7 +18047,7 @@
         <v>46056</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         <v>45180</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18203,7 +18203,7 @@
         <v>45929</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18276,7 +18276,7 @@
         <v>45929</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
         <v>44977</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>45926</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18500,7 +18500,7 @@
         <v>45929</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18573,7 +18573,7 @@
         <v>46058</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>46058</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18724,7 +18724,7 @@
         <v>46058</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18797,7 +18797,7 @@
         <v>46062</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18870,7 +18870,7 @@
         <v>45607</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>45678</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>46065</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>46065</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>45932</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>46066</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>45936</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>45938</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>45938</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>46072</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>45940</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>46072</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>45940</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19829,7 +19829,7 @@
         <v>45688</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19902,7 +19902,7 @@
         <v>45187</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>46072</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20053,7 +20053,7 @@
         <v>44753</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>45944</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20204,7 +20204,7 @@
         <v>46076</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20277,7 +20277,7 @@
         <v>45245</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>45946</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>45673</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20496,7 +20496,7 @@
         <v>45946</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20569,7 +20569,7 @@
         <v>45951</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>45950</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         <v>45950</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20788,7 +20788,7 @@
         <v>45951</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20861,7 +20861,7 @@
         <v>44949</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20934,7 +20934,7 @@
         <v>45953</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>45419</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21080,7 +21080,7 @@
         <v>45247</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21153,7 +21153,7 @@
         <v>45589</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>45959</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21299,7 +21299,7 @@
         <v>44905</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21377,7 +21377,7 @@
         <v>45443</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21450,7 +21450,7 @@
         <v>45961</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>45960</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21596,7 +21596,7 @@
         <v>45960</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21669,7 +21669,7 @@
         <v>45964</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21742,7 +21742,7 @@
         <v>45962</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21820,7 +21820,7 @@
         <v>45965</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>45964</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>45965</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22039,7 +22039,7 @@
         <v>45965</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22112,7 +22112,7 @@
         <v>45966</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
         <v>46094</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>44916</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22336,7 +22336,7 @@
         <v>46094</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22409,7 +22409,7 @@
         <v>44515</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22482,7 +22482,7 @@
         <v>46094</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22555,7 +22555,7 @@
         <v>45972</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22628,7 +22628,7 @@
         <v>45608</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22706,7 +22706,7 @@
         <v>45096</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22784,7 +22784,7 @@
         <v>44949</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22857,7 +22857,7 @@
         <v>45049</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22935,7 +22935,7 @@
         <v>45974</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23008,7 +23008,7 @@
         <v>44922</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23081,7 +23081,7 @@
         <v>45470</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23154,7 +23154,7 @@
         <v>45979</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23227,7 +23227,7 @@
         <v>45979</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>45979</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23373,7 +23373,7 @@
         <v>45981</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23446,7 +23446,7 @@
         <v>46108</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23524,7 +23524,7 @@
         <v>45980</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23602,7 +23602,7 @@
         <v>45981</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23675,7 +23675,7 @@
         <v>46108</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>45982</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>46111</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23899,7 +23899,7 @@
         <v>45986</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23977,7 +23977,7 @@
         <v>46113</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24050,7 +24050,7 @@
         <v>46113</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24123,7 +24123,7 @@
         <v>45986</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24196,7 +24196,7 @@
         <v>45825</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24269,7 +24269,7 @@
         <v>45986</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>45825</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24415,7 +24415,7 @@
         <v>45986</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>45988</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24561,7 +24561,7 @@
         <v>45825</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24634,7 +24634,7 @@
         <v>45825</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24707,7 +24707,7 @@
         <v>45993</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24785,7 +24785,7 @@
         <v>45173</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         <v>45825</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>45988</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>45993</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25077,7 +25077,7 @@
         <v>45988</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>46125</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25223,7 +25223,7 @@
         <v>45994</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25296,7 +25296,7 @@
         <v>45994</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>46125</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25442,7 +25442,7 @@
         <v>46127</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>44687</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>45562</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25661,7 +25661,7 @@
         <v>45126</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25734,7 +25734,7 @@
         <v>46129</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25807,7 +25807,7 @@
         <v>44547</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25880,7 +25880,7 @@
         <v>46000</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25958,7 +25958,7 @@
         <v>46000</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26031,7 +26031,7 @@
         <v>44908</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26109,7 +26109,7 @@
         <v>45770</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26182,7 +26182,7 @@
         <v>46132</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>46132</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>44540</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>45141</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26474,7 +26474,7 @@
         <v>45051</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26547,7 +26547,7 @@
         <v>46135</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26625,7 +26625,7 @@
         <v>45712</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26698,7 +26698,7 @@
         <v>45713</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26771,7 +26771,7 @@
         <v>46135</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26844,7 +26844,7 @@
         <v>45343</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
         <v>46029</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26995,7 +26995,7 @@
         <v>45835</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27068,7 +27068,7 @@
         <v>45618</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27141,7 +27141,7 @@
         <v>45838</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         <v>45877</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27287,7 +27287,7 @@
         <v>45890</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27360,7 +27360,7 @@
         <v>44886</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27433,7 +27433,7 @@
         <v>45866</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27506,7 +27506,7 @@
         <v>45841</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27579,7 +27579,7 @@
         <v>44834</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27657,7 +27657,7 @@
         <v>45842</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         <v>45673</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27808,7 +27808,7 @@
         <v>45981</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27881,7 +27881,7 @@
         <v>45800</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>45638</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28032,7 +28032,7 @@
         <v>46139</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28105,7 +28105,7 @@
         <v>45846</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28178,7 +28178,7 @@
         <v>45536</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>45849</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28324,7 +28324,7 @@
         <v>45552</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28397,7 +28397,7 @@
         <v>45852</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28470,7 +28470,7 @@
         <v>45489</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         <v>45996</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28621,7 +28621,7 @@
         <v>45799</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28694,7 +28694,7 @@
         <v>44531</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28767,7 +28767,7 @@
         <v>45126</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28840,7 +28840,7 @@
         <v>45265</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>45926</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28991,7 +28991,7 @@
         <v>45265</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29069,7 +29069,7 @@
         <v>45102</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29142,7 +29142,7 @@
         <v>45929</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>44943</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29288,7 +29288,7 @@
         <v>46050</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29361,7 +29361,7 @@
         <v>45470</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29434,7 +29434,7 @@
         <v>44938</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29507,7 +29507,7 @@
         <v>45239</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29580,7 +29580,7 @@
         <v>45867</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29653,7 +29653,7 @@
         <v>45866</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         <v>46141</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29799,7 +29799,7 @@
         <v>45965</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44972</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29945,7 +29945,7 @@
         <v>44893</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30023,7 +30023,7 @@
         <v>45078</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30096,7 +30096,7 @@
         <v>45961</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>45525</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30242,7 +30242,7 @@
         <v>45021</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30315,7 +30315,7 @@
         <v>45092</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30388,7 +30388,7 @@
         <v>46151</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30461,7 +30461,7 @@
         <v>46151</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         <v>45607</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30607,7 +30607,7 @@
         <v>45607</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30680,7 +30680,7 @@
         <v>46155</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>46155</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30826,7 +30826,7 @@
         <v>45158</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30899,7 +30899,7 @@
         <v>45433</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30972,7 +30972,7 @@
         <v>45167</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31045,7 +31045,7 @@
         <v>46161</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31118,7 +31118,7 @@
         <v>45378</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31191,7 +31191,7 @@
         <v>46160</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31264,7 +31264,7 @@
         <v>46160</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31337,7 +31337,7 @@
         <v>44859</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31415,7 +31415,7 @@
         <v>46161</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31488,7 +31488,7 @@
         <v>46161</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31561,7 +31561,7 @@
         <v>46161</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31634,7 +31634,7 @@
         <v>46161</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31707,7 +31707,7 @@
         <v>46162</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         <v>45435</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31858,7 +31858,7 @@
         <v>45691</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31931,7 +31931,7 @@
         <v>45707</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32004,7 +32004,7 @@
         <v>44977</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32077,7 +32077,7 @@
         <v>45638</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32150,7 +32150,7 @@
         <v>45538</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32223,7 +32223,7 @@
         <v>44993</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32296,7 +32296,7 @@
         <v>45344</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32369,7 +32369,7 @@
         <v>45775</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32442,7 +32442,7 @@
         <v>46171</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32515,7 +32515,7 @@
         <v>46174</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32588,7 +32588,7 @@
         <v>46174</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32661,7 +32661,7 @@
         <v>44881</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32734,7 +32734,7 @@
         <v>46174</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32807,7 +32807,7 @@
         <v>44473</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32885,7 +32885,7 @@
         <v>45883</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32958,7 +32958,7 @@
         <v>45419</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33031,7 +33031,7 @@
         <v>45754</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33104,7 +33104,7 @@
         <v>45503</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33177,7 +33177,7 @@
         <v>46176</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33250,7 +33250,7 @@
         <v>45883</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33323,7 +33323,7 @@
         <v>45586</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>46178</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>45021</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33542,7 +33542,7 @@
         <v>45034</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33615,7 +33615,7 @@
         <v>45280</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33693,7 +33693,7 @@
         <v>46185</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33766,7 +33766,7 @@
         <v>45457</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33839,7 +33839,7 @@
         <v>46188</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33912,7 +33912,7 @@
         <v>45327</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33985,7 +33985,7 @@
         <v>45922</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>45615</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>45022</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34209,7 +34209,7 @@
         <v>46195</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34282,7 +34282,7 @@
         <v>46196</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34355,7 +34355,7 @@
         <v>45330</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34433,7 +34433,7 @@
         <v>44859</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34511,7 +34511,7 @@
         <v>46197</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34584,7 +34584,7 @@
         <v>46197</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34657,7 +34657,7 @@
         <v>44609</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34730,7 +34730,7 @@
         <v>46199</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34803,7 +34803,7 @@
         <v>46202</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34876,7 +34876,7 @@
         <v>46205</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34949,7 +34949,7 @@
         <v>46205</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35022,7 +35022,7 @@
         <v>46205</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35095,7 +35095,7 @@
         <v>46205</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35168,7 +35168,7 @@
         <v>45775</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35241,7 +35241,7 @@
         <v>45775</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35314,7 +35314,7 @@
         <v>46205</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35387,7 +35387,7 @@
         <v>46205</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35460,7 +35460,7 @@
         <v>45349</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35533,7 +35533,7 @@
         <v>44812</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35606,7 +35606,7 @@
         <v>45453</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>45568</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>45568</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35830,7 +35830,7 @@
         <v>46212</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35903,7 +35903,7 @@
         <v>46258</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>46258</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36049,7 +36049,7 @@
         <v>46134</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>46258</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36195,7 +36195,7 @@
         <v>46258</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36268,7 +36268,7 @@
         <v>44789</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36341,7 +36341,7 @@
         <v>46258</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36419,7 +36419,7 @@
         <v>45139</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36497,7 +36497,7 @@
         <v>46258</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36570,7 +36570,7 @@
         <v>45188</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36648,7 +36648,7 @@
         <v>45344</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>45593</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36794,7 +36794,7 @@
         <v>45988</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36867,7 +36867,7 @@
         <v>44533</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36940,7 +36940,7 @@
         <v>44812</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37013,7 +37013,7 @@
         <v>46265</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37086,7 +37086,7 @@
         <v>46265</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37159,7 +37159,7 @@
         <v>46265</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37232,7 +37232,7 @@
         <v>46262</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37310,7 +37310,7 @@
         <v>46136</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37383,7 +37383,7 @@
         <v>46262</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37461,7 +37461,7 @@
         <v>45525</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37534,7 +37534,7 @@
         <v>45075</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37607,7 +37607,7 @@
         <v>46267</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>46267</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37753,7 +37753,7 @@
         <v>46266</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37826,7 +37826,7 @@
         <v>45524</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37899,7 +37899,7 @@
         <v>44977</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>45482</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38050,7 +38050,7 @@
         <v>46263</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38123,7 +38123,7 @@
         <v>45586</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>44907</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38269,7 +38269,7 @@
         <v>46272</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38342,7 +38342,7 @@
         <v>45936</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38415,7 +38415,7 @@
         <v>46275</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38488,7 +38488,7 @@
         <v>46275</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38561,7 +38561,7 @@
         <v>44480</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38634,7 +38634,7 @@
         <v>46274</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38707,7 +38707,7 @@
         <v>46279</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38780,7 +38780,7 @@
         <v>46237</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38853,7 +38853,7 @@
         <v>46280</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38926,7 +38926,7 @@
         <v>44902</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>45231</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39072,7 +39072,7 @@
         <v>44909</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39150,7 +39150,7 @@
         <v>45105</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>46239</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39306,7 +39306,7 @@
         <v>44742</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39379,7 +39379,7 @@
         <v>45517</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39457,7 +39457,7 @@
         <v>46239</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39535,7 +39535,7 @@
         <v>45569</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39608,7 +39608,7 @@
         <v>46286</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>46287</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39754,7 +39754,7 @@
         <v>46244</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39827,7 +39827,7 @@
         <v>46287</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39900,7 +39900,7 @@
         <v>46244</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39973,7 +39973,7 @@
         <v>46244</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40046,7 +40046,7 @@
         <v>46244</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40119,7 +40119,7 @@
         <v>45574</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40192,7 +40192,7 @@
         <v>44888</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40265,7 +40265,7 @@
         <v>46244</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40338,7 +40338,7 @@
         <v>46006</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40411,7 +40411,7 @@
         <v>46244</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40484,7 +40484,7 @@
         <v>46287</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40557,7 +40557,7 @@
         <v>46244</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40630,7 +40630,7 @@
         <v>46244</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40703,7 +40703,7 @@
         <v>46244</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>46245</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40849,7 +40849,7 @@
         <v>46245</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40922,7 +40922,7 @@
         <v>46245</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40995,7 +40995,7 @@
         <v>46245</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41068,7 +41068,7 @@
         <v>46289</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41141,7 +41141,7 @@
         <v>45378</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41214,7 +41214,7 @@
         <v>46245</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41287,7 +41287,7 @@
         <v>46245</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41360,7 +41360,7 @@
         <v>46245</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41433,7 +41433,7 @@
         <v>46245</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>44706</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41579,7 +41579,7 @@
         <v>46245</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41652,7 +41652,7 @@
         <v>46245</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41725,7 +41725,7 @@
         <v>46245</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41798,7 +41798,7 @@
         <v>46266</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41871,7 +41871,7 @@
         <v>46245</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41944,7 +41944,7 @@
         <v>45028</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42017,7 +42017,7 @@
         <v>46245</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42090,7 +42090,7 @@
         <v>46246</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42163,7 +42163,7 @@
         <v>46245</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42236,7 +42236,7 @@
         <v>44788</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42309,7 +42309,7 @@
         <v>46293</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42382,7 +42382,7 @@
         <v>45525</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42455,7 +42455,7 @@
         <v>46293</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42528,7 +42528,7 @@
         <v>45524</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42601,7 +42601,7 @@
         <v>46295</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42679,7 +42679,7 @@
         <v>45736</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>46295</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42830,7 +42830,7 @@
         <v>46253</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42903,7 +42903,7 @@
         <v>46293</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42976,7 +42976,7 @@
         <v>46295</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43054,7 +43054,7 @@
         <v>45462</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43127,7 +43127,7 @@
         <v>45462</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43200,7 +43200,7 @@
         <v>45245</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43273,7 +43273,7 @@
         <v>46254</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43346,7 +43346,7 @@
         <v>44722</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43424,7 +43424,7 @@
         <v>45348</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43497,7 +43497,7 @@
         <v>45096</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43575,7 +43575,7 @@
         <v>44854</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43648,7 +43648,7 @@
         <v>45139</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43726,7 +43726,7 @@
         <v>45569</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43799,7 +43799,7 @@
         <v>44859</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43872,7 +43872,7 @@
         <v>46245</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43945,7 +43945,7 @@
         <v>46253</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44018,7 +44018,7 @@
         <v>46274</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44091,7 +44091,7 @@
         <v>46254</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44164,7 +44164,7 @@
         <v>45241</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44237,7 +44237,7 @@
         <v>45147</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44310,7 +44310,7 @@
         <v>45742</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44383,7 +44383,7 @@
         <v>45575</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44456,7 +44456,7 @@
         <v>45119</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44529,7 +44529,7 @@
         <v>45034</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44602,7 +44602,7 @@
         <v>45566</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44675,7 +44675,7 @@
         <v>44812</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44748,7 +44748,7 @@
         <v>45251</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44821,7 +44821,7 @@
         <v>45141</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44894,7 +44894,7 @@
         <v>45775</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44967,7 +44967,7 @@
         <v>45439</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45040,7 +45040,7 @@
         <v>45429</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45113,7 +45113,7 @@
         <v>44816</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45186,7 +45186,7 @@
         <v>45238</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45259,7 +45259,7 @@
         <v>44620</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45332,7 +45332,7 @@
         <v>45764</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45405,7 +45405,7 @@
         <v>45764</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45478,7 +45478,7 @@
         <v>45420</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45556,7 +45556,7 @@
         <v>45187</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45629,7 +45629,7 @@
         <v>45763</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45707,7 +45707,7 @@
         <v>45491</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45780,7 +45780,7 @@
         <v>45140</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45858,7 +45858,7 @@
         <v>45216</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45936,7 +45936,7 @@
         <v>45237</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46009,7 +46009,7 @@
         <v>45145</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46087,7 +46087,7 @@
         <v>44531</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>45147</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46233,7 +46233,7 @@
         <v>45676</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46306,7 +46306,7 @@
         <v>45187</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46379,7 +46379,7 @@
         <v>45187</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46452,7 +46452,7 @@
         <v>45772</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46525,7 +46525,7 @@
         <v>45187</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45616</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46671,7 +46671,7 @@
         <v>45665</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46744,7 +46744,7 @@
         <v>45638</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45030</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46895,7 +46895,7 @@
         <v>45783</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46968,7 +46968,7 @@
         <v>45783</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47041,7 +47041,7 @@
         <v>44603</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47119,7 +47119,7 @@
         <v>45567</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47197,7 +47197,7 @@
         <v>44489</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>44559</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47348,7 +47348,7 @@
         <v>45667</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47426,7 +47426,7 @@
         <v>44517</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47499,7 +47499,7 @@
         <v>45250</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47577,7 +47577,7 @@
         <v>45638</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47650,7 +47650,7 @@
         <v>45762</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47723,7 +47723,7 @@
         <v>45762</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47796,7 +47796,7 @@
         <v>46071</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47869,7 +47869,7 @@
         <v>46070</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47947,7 +47947,7 @@
         <v>46071</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>46071</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48093,7 +48093,7 @@
         <v>46135</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48166,7 +48166,7 @@
         <v>46148</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>

--- a/Översikt NORDMALING.xlsx
+++ b/Översikt NORDMALING.xlsx
@@ -601,7 +601,7 @@
         <v>46205</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45168</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45183</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>45265</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>46139</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>45158</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>45154</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>46044</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>45920</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>45273</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>45219</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>45567</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>44694</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>44859</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>44806</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>44728</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>45239</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>45873</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>45574</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>45575</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>44721</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>45077</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>44820</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>44904</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>46042</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>46043</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>44964</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>46295</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>45400</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>45238</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>45265</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         <v>45713</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>46032</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>45283</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>45283</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>46294</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>44648</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>44802</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>44495</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>44495</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
         <v>44859</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>44859</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         <v>45651</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>45275</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>44788</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>45693</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>45343</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>44547</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         <v>44908</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>45145</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>45570</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         <v>45166</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         <v>45824</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>45158</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>45999</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>45999</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>46129</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>46002</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>45618</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>46072</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>46181</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>46205</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>44519</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         <v>46183</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
         <v>44858</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>44487</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>44510</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>44818</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>44859</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         <v>44851</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>44651</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         <v>44867</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>44867</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>44866</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>44859</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>44744</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>44859</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
         <v>44859</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>44833</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         <v>44565</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>44651</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         <v>44487</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>44620</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>44832</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>44859</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         <v>44657</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>44687</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>44759</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>44854</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
         <v>44830</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         <v>44868</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>44859</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9781,7 +9781,7 @@
         <v>44861</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         <v>45378</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9932,7 +9932,7 @@
         <v>44621</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>45102</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>44655</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>45021</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>45096</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>44812</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>45126</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>45145</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>45092</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>45096</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>45419</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>45343</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>45757</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
         <v>44888</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         <v>44886</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>44812</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11115,7 +11115,7 @@
         <v>44972</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
         <v>45608</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
         <v>45378</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
         <v>45419</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>44763</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>45096</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>44859</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
         <v>45772</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>45517</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
         <v>45105</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>45491</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
         <v>45231</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>44480</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>44893</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>45435</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12245,7 +12245,7 @@
         <v>45407</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         <v>45754</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         <v>45216</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         <v>44949</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12542,7 +12542,7 @@
         <v>45245</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>45245</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>45188</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
         <v>45139</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
         <v>44909</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12922,7 +12922,7 @@
         <v>45187</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12995,7 +12995,7 @@
         <v>45187</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13068,7 +13068,7 @@
         <v>45265</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
         <v>45562</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13219,7 +13219,7 @@
         <v>44896</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>44788</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>45607</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>45622</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>45883</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>45489</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13667,7 +13667,7 @@
         <v>44968</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13740,7 +13740,7 @@
         <v>45078</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13813,7 +13813,7 @@
         <v>45443</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>45883</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>45525</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14032,7 +14032,7 @@
         <v>45453</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>45569</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14183,7 +14183,7 @@
         <v>45575</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         <v>44964</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>45344</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14402,7 +14402,7 @@
         <v>45665</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>45021</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>45887</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>45888</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>45676</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>45764</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14840,7 +14840,7 @@
         <v>44515</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14913,7 +14913,7 @@
         <v>45713</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>44921</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15059,7 +15059,7 @@
         <v>45264</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>45894</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>45796</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15283,7 +15283,7 @@
         <v>45891</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         <v>45896</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>45898</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>45241</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         <v>45901</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15653,7 +15653,7 @@
         <v>45568</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
         <v>45568</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15799,7 +15799,7 @@
         <v>44922</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15872,7 +15872,7 @@
         <v>45900</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>45482</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
         <v>44977</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>45835</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>45900</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16237,7 +16237,7 @@
         <v>45470</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16310,7 +16310,7 @@
         <v>45447</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16388,7 +16388,7 @@
         <v>44531</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16461,7 +16461,7 @@
         <v>45141</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>45903</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>45664</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16685,7 +16685,7 @@
         <v>45327</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>45429</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16831,7 +16831,7 @@
         <v>44540</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         <v>45764</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>45457</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>45204</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17123,7 +17123,7 @@
         <v>45638</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>45538</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>45590</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>45180</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>45911</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17498,7 +17498,7 @@
         <v>45589</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17571,7 +17571,7 @@
         <v>45126</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>45030</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>45673</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>45783</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17868,7 +17868,7 @@
         <v>45022</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17946,7 +17946,7 @@
         <v>45593</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>44981</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>45783</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
         <v>45615</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>45141</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18311,7 +18311,7 @@
         <v>45491</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>45587</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>45917</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18530,7 +18530,7 @@
         <v>45917</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18603,7 +18603,7 @@
         <v>45158</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18676,7 +18676,7 @@
         <v>45678</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18749,7 +18749,7 @@
         <v>45917</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18822,7 +18822,7 @@
         <v>45343</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18900,7 +18900,7 @@
         <v>45349</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18973,7 +18973,7 @@
         <v>45917</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19046,7 +19046,7 @@
         <v>45261</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>44991</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>45603</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19270,7 +19270,7 @@
         <v>44993</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>45524</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19416,7 +19416,7 @@
         <v>45790</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19489,7 +19489,7 @@
         <v>45790</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19562,7 +19562,7 @@
         <v>45036</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19635,7 +19635,7 @@
         <v>45789</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19708,7 +19708,7 @@
         <v>45923</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19781,7 +19781,7 @@
         <v>45923</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19854,7 +19854,7 @@
         <v>45790</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19927,7 +19927,7 @@
         <v>45574</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20000,7 +20000,7 @@
         <v>45790</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>45330</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>45525</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>44609</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>44908</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20375,7 +20375,7 @@
         <v>45926</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20448,7 +20448,7 @@
         <v>45182</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20521,7 +20521,7 @@
         <v>45929</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20594,7 +20594,7 @@
         <v>45929</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20667,7 +20667,7 @@
         <v>45232</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20740,7 +20740,7 @@
         <v>45929</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20813,7 +20813,7 @@
         <v>45187</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>45462</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>45462</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>45638</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>45796</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
         <v>45586</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21251,7 +21251,7 @@
         <v>45712</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>45699</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>45932</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>45936</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>44905</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21631,7 +21631,7 @@
         <v>45420</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21709,7 +21709,7 @@
         <v>45799</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>45344</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21855,7 +21855,7 @@
         <v>45062</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>44977</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22006,7 +22006,7 @@
         <v>45141</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>45938</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22152,7 +22152,7 @@
         <v>44753</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22230,7 +22230,7 @@
         <v>45049</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22308,7 +22308,7 @@
         <v>45569</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22381,7 +22381,7 @@
         <v>44722</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
         <v>45238</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22532,7 +22532,7 @@
         <v>45938</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22605,7 +22605,7 @@
         <v>44854</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22678,7 +22678,7 @@
         <v>44859</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22756,7 +22756,7 @@
         <v>45688</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22829,7 +22829,7 @@
         <v>45607</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
         <v>45940</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22975,7 +22975,7 @@
         <v>45940</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23048,7 +23048,7 @@
         <v>45607</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23121,7 +23121,7 @@
         <v>45944</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23194,7 +23194,7 @@
         <v>44547</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23267,7 +23267,7 @@
         <v>45638</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23340,7 +23340,7 @@
         <v>45946</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>44789</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23486,7 +23486,7 @@
         <v>45204</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23559,7 +23559,7 @@
         <v>45946</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23632,7 +23632,7 @@
         <v>45140</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23710,7 +23710,7 @@
         <v>45950</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23783,7 +23783,7 @@
         <v>45139</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23861,7 +23861,7 @@
         <v>45950</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>45775</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>45775</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24080,7 +24080,7 @@
         <v>44812</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24153,7 +24153,7 @@
         <v>45825</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>45825</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>45825</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24372,7 +24372,7 @@
         <v>45951</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24445,7 +24445,7 @@
         <v>45825</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24518,7 +24518,7 @@
         <v>45825</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>45951</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24664,7 +24664,7 @@
         <v>45034</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24737,7 +24737,7 @@
         <v>45237</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>45525</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         <v>45953</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
         <v>45960</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25029,7 +25029,7 @@
         <v>45959</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25102,7 +25102,7 @@
         <v>45960</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25175,7 +25175,7 @@
         <v>45962</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25253,7 +25253,7 @@
         <v>45964</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25326,7 +25326,7 @@
         <v>45075</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25399,7 +25399,7 @@
         <v>44977</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25477,7 +25477,7 @@
         <v>45167</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25555,7 +25555,7 @@
         <v>44687</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25628,7 +25628,7 @@
         <v>45838</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25701,7 +25701,7 @@
         <v>45835</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25774,7 +25774,7 @@
         <v>45665</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25847,7 +25847,7 @@
         <v>45964</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25920,7 +25920,7 @@
         <v>45239</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25993,7 +25993,7 @@
         <v>45961</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26066,7 +26066,7 @@
         <v>45158</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26139,7 +26139,7 @@
         <v>45965</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26212,7 +26212,7 @@
         <v>45966</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26285,7 +26285,7 @@
         <v>45965</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26358,7 +26358,7 @@
         <v>45770</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26431,7 +26431,7 @@
         <v>45119</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26504,7 +26504,7 @@
         <v>45469</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26577,7 +26577,7 @@
         <v>45965</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26650,7 +26650,7 @@
         <v>45841</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26723,7 +26723,7 @@
         <v>45842</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26801,7 +26801,7 @@
         <v>45846</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26874,7 +26874,7 @@
         <v>45972</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26947,7 +26947,7 @@
         <v>45187</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27020,7 +27020,7 @@
         <v>44756</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>45974</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27171,7 +27171,7 @@
         <v>45265</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27249,7 +27249,7 @@
         <v>45147</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27322,7 +27322,7 @@
         <v>45147</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27395,7 +27395,7 @@
         <v>45849</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>45852</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27541,7 +27541,7 @@
         <v>44742</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27614,7 +27614,7 @@
         <v>45470</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27687,7 +27687,7 @@
         <v>45866</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27760,7 +27760,7 @@
         <v>45867</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27833,7 +27833,7 @@
         <v>45187</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         <v>45979</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27979,7 +27979,7 @@
         <v>45021</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28052,7 +28052,7 @@
         <v>45979</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28125,7 +28125,7 @@
         <v>45763</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28203,7 +28203,7 @@
         <v>45979</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28276,7 +28276,7 @@
         <v>44816</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>45980</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28427,7 +28427,7 @@
         <v>44902</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28500,7 +28500,7 @@
         <v>45051</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28573,7 +28573,7 @@
         <v>45982</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28651,7 +28651,7 @@
         <v>45775</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28724,7 +28724,7 @@
         <v>45981</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28797,7 +28797,7 @@
         <v>44938</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28870,7 +28870,7 @@
         <v>45736</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28943,7 +28943,7 @@
         <v>45566</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29016,7 +29016,7 @@
         <v>45028</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29089,7 +29089,7 @@
         <v>44907</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29162,7 +29162,7 @@
         <v>45586</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44533</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29308,7 +29308,7 @@
         <v>45173</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29381,7 +29381,7 @@
         <v>45616</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>45986</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29527,7 +29527,7 @@
         <v>45167</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29600,7 +29600,7 @@
         <v>45707</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29673,7 +29673,7 @@
         <v>45503</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29746,7 +29746,7 @@
         <v>45986</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29819,7 +29819,7 @@
         <v>45986</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29897,7 +29897,7 @@
         <v>45986</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29970,7 +29970,7 @@
         <v>45524</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>45505</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30121,7 +30121,7 @@
         <v>46108</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30199,7 +30199,7 @@
         <v>45736</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>46111</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>46108</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30418,7 +30418,7 @@
         <v>45988</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30491,7 +30491,7 @@
         <v>45280</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30569,7 +30569,7 @@
         <v>45536</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30642,7 +30642,7 @@
         <v>44922</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30715,7 +30715,7 @@
         <v>44943</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30788,7 +30788,7 @@
         <v>46113</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30861,7 +30861,7 @@
         <v>46113</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30934,7 +30934,7 @@
         <v>44531</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         <v>44834</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31085,7 +31085,7 @@
         <v>45993</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31158,7 +31158,7 @@
         <v>45433</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31231,7 +31231,7 @@
         <v>45988</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31304,7 +31304,7 @@
         <v>45994</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31377,7 +31377,7 @@
         <v>45993</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31455,7 +31455,7 @@
         <v>45994</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31528,7 +31528,7 @@
         <v>45988</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31601,7 +31601,7 @@
         <v>46125</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31674,7 +31674,7 @@
         <v>46125</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31747,7 +31747,7 @@
         <v>45775</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31820,7 +31820,7 @@
         <v>46127</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31893,7 +31893,7 @@
         <v>46000</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31966,7 +31966,7 @@
         <v>46129</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32039,7 +32039,7 @@
         <v>46000</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32117,7 +32117,7 @@
         <v>46132</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32190,7 +32190,7 @@
         <v>44916</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32268,7 +32268,7 @@
         <v>46000</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>46132</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32419,7 +32419,7 @@
         <v>46003</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32497,7 +32497,7 @@
         <v>46003</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32575,7 +32575,7 @@
         <v>46006</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>46006</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32726,7 +32726,7 @@
         <v>46006</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32799,7 +32799,7 @@
         <v>46006</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32872,7 +32872,7 @@
         <v>46006</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32945,7 +32945,7 @@
         <v>46006</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>46006</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>44949</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33164,7 +33164,7 @@
         <v>44816</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33237,7 +33237,7 @@
         <v>46135</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33310,7 +33310,7 @@
         <v>45800</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33383,7 +33383,7 @@
         <v>44706</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33456,7 +33456,7 @@
         <v>46135</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33534,7 +33534,7 @@
         <v>45247</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33607,7 +33607,7 @@
         <v>45147</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33680,7 +33680,7 @@
         <v>45251</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33753,7 +33753,7 @@
         <v>45348</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>46009</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         <v>46010</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33972,7 +33972,7 @@
         <v>45343</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34050,7 +34050,7 @@
         <v>46010</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34123,7 +34123,7 @@
         <v>45147</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34196,7 +34196,7 @@
         <v>45866</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34269,7 +34269,7 @@
         <v>46010</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34342,7 +34342,7 @@
         <v>45147</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34415,7 +34415,7 @@
         <v>45147</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>45147</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34561,7 +34561,7 @@
         <v>46009</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>46009</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34707,7 +34707,7 @@
         <v>46050</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34780,7 +34780,7 @@
         <v>45877</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34853,7 +34853,7 @@
         <v>46018</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34926,7 +34926,7 @@
         <v>46018</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34999,7 +34999,7 @@
         <v>46018</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35072,7 +35072,7 @@
         <v>46020</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35145,7 +35145,7 @@
         <v>44620</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35218,7 +35218,7 @@
         <v>46020</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35291,7 +35291,7 @@
         <v>46022</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35364,7 +35364,7 @@
         <v>45799</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35437,7 +35437,7 @@
         <v>45926</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35510,7 +35510,7 @@
         <v>46028</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35583,7 +35583,7 @@
         <v>45034</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35656,7 +35656,7 @@
         <v>46139</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>45439</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35802,7 +35802,7 @@
         <v>45929</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>44881</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35948,7 +35948,7 @@
         <v>46029</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36021,7 +36021,7 @@
         <v>46029</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36094,7 +36094,7 @@
         <v>46032</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36172,7 +36172,7 @@
         <v>45618</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36245,7 +36245,7 @@
         <v>46037</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36318,7 +36318,7 @@
         <v>46038</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36391,7 +36391,7 @@
         <v>46042</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36464,7 +36464,7 @@
         <v>46042</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>45552</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>46041</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36683,7 +36683,7 @@
         <v>46029</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36756,7 +36756,7 @@
         <v>45965</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36829,7 +36829,7 @@
         <v>46043</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36902,7 +36902,7 @@
         <v>45673</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36975,7 +36975,7 @@
         <v>44735</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37048,7 +37048,7 @@
         <v>45961</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37121,7 +37121,7 @@
         <v>45890</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>46048</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37267,7 +37267,7 @@
         <v>46045</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37340,7 +37340,7 @@
         <v>45238</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37413,7 +37413,7 @@
         <v>45996</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>44859</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37559,7 +37559,7 @@
         <v>45742</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37632,7 +37632,7 @@
         <v>45981</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37705,7 +37705,7 @@
         <v>46141</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37778,7 +37778,7 @@
         <v>46050</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37851,7 +37851,7 @@
         <v>46050</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37924,7 +37924,7 @@
         <v>46056</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38002,7 +38002,7 @@
         <v>46058</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38075,7 +38075,7 @@
         <v>46058</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38148,7 +38148,7 @@
         <v>46058</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38226,7 +38226,7 @@
         <v>46062</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38299,7 +38299,7 @@
         <v>46065</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38372,7 +38372,7 @@
         <v>46065</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38445,7 +38445,7 @@
         <v>46066</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38518,7 +38518,7 @@
         <v>46151</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38591,7 +38591,7 @@
         <v>46072</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38664,7 +38664,7 @@
         <v>46072</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38737,7 +38737,7 @@
         <v>46076</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38810,7 +38810,7 @@
         <v>46072</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38888,7 +38888,7 @@
         <v>46151</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38961,7 +38961,7 @@
         <v>46155</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39034,7 +39034,7 @@
         <v>46155</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39107,7 +39107,7 @@
         <v>46160</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39180,7 +39180,7 @@
         <v>46161</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39253,7 +39253,7 @@
         <v>46161</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39326,7 +39326,7 @@
         <v>46094</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39399,7 +39399,7 @@
         <v>46094</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39472,7 +39472,7 @@
         <v>46094</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39545,7 +39545,7 @@
         <v>46160</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39618,7 +39618,7 @@
         <v>46161</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39691,7 +39691,7 @@
         <v>46161</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39764,7 +39764,7 @@
         <v>46161</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39837,7 +39837,7 @@
         <v>46162</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39915,7 +39915,7 @@
         <v>45691</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39988,7 +39988,7 @@
         <v>46171</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40061,7 +40061,7 @@
         <v>46174</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40134,7 +40134,7 @@
         <v>46174</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40207,7 +40207,7 @@
         <v>46174</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40280,7 +40280,7 @@
         <v>46176</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40353,7 +40353,7 @@
         <v>46178</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40426,7 +40426,7 @@
         <v>46185</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40499,7 +40499,7 @@
         <v>46188</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40572,7 +40572,7 @@
         <v>45922</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40645,7 +40645,7 @@
         <v>46195</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40718,7 +40718,7 @@
         <v>46197</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40791,7 +40791,7 @@
         <v>46197</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>46196</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40937,7 +40937,7 @@
         <v>46199</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41010,7 +41010,7 @@
         <v>46202</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41083,7 +41083,7 @@
         <v>46205</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41156,7 +41156,7 @@
         <v>46205</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>46205</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41302,7 +41302,7 @@
         <v>46205</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41375,7 +41375,7 @@
         <v>46205</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41448,7 +41448,7 @@
         <v>46205</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41521,7 +41521,7 @@
         <v>46134</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41594,7 +41594,7 @@
         <v>46212</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41667,7 +41667,7 @@
         <v>45988</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41740,7 +41740,7 @@
         <v>46136</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41813,7 +41813,7 @@
         <v>46265</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41886,7 +41886,7 @@
         <v>46265</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41959,7 +41959,7 @@
         <v>46265</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>46263</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42105,7 +42105,7 @@
         <v>46266</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42178,7 +42178,7 @@
         <v>46267</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42251,7 +42251,7 @@
         <v>46267</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42324,7 +42324,7 @@
         <v>46272</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42397,7 +42397,7 @@
         <v>45936</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42470,7 +42470,7 @@
         <v>46274</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42543,7 +42543,7 @@
         <v>46275</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42616,7 +42616,7 @@
         <v>46275</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42689,7 +42689,7 @@
         <v>46237</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42762,7 +42762,7 @@
         <v>46279</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42835,7 +42835,7 @@
         <v>46280</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42908,7 +42908,7 @@
         <v>46239</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42986,7 +42986,7 @@
         <v>46239</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43064,7 +43064,7 @@
         <v>46286</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43137,7 +43137,7 @@
         <v>46245</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43210,7 +43210,7 @@
         <v>46245</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43283,7 +43283,7 @@
         <v>46245</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43356,7 +43356,7 @@
         <v>46245</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43429,7 +43429,7 @@
         <v>46244</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43502,7 +43502,7 @@
         <v>46245</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43575,7 +43575,7 @@
         <v>46245</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43648,7 +43648,7 @@
         <v>46245</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43721,7 +43721,7 @@
         <v>46245</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43794,7 +43794,7 @@
         <v>46245</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43867,7 +43867,7 @@
         <v>46245</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43940,7 +43940,7 @@
         <v>46244</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44013,7 +44013,7 @@
         <v>46266</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44086,7 +44086,7 @@
         <v>46245</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44159,7 +44159,7 @@
         <v>46287</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>46245</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44305,7 +44305,7 @@
         <v>46245</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44378,7 +44378,7 @@
         <v>46244</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44451,7 +44451,7 @@
         <v>46244</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44524,7 +44524,7 @@
         <v>46244</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44597,7 +44597,7 @@
         <v>46244</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44670,7 +44670,7 @@
         <v>46244</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44743,7 +44743,7 @@
         <v>46245</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44816,7 +44816,7 @@
         <v>46287</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44889,7 +44889,7 @@
         <v>46006</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44962,7 +44962,7 @@
         <v>46244</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45035,7 +45035,7 @@
         <v>46244</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45108,7 +45108,7 @@
         <v>46287</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45181,7 +45181,7 @@
         <v>46246</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45254,7 +45254,7 @@
         <v>46289</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45327,7 +45327,7 @@
         <v>46293</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45400,7 +45400,7 @@
         <v>46293</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45473,7 +45473,7 @@
         <v>46293</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45546,7 +45546,7 @@
         <v>46253</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45619,7 +45619,7 @@
         <v>46253</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45692,7 +45692,7 @@
         <v>46295</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45770,7 +45770,7 @@
         <v>46295</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45848,7 +45848,7 @@
         <v>46295</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45926,7 +45926,7 @@
         <v>46254</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45999,7 +45999,7 @@
         <v>46245</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46072,7 +46072,7 @@
         <v>46274</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46145,7 +46145,7 @@
         <v>46254</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46218,7 +46218,7 @@
         <v>46258</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46291,7 +46291,7 @@
         <v>46258</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46369,7 +46369,7 @@
         <v>46258</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46442,7 +46442,7 @@
         <v>46258</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46515,7 +46515,7 @@
         <v>46302</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46588,7 +46588,7 @@
         <v>46258</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46661,7 +46661,7 @@
         <v>46258</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46734,7 +46734,7 @@
         <v>46262</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46812,7 +46812,7 @@
         <v>46304</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46885,7 +46885,7 @@
         <v>46262</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46963,7 +46963,7 @@
         <v>44603</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47041,7 +47041,7 @@
         <v>44559</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47119,7 +47119,7 @@
         <v>45567</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47197,7 +47197,7 @@
         <v>44489</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>45667</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47348,7 +47348,7 @@
         <v>44517</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47421,7 +47421,7 @@
         <v>45250</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47499,7 +47499,7 @@
         <v>45638</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47572,7 +47572,7 @@
         <v>45762</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47645,7 +47645,7 @@
         <v>45762</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47718,7 +47718,7 @@
         <v>46070</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47796,7 +47796,7 @@
         <v>46071</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47869,7 +47869,7 @@
         <v>46071</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47942,7 +47942,7 @@
         <v>46071</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48015,7 +48015,7 @@
         <v>46135</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48088,7 +48088,7 @@
         <v>46148</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>

--- a/Översikt NORDMALING.xlsx
+++ b/Översikt NORDMALING.xlsx
@@ -601,7 +601,7 @@
         <v>46205</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45168</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45183</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>45265</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>46139</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>45158</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>45154</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>46044</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>45920</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>45273</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>45219</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>45567</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>44694</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>44859</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>44806</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>44728</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>45239</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>45873</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>45574</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>45575</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>44721</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>45077</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>44820</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>44904</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>46042</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>46043</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>44964</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>46295</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>45400</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>45238</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>45265</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         <v>45713</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>46032</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>45283</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>45283</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>46294</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>44648</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>44802</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>44495</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>44495</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
         <v>44859</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>44859</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         <v>45651</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>45275</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>44788</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>45693</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>45343</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>44547</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         <v>44908</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>45145</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>45570</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         <v>45166</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         <v>45824</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>45158</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>45999</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>45999</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>46129</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>46002</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>45618</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>46072</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>46181</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>46205</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>44519</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         <v>46183</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
         <v>44858</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>44487</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>44510</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>44818</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>44859</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         <v>44851</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>44651</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         <v>44867</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>44867</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>44866</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>44859</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>44744</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>44859</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
         <v>44859</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>44833</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         <v>44565</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>44651</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         <v>44487</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>44620</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>44832</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>44859</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         <v>44657</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>44687</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>44759</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>44854</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
         <v>44830</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         <v>44868</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>44859</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9781,7 +9781,7 @@
         <v>44861</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         <v>45378</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9932,7 +9932,7 @@
         <v>44621</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>45102</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>44655</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>45021</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>45096</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>44812</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>45126</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>45145</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>45092</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>45096</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>45419</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>45343</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>45757</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
         <v>44888</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         <v>44886</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>44812</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11115,7 +11115,7 @@
         <v>44972</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
         <v>45608</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
         <v>45378</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
         <v>45419</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>44763</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>45096</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>44859</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
         <v>45772</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>45517</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
         <v>45105</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>45491</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
         <v>45231</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>44480</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>44893</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>45435</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12245,7 +12245,7 @@
         <v>45407</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         <v>45754</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         <v>45216</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         <v>44949</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12542,7 +12542,7 @@
         <v>45245</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>45245</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>45188</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
         <v>45139</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
         <v>44909</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12922,7 +12922,7 @@
         <v>45187</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12995,7 +12995,7 @@
         <v>45187</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13068,7 +13068,7 @@
         <v>45265</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
         <v>45562</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13219,7 +13219,7 @@
         <v>44896</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>44788</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>45607</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>45622</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>45883</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>45489</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13667,7 +13667,7 @@
         <v>44968</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13740,7 +13740,7 @@
         <v>45078</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13813,7 +13813,7 @@
         <v>45443</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>45883</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>45525</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14032,7 +14032,7 @@
         <v>45453</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>45569</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14183,7 +14183,7 @@
         <v>45575</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         <v>44964</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>45344</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14402,7 +14402,7 @@
         <v>45665</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>45021</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>45887</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>45888</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>45676</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>45764</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14840,7 +14840,7 @@
         <v>44515</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14913,7 +14913,7 @@
         <v>45713</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>44921</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15059,7 +15059,7 @@
         <v>45264</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>45894</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>45796</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15283,7 +15283,7 @@
         <v>45891</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         <v>45896</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>45898</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>45241</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         <v>45901</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15653,7 +15653,7 @@
         <v>45568</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
         <v>45568</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15799,7 +15799,7 @@
         <v>44922</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15872,7 +15872,7 @@
         <v>45900</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>45482</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
         <v>44977</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>45835</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>45900</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16237,7 +16237,7 @@
         <v>45470</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16310,7 +16310,7 @@
         <v>45447</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16388,7 +16388,7 @@
         <v>44531</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16461,7 +16461,7 @@
         <v>45141</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>45903</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>45664</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16685,7 +16685,7 @@
         <v>45327</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>45429</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16831,7 +16831,7 @@
         <v>44540</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         <v>45764</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>45457</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>45204</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17123,7 +17123,7 @@
         <v>45638</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>45538</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>45590</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>45180</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>45911</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17498,7 +17498,7 @@
         <v>45589</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17571,7 +17571,7 @@
         <v>45126</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>45030</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>45673</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>45783</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17868,7 +17868,7 @@
         <v>45022</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17946,7 +17946,7 @@
         <v>45593</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>44981</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>45783</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
         <v>45615</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>45141</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18311,7 +18311,7 @@
         <v>45491</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>45587</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>45917</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18530,7 +18530,7 @@
         <v>45917</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18603,7 +18603,7 @@
         <v>45158</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18676,7 +18676,7 @@
         <v>45678</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18749,7 +18749,7 @@
         <v>45917</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18822,7 +18822,7 @@
         <v>45343</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18900,7 +18900,7 @@
         <v>45349</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18973,7 +18973,7 @@
         <v>45917</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19046,7 +19046,7 @@
         <v>45261</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>44991</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>45603</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19270,7 +19270,7 @@
         <v>44993</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>45524</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19416,7 +19416,7 @@
         <v>45790</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19489,7 +19489,7 @@
         <v>45790</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19562,7 +19562,7 @@
         <v>45036</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19635,7 +19635,7 @@
         <v>45789</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19708,7 +19708,7 @@
         <v>45923</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19781,7 +19781,7 @@
         <v>45923</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19854,7 +19854,7 @@
         <v>45790</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19927,7 +19927,7 @@
         <v>45574</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20000,7 +20000,7 @@
         <v>45790</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>45330</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>45525</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>44609</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>44908</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20375,7 +20375,7 @@
         <v>45926</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20448,7 +20448,7 @@
         <v>45182</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20521,7 +20521,7 @@
         <v>45929</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20594,7 +20594,7 @@
         <v>45929</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20667,7 +20667,7 @@
         <v>45232</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20740,7 +20740,7 @@
         <v>45929</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20813,7 +20813,7 @@
         <v>45187</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>45462</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>45462</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>45638</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>45796</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
         <v>45586</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21251,7 +21251,7 @@
         <v>45712</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>45699</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>45932</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>45936</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>44905</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21631,7 +21631,7 @@
         <v>45420</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21709,7 +21709,7 @@
         <v>45799</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>45344</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21855,7 +21855,7 @@
         <v>45062</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>44977</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22006,7 +22006,7 @@
         <v>45141</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>45938</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22152,7 +22152,7 @@
         <v>44753</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22230,7 +22230,7 @@
         <v>45049</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22308,7 +22308,7 @@
         <v>45569</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22381,7 +22381,7 @@
         <v>44722</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
         <v>45238</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22532,7 +22532,7 @@
         <v>45938</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22605,7 +22605,7 @@
         <v>44854</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22678,7 +22678,7 @@
         <v>44859</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22756,7 +22756,7 @@
         <v>45688</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22829,7 +22829,7 @@
         <v>45607</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
         <v>45940</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22975,7 +22975,7 @@
         <v>45940</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23048,7 +23048,7 @@
         <v>45607</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23121,7 +23121,7 @@
         <v>45944</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23194,7 +23194,7 @@
         <v>44547</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23267,7 +23267,7 @@
         <v>45638</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23340,7 +23340,7 @@
         <v>45946</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>44789</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23486,7 +23486,7 @@
         <v>45204</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23559,7 +23559,7 @@
         <v>45946</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23632,7 +23632,7 @@
         <v>45140</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23710,7 +23710,7 @@
         <v>45950</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23783,7 +23783,7 @@
         <v>45139</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23861,7 +23861,7 @@
         <v>45950</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>45775</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>45775</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24080,7 +24080,7 @@
         <v>44812</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24153,7 +24153,7 @@
         <v>45825</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>45825</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>45825</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24372,7 +24372,7 @@
         <v>45951</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24445,7 +24445,7 @@
         <v>45825</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24518,7 +24518,7 @@
         <v>45825</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>45951</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24664,7 +24664,7 @@
         <v>45034</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24737,7 +24737,7 @@
         <v>45237</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>45525</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         <v>45953</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
         <v>45960</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25029,7 +25029,7 @@
         <v>45959</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25102,7 +25102,7 @@
         <v>45960</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25175,7 +25175,7 @@
         <v>45962</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25253,7 +25253,7 @@
         <v>45964</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25326,7 +25326,7 @@
         <v>45075</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25399,7 +25399,7 @@
         <v>44977</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25477,7 +25477,7 @@
         <v>45167</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25555,7 +25555,7 @@
         <v>44687</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25628,7 +25628,7 @@
         <v>45838</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25701,7 +25701,7 @@
         <v>45835</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25774,7 +25774,7 @@
         <v>45665</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25847,7 +25847,7 @@
         <v>45964</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25920,7 +25920,7 @@
         <v>45239</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25993,7 +25993,7 @@
         <v>45961</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26066,7 +26066,7 @@
         <v>45158</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26139,7 +26139,7 @@
         <v>45965</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26212,7 +26212,7 @@
         <v>45966</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26285,7 +26285,7 @@
         <v>45965</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26358,7 +26358,7 @@
         <v>45770</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26431,7 +26431,7 @@
         <v>45119</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26504,7 +26504,7 @@
         <v>45469</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26577,7 +26577,7 @@
         <v>45965</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26650,7 +26650,7 @@
         <v>45841</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26723,7 +26723,7 @@
         <v>45842</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26801,7 +26801,7 @@
         <v>45846</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26874,7 +26874,7 @@
         <v>45972</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26947,7 +26947,7 @@
         <v>45187</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27020,7 +27020,7 @@
         <v>44756</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>45974</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27171,7 +27171,7 @@
         <v>45265</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27249,7 +27249,7 @@
         <v>45147</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27322,7 +27322,7 @@
         <v>45147</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27395,7 +27395,7 @@
         <v>45849</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>45852</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27541,7 +27541,7 @@
         <v>44742</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27614,7 +27614,7 @@
         <v>45470</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27687,7 +27687,7 @@
         <v>45866</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27760,7 +27760,7 @@
         <v>45867</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27833,7 +27833,7 @@
         <v>45187</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         <v>45979</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27979,7 +27979,7 @@
         <v>45021</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28052,7 +28052,7 @@
         <v>45979</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28125,7 +28125,7 @@
         <v>45763</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28203,7 +28203,7 @@
         <v>45979</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28276,7 +28276,7 @@
         <v>44816</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>45980</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28427,7 +28427,7 @@
         <v>44902</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28500,7 +28500,7 @@
         <v>45051</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28573,7 +28573,7 @@
         <v>45982</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28651,7 +28651,7 @@
         <v>45775</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28724,7 +28724,7 @@
         <v>45981</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28797,7 +28797,7 @@
         <v>44938</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28870,7 +28870,7 @@
         <v>45736</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28943,7 +28943,7 @@
         <v>45566</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29016,7 +29016,7 @@
         <v>45028</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29089,7 +29089,7 @@
         <v>44907</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29162,7 +29162,7 @@
         <v>45586</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44533</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29308,7 +29308,7 @@
         <v>45173</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29381,7 +29381,7 @@
         <v>45616</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>45986</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29527,7 +29527,7 @@
         <v>45167</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29600,7 +29600,7 @@
         <v>45707</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29673,7 +29673,7 @@
         <v>45503</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29746,7 +29746,7 @@
         <v>45986</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29819,7 +29819,7 @@
         <v>45986</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29897,7 +29897,7 @@
         <v>45986</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29970,7 +29970,7 @@
         <v>45524</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>45505</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30121,7 +30121,7 @@
         <v>46108</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30199,7 +30199,7 @@
         <v>45736</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>46111</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>46108</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30418,7 +30418,7 @@
         <v>45988</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30491,7 +30491,7 @@
         <v>45280</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30569,7 +30569,7 @@
         <v>45536</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30642,7 +30642,7 @@
         <v>44922</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30715,7 +30715,7 @@
         <v>44943</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30788,7 +30788,7 @@
         <v>46113</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30861,7 +30861,7 @@
         <v>46113</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30934,7 +30934,7 @@
         <v>44531</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         <v>44834</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31085,7 +31085,7 @@
         <v>45993</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31158,7 +31158,7 @@
         <v>45433</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31231,7 +31231,7 @@
         <v>45988</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31304,7 +31304,7 @@
         <v>45994</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31377,7 +31377,7 @@
         <v>45993</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31455,7 +31455,7 @@
         <v>45994</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31528,7 +31528,7 @@
         <v>45988</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31601,7 +31601,7 @@
         <v>46125</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31674,7 +31674,7 @@
         <v>46125</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31747,7 +31747,7 @@
         <v>45775</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31820,7 +31820,7 @@
         <v>46127</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31893,7 +31893,7 @@
         <v>46000</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31966,7 +31966,7 @@
         <v>46129</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32039,7 +32039,7 @@
         <v>46000</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32117,7 +32117,7 @@
         <v>46132</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32190,7 +32190,7 @@
         <v>44916</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32268,7 +32268,7 @@
         <v>46000</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>46132</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32419,7 +32419,7 @@
         <v>46003</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32497,7 +32497,7 @@
         <v>46003</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32575,7 +32575,7 @@
         <v>46006</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>46006</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32726,7 +32726,7 @@
         <v>46006</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32799,7 +32799,7 @@
         <v>46006</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32872,7 +32872,7 @@
         <v>46006</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32945,7 +32945,7 @@
         <v>46006</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>46006</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>44949</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33164,7 +33164,7 @@
         <v>44816</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33237,7 +33237,7 @@
         <v>46135</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33310,7 +33310,7 @@
         <v>45800</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33383,7 +33383,7 @@
         <v>44706</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33456,7 +33456,7 @@
         <v>46135</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33534,7 +33534,7 @@
         <v>45247</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33607,7 +33607,7 @@
         <v>45147</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33680,7 +33680,7 @@
         <v>45251</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33753,7 +33753,7 @@
         <v>45348</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>46009</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         <v>46010</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33972,7 +33972,7 @@
         <v>45343</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34050,7 +34050,7 @@
         <v>46010</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34123,7 +34123,7 @@
         <v>45147</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34196,7 +34196,7 @@
         <v>45866</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34269,7 +34269,7 @@
         <v>46010</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34342,7 +34342,7 @@
         <v>45147</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34415,7 +34415,7 @@
         <v>45147</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>45147</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34561,7 +34561,7 @@
         <v>46009</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>46009</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34707,7 +34707,7 @@
         <v>46050</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34780,7 +34780,7 @@
         <v>45877</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34853,7 +34853,7 @@
         <v>46018</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34926,7 +34926,7 @@
         <v>46018</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34999,7 +34999,7 @@
         <v>46018</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35072,7 +35072,7 @@
         <v>46020</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35145,7 +35145,7 @@
         <v>44620</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35218,7 +35218,7 @@
         <v>46020</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35291,7 +35291,7 @@
         <v>46022</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35364,7 +35364,7 @@
         <v>45799</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35437,7 +35437,7 @@
         <v>45926</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35510,7 +35510,7 @@
         <v>46028</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35583,7 +35583,7 @@
         <v>45034</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35656,7 +35656,7 @@
         <v>46139</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>45439</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35802,7 +35802,7 @@
         <v>45929</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>44881</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35948,7 +35948,7 @@
         <v>46029</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36021,7 +36021,7 @@
         <v>46029</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36094,7 +36094,7 @@
         <v>46032</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36172,7 +36172,7 @@
         <v>45618</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36245,7 +36245,7 @@
         <v>46037</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36318,7 +36318,7 @@
         <v>46038</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36391,7 +36391,7 @@
         <v>46042</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36464,7 +36464,7 @@
         <v>46042</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>45552</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>46041</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36683,7 +36683,7 @@
         <v>46029</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36756,7 +36756,7 @@
         <v>45965</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36829,7 +36829,7 @@
         <v>46043</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36902,7 +36902,7 @@
         <v>45673</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36975,7 +36975,7 @@
         <v>44735</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37048,7 +37048,7 @@
         <v>45961</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37121,7 +37121,7 @@
         <v>45890</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>46048</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37267,7 +37267,7 @@
         <v>46045</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37340,7 +37340,7 @@
         <v>45238</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37413,7 +37413,7 @@
         <v>45996</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>44859</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37559,7 +37559,7 @@
         <v>45742</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37632,7 +37632,7 @@
         <v>45981</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37705,7 +37705,7 @@
         <v>46141</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37778,7 +37778,7 @@
         <v>46050</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37851,7 +37851,7 @@
         <v>46050</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37924,7 +37924,7 @@
         <v>46056</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38002,7 +38002,7 @@
         <v>46058</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38075,7 +38075,7 @@
         <v>46058</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38148,7 +38148,7 @@
         <v>46058</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38226,7 +38226,7 @@
         <v>46062</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38299,7 +38299,7 @@
         <v>46065</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38372,7 +38372,7 @@
         <v>46065</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38445,7 +38445,7 @@
         <v>46066</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38518,7 +38518,7 @@
         <v>46151</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38591,7 +38591,7 @@
         <v>46072</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38664,7 +38664,7 @@
         <v>46072</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38737,7 +38737,7 @@
         <v>46076</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38810,7 +38810,7 @@
         <v>46072</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38888,7 +38888,7 @@
         <v>46151</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38961,7 +38961,7 @@
         <v>46155</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39034,7 +39034,7 @@
         <v>46155</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39107,7 +39107,7 @@
         <v>46160</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39180,7 +39180,7 @@
         <v>46161</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39253,7 +39253,7 @@
         <v>46161</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39326,7 +39326,7 @@
         <v>46094</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39399,7 +39399,7 @@
         <v>46094</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39472,7 +39472,7 @@
         <v>46094</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39545,7 +39545,7 @@
         <v>46160</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39618,7 +39618,7 @@
         <v>46161</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39691,7 +39691,7 @@
         <v>46161</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39764,7 +39764,7 @@
         <v>46161</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39837,7 +39837,7 @@
         <v>46162</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39915,7 +39915,7 @@
         <v>45691</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39988,7 +39988,7 @@
         <v>46171</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40061,7 +40061,7 @@
         <v>46174</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40134,7 +40134,7 @@
         <v>46174</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40207,7 +40207,7 @@
         <v>46174</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40280,7 +40280,7 @@
         <v>46176</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40353,7 +40353,7 @@
         <v>46178</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40426,7 +40426,7 @@
         <v>46185</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40499,7 +40499,7 @@
         <v>46188</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40572,7 +40572,7 @@
         <v>45922</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40645,7 +40645,7 @@
         <v>46195</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40718,7 +40718,7 @@
         <v>46197</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40791,7 +40791,7 @@
         <v>46197</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>46196</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40937,7 +40937,7 @@
         <v>46199</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41010,7 +41010,7 @@
         <v>46202</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41083,7 +41083,7 @@
         <v>46205</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41156,7 +41156,7 @@
         <v>46205</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>46205</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41302,7 +41302,7 @@
         <v>46205</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41375,7 +41375,7 @@
         <v>46205</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41448,7 +41448,7 @@
         <v>46205</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41521,7 +41521,7 @@
         <v>46134</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41594,7 +41594,7 @@
         <v>46212</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41667,7 +41667,7 @@
         <v>45988</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41740,7 +41740,7 @@
         <v>46136</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41813,7 +41813,7 @@
         <v>46265</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41886,7 +41886,7 @@
         <v>46265</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41959,7 +41959,7 @@
         <v>46265</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>46263</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42105,7 +42105,7 @@
         <v>46266</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42178,7 +42178,7 @@
         <v>46267</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42251,7 +42251,7 @@
         <v>46267</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42324,7 +42324,7 @@
         <v>46272</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42397,7 +42397,7 @@
         <v>45936</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42470,7 +42470,7 @@
         <v>46274</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42543,7 +42543,7 @@
         <v>46275</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42616,7 +42616,7 @@
         <v>46275</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42689,7 +42689,7 @@
         <v>46237</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42762,7 +42762,7 @@
         <v>46279</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42835,7 +42835,7 @@
         <v>46280</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42908,7 +42908,7 @@
         <v>46239</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42986,7 +42986,7 @@
         <v>46239</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43064,7 +43064,7 @@
         <v>46286</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43137,7 +43137,7 @@
         <v>46245</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43210,7 +43210,7 @@
         <v>46245</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43283,7 +43283,7 @@
         <v>46245</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43356,7 +43356,7 @@
         <v>46245</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43429,7 +43429,7 @@
         <v>46244</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43502,7 +43502,7 @@
         <v>46245</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43575,7 +43575,7 @@
         <v>46245</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43648,7 +43648,7 @@
         <v>46245</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43721,7 +43721,7 @@
         <v>46245</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43794,7 +43794,7 @@
         <v>46245</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43867,7 +43867,7 @@
         <v>46245</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43940,7 +43940,7 @@
         <v>46244</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44013,7 +44013,7 @@
         <v>46266</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44086,7 +44086,7 @@
         <v>46245</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44159,7 +44159,7 @@
         <v>46287</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>46245</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44305,7 +44305,7 @@
         <v>46245</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44378,7 +44378,7 @@
         <v>46244</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44451,7 +44451,7 @@
         <v>46244</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44524,7 +44524,7 @@
         <v>46244</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44597,7 +44597,7 @@
         <v>46244</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44670,7 +44670,7 @@
         <v>46244</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44743,7 +44743,7 @@
         <v>46245</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44816,7 +44816,7 @@
         <v>46287</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44889,7 +44889,7 @@
         <v>46006</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44962,7 +44962,7 @@
         <v>46244</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45035,7 +45035,7 @@
         <v>46244</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45108,7 +45108,7 @@
         <v>46287</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45181,7 +45181,7 @@
         <v>46246</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45254,7 +45254,7 @@
         <v>46289</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45327,7 +45327,7 @@
         <v>46293</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45400,7 +45400,7 @@
         <v>46293</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45473,7 +45473,7 @@
         <v>46293</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45546,7 +45546,7 @@
         <v>46253</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45619,7 +45619,7 @@
         <v>46253</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45692,7 +45692,7 @@
         <v>46295</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45770,7 +45770,7 @@
         <v>46295</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45848,7 +45848,7 @@
         <v>46295</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45926,7 +45926,7 @@
         <v>46254</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45999,7 +45999,7 @@
         <v>46245</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46072,7 +46072,7 @@
         <v>46274</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46145,7 +46145,7 @@
         <v>46254</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46218,7 +46218,7 @@
         <v>46258</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46291,7 +46291,7 @@
         <v>46258</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46369,7 +46369,7 @@
         <v>46258</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46442,7 +46442,7 @@
         <v>46258</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46515,7 +46515,7 @@
         <v>46302</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46588,7 +46588,7 @@
         <v>46258</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46661,7 +46661,7 @@
         <v>46258</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46734,7 +46734,7 @@
         <v>46262</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46812,7 +46812,7 @@
         <v>46304</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46885,7 +46885,7 @@
         <v>46262</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46963,7 +46963,7 @@
         <v>44603</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47041,7 +47041,7 @@
         <v>44559</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47119,7 +47119,7 @@
         <v>45567</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47197,7 +47197,7 @@
         <v>44489</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>45667</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47348,7 +47348,7 @@
         <v>44517</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47421,7 +47421,7 @@
         <v>45250</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47499,7 +47499,7 @@
         <v>45638</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47572,7 +47572,7 @@
         <v>45762</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47645,7 +47645,7 @@
         <v>45762</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47718,7 +47718,7 @@
         <v>46070</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47796,7 +47796,7 @@
         <v>46071</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47869,7 +47869,7 @@
         <v>46071</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47942,7 +47942,7 @@
         <v>46071</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48015,7 +48015,7 @@
         <v>46135</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48088,7 +48088,7 @@
         <v>46148</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>

--- a/Översikt NORDMALING.xlsx
+++ b/Översikt NORDMALING.xlsx
@@ -601,7 +601,7 @@
         <v>45283</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45400</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>46205</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45168</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>45183</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>45283</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>45265</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>46139</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>45158</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>45154</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>46044</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>45920</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>45273</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>45219</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>45567</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>44694</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>44859</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>44806</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>45239</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>44728</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>45873</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>45574</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>44964</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>45575</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>45077</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>46043</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>46042</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>44820</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>44904</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>44721</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>46295</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>45713</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>45265</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>46032</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>45238</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
         <v>46294</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>44648</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         <v>44802</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>44495</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>44495</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>44859</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>44859</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         <v>45275</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>45158</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>45343</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>45570</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>45693</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>45618</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         <v>45999</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         <v>45999</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>46002</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>44788</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>46181</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         <v>45166</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>46072</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>44908</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>46129</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>46205</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>45651</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         <v>45145</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>44547</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
         <v>45824</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>44519</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>46183</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7696,7 +7696,7 @@
         <v>44858</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
         <v>44487</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>44510</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>44818</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>44859</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         <v>44851</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>44651</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>44867</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>44867</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
         <v>44866</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>44859</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8519,7 +8519,7 @@
         <v>44744</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         <v>44859</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         <v>44859</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>44833</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
         <v>44565</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>44651</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>44487</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         <v>44687</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>44657</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>44759</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         <v>44859</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9357,7 +9357,7 @@
         <v>44859</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>44854</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>44832</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>44830</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>44868</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9742,7 +9742,7 @@
         <v>44620</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         <v>44861</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9893,7 +9893,7 @@
         <v>44621</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>44655</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>45736</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>45447</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>44922</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10263,7 +10263,7 @@
         <v>45096</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
         <v>45062</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>45167</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10492,7 +10492,7 @@
         <v>44968</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10565,7 +10565,7 @@
         <v>44756</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         <v>45664</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10721,7 +10721,7 @@
         <v>44964</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10794,7 +10794,7 @@
         <v>45182</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10867,7 +10867,7 @@
         <v>45141</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10940,7 +10940,7 @@
         <v>45204</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>45590</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>45204</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11159,7 +11159,7 @@
         <v>45665</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         <v>44991</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>45158</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>44921</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>45407</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
         <v>44735</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>45757</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         <v>45021</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>45469</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>45622</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         <v>45343</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11972,7 +11972,7 @@
         <v>44763</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>44896</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>44816</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>44981</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         <v>45505</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12352,7 +12352,7 @@
         <v>45232</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
         <v>45264</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12503,7 +12503,7 @@
         <v>45491</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>45343</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12649,7 +12649,7 @@
         <v>45587</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12722,7 +12722,7 @@
         <v>44977</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>45180</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12878,7 +12878,7 @@
         <v>45187</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
         <v>45245</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
         <v>45673</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         <v>44753</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>45419</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13248,7 +13248,7 @@
         <v>45247</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13321,7 +13321,7 @@
         <v>44949</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
         <v>45589</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>44905</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13545,7 +13545,7 @@
         <v>45443</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>44916</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>45678</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13769,7 +13769,7 @@
         <v>45608</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13847,7 +13847,7 @@
         <v>44515</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>44949</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>44922</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14066,7 +14066,7 @@
         <v>45049</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         <v>45096</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>45470</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>45883</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>45887</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>45981</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>45800</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>46139</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>45552</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>45996</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>45173</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>45799</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>45888</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>44687</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>45926</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
         <v>45562</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15244,7 +15244,7 @@
         <v>45891</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>45126</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15395,7 +15395,7 @@
         <v>44547</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15468,7 +15468,7 @@
         <v>44908</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
         <v>45894</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15619,7 +15619,7 @@
         <v>45796</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15692,7 +15692,7 @@
         <v>45770</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>45896</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>45929</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15911,7 +15911,7 @@
         <v>44540</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15984,7 +15984,7 @@
         <v>45901</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16057,7 +16057,7 @@
         <v>45900</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>45141</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>45835</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>45051</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>46050</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16422,7 +16422,7 @@
         <v>45900</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16495,7 +16495,7 @@
         <v>45712</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16568,7 +16568,7 @@
         <v>46141</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         <v>45713</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16714,7 +16714,7 @@
         <v>45898</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16787,7 +16787,7 @@
         <v>45965</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16860,7 +16860,7 @@
         <v>45903</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>45343</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17011,7 +17011,7 @@
         <v>45961</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17084,7 +17084,7 @@
         <v>45911</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
         <v>44886</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>45917</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>45917</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>44834</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17454,7 +17454,7 @@
         <v>45917</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17527,7 +17527,7 @@
         <v>45673</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>45917</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>45923</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17746,7 +17746,7 @@
         <v>45638</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17824,7 +17824,7 @@
         <v>45536</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17897,7 +17897,7 @@
         <v>45923</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17970,7 +17970,7 @@
         <v>45929</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>45929</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18116,7 +18116,7 @@
         <v>45489</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>45926</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18267,7 +18267,7 @@
         <v>45929</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>44531</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>46151</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18486,7 +18486,7 @@
         <v>46151</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>45932</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18637,7 +18637,7 @@
         <v>45936</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45126</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>45265</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
         <v>45938</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>45938</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>45265</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19090,7 +19090,7 @@
         <v>45940</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19163,7 +19163,7 @@
         <v>45102</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>44943</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19309,7 +19309,7 @@
         <v>45940</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>45944</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>46155</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19528,7 +19528,7 @@
         <v>45946</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19601,7 +19601,7 @@
         <v>45946</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>44938</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>45239</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19820,7 +19820,7 @@
         <v>45951</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>45950</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>45950</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20039,7 +20039,7 @@
         <v>46155</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>45951</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20185,7 +20185,7 @@
         <v>45953</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20258,7 +20258,7 @@
         <v>45959</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20331,7 +20331,7 @@
         <v>45961</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>46161</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20477,7 +20477,7 @@
         <v>44972</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20550,7 +20550,7 @@
         <v>45960</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20623,7 +20623,7 @@
         <v>45960</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>46160</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20769,7 +20769,7 @@
         <v>46160</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20842,7 +20842,7 @@
         <v>45964</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20915,7 +20915,7 @@
         <v>45962</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20993,7 +20993,7 @@
         <v>44893</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>45965</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>45964</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21217,7 +21217,7 @@
         <v>45965</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>45078</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21363,7 +21363,7 @@
         <v>46161</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21436,7 +21436,7 @@
         <v>45965</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>46161</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21582,7 +21582,7 @@
         <v>46161</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         <v>45966</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21728,7 +21728,7 @@
         <v>46161</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21801,7 +21801,7 @@
         <v>45525</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>45021</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21947,7 +21947,7 @@
         <v>45092</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22020,7 +22020,7 @@
         <v>46162</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22098,7 +22098,7 @@
         <v>45972</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22171,7 +22171,7 @@
         <v>45974</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         <v>45979</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>45979</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22390,7 +22390,7 @@
         <v>45979</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22463,7 +22463,7 @@
         <v>45981</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22536,7 +22536,7 @@
         <v>45980</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22614,7 +22614,7 @@
         <v>45607</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22687,7 +22687,7 @@
         <v>45607</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22760,7 +22760,7 @@
         <v>45982</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22838,7 +22838,7 @@
         <v>45691</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22911,7 +22911,7 @@
         <v>45158</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22984,7 +22984,7 @@
         <v>45986</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23062,7 +23062,7 @@
         <v>45986</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23135,7 +23135,7 @@
         <v>45986</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23208,7 +23208,7 @@
         <v>45433</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23281,7 +23281,7 @@
         <v>45986</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23354,7 +23354,7 @@
         <v>45988</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>45167</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23500,7 +23500,7 @@
         <v>45378</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23573,7 +23573,7 @@
         <v>44859</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23651,7 +23651,7 @@
         <v>45993</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23729,7 +23729,7 @@
         <v>45988</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23802,7 +23802,7 @@
         <v>45993</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>45988</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23948,7 +23948,7 @@
         <v>45994</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24021,7 +24021,7 @@
         <v>45994</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24094,7 +24094,7 @@
         <v>45435</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24167,7 +24167,7 @@
         <v>46000</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24245,7 +24245,7 @@
         <v>46000</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
         <v>45707</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24391,7 +24391,7 @@
         <v>46000</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>44977</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>45638</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
         <v>46171</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>46003</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24766,7 +24766,7 @@
         <v>46003</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24844,7 +24844,7 @@
         <v>45538</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24917,7 +24917,7 @@
         <v>44993</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24990,7 +24990,7 @@
         <v>46006</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25063,7 +25063,7 @@
         <v>46006</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25136,7 +25136,7 @@
         <v>46006</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>46006</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>45344</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25355,7 +25355,7 @@
         <v>46006</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>46006</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25506,7 +25506,7 @@
         <v>46006</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25579,7 +25579,7 @@
         <v>46009</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25652,7 +25652,7 @@
         <v>46009</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>46174</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25798,7 +25798,7 @@
         <v>46174</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25871,7 +25871,7 @@
         <v>46009</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>44881</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>45147</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>45147</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26163,7 +26163,7 @@
         <v>45147</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>45147</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>46010</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>46010</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26455,7 +26455,7 @@
         <v>46010</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26528,7 +26528,7 @@
         <v>45419</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26601,7 +26601,7 @@
         <v>45754</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26674,7 +26674,7 @@
         <v>45503</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26747,7 +26747,7 @@
         <v>46174</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26820,7 +26820,7 @@
         <v>45147</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>46020</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26966,7 +26966,7 @@
         <v>46018</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>45586</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27112,7 +27112,7 @@
         <v>46020</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27185,7 +27185,7 @@
         <v>46018</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27258,7 +27258,7 @@
         <v>46018</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>46022</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27404,7 +27404,7 @@
         <v>46029</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27477,7 +27477,7 @@
         <v>45021</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27550,7 +27550,7 @@
         <v>45034</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27623,7 +27623,7 @@
         <v>46028</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>46029</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27769,7 +27769,7 @@
         <v>45280</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>46176</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27920,7 +27920,7 @@
         <v>45457</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27993,7 +27993,7 @@
         <v>46032</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28071,7 +28071,7 @@
         <v>46041</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28144,7 +28144,7 @@
         <v>46037</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28217,7 +28217,7 @@
         <v>46038</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28290,7 +28290,7 @@
         <v>45327</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28363,7 +28363,7 @@
         <v>46042</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28436,7 +28436,7 @@
         <v>46042</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28509,7 +28509,7 @@
         <v>46043</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28582,7 +28582,7 @@
         <v>46178</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28655,7 +28655,7 @@
         <v>46045</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28728,7 +28728,7 @@
         <v>45615</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28801,7 +28801,7 @@
         <v>45022</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28879,7 +28879,7 @@
         <v>46048</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28952,7 +28952,7 @@
         <v>46050</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29025,7 +29025,7 @@
         <v>46050</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29098,7 +29098,7 @@
         <v>46056</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29176,7 +29176,7 @@
         <v>45330</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29254,7 +29254,7 @@
         <v>44859</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29332,7 +29332,7 @@
         <v>46058</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29410,7 +29410,7 @@
         <v>46058</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29483,7 +29483,7 @@
         <v>46185</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29556,7 +29556,7 @@
         <v>46058</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29629,7 +29629,7 @@
         <v>46062</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29702,7 +29702,7 @@
         <v>44609</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29775,7 +29775,7 @@
         <v>46065</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29848,7 +29848,7 @@
         <v>46065</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29921,7 +29921,7 @@
         <v>46066</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29994,7 +29994,7 @@
         <v>46188</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30067,7 +30067,7 @@
         <v>46072</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30140,7 +30140,7 @@
         <v>46072</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30213,7 +30213,7 @@
         <v>46072</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30291,7 +30291,7 @@
         <v>46076</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>45775</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>45775</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>45349</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30583,7 +30583,7 @@
         <v>44812</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         <v>45453</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30734,7 +30734,7 @@
         <v>45922</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30807,7 +30807,7 @@
         <v>45568</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30880,7 +30880,7 @@
         <v>45568</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30953,7 +30953,7 @@
         <v>46094</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31026,7 +31026,7 @@
         <v>46094</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31099,7 +31099,7 @@
         <v>46094</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31172,7 +31172,7 @@
         <v>44789</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31245,7 +31245,7 @@
         <v>45139</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31323,7 +31323,7 @@
         <v>45188</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31401,7 +31401,7 @@
         <v>46195</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>45344</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31547,7 +31547,7 @@
         <v>46196</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31620,7 +31620,7 @@
         <v>45593</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31693,7 +31693,7 @@
         <v>44533</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31766,7 +31766,7 @@
         <v>44812</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31839,7 +31839,7 @@
         <v>46108</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31917,7 +31917,7 @@
         <v>46108</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>46197</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32063,7 +32063,7 @@
         <v>46111</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>46113</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32209,7 +32209,7 @@
         <v>46113</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32282,7 +32282,7 @@
         <v>45525</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>45075</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32428,7 +32428,7 @@
         <v>46197</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32501,7 +32501,7 @@
         <v>45524</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32574,7 +32574,7 @@
         <v>44977</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32652,7 +32652,7 @@
         <v>45482</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32725,7 +32725,7 @@
         <v>46199</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32798,7 +32798,7 @@
         <v>46125</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32871,7 +32871,7 @@
         <v>46125</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32944,7 +32944,7 @@
         <v>46202</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>45586</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33090,7 +33090,7 @@
         <v>46127</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33163,7 +33163,7 @@
         <v>44907</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>46129</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33309,7 +33309,7 @@
         <v>46132</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33382,7 +33382,7 @@
         <v>46132</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33455,7 +33455,7 @@
         <v>46135</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>46205</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33606,7 +33606,7 @@
         <v>46205</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33679,7 +33679,7 @@
         <v>46205</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33752,7 +33752,7 @@
         <v>46205</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33825,7 +33825,7 @@
         <v>46135</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33898,7 +33898,7 @@
         <v>46029</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33971,7 +33971,7 @@
         <v>46205</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34044,7 +34044,7 @@
         <v>46205</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34117,7 +34117,7 @@
         <v>45618</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34190,7 +34190,7 @@
         <v>44902</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34263,7 +34263,7 @@
         <v>45877</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34336,7 +34336,7 @@
         <v>45890</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34409,7 +34409,7 @@
         <v>45231</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34482,7 +34482,7 @@
         <v>44909</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34560,7 +34560,7 @@
         <v>45105</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34638,7 +34638,7 @@
         <v>45866</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34711,7 +34711,7 @@
         <v>44742</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34784,7 +34784,7 @@
         <v>45517</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
         <v>45569</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34935,7 +34935,7 @@
         <v>46212</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35008,7 +35008,7 @@
         <v>46134</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35081,7 +35081,7 @@
         <v>45574</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35154,7 +35154,7 @@
         <v>44888</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35227,7 +35227,7 @@
         <v>45988</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35300,7 +35300,7 @@
         <v>46136</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35373,7 +35373,7 @@
         <v>45378</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35446,7 +35446,7 @@
         <v>44706</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>45028</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35592,7 +35592,7 @@
         <v>44788</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35665,7 +35665,7 @@
         <v>46272</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35738,7 +35738,7 @@
         <v>45936</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35811,7 +35811,7 @@
         <v>46275</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35884,7 +35884,7 @@
         <v>46275</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35957,7 +35957,7 @@
         <v>46274</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36030,7 +36030,7 @@
         <v>45525</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36103,7 +36103,7 @@
         <v>46279</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36176,7 +36176,7 @@
         <v>45524</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36249,7 +36249,7 @@
         <v>45736</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36322,7 +36322,7 @@
         <v>46237</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36395,7 +36395,7 @@
         <v>46280</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36468,7 +36468,7 @@
         <v>45462</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36541,7 +36541,7 @@
         <v>45462</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36614,7 +36614,7 @@
         <v>45245</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36687,7 +36687,7 @@
         <v>46239</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36765,7 +36765,7 @@
         <v>44722</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36843,7 +36843,7 @@
         <v>46239</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36921,7 +36921,7 @@
         <v>45348</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36994,7 +36994,7 @@
         <v>45096</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37072,7 +37072,7 @@
         <v>44854</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37145,7 +37145,7 @@
         <v>45139</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>45569</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37296,7 +37296,7 @@
         <v>44859</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37369,7 +37369,7 @@
         <v>46286</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37442,7 +37442,7 @@
         <v>45241</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37515,7 +37515,7 @@
         <v>46287</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37588,7 +37588,7 @@
         <v>46244</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37661,7 +37661,7 @@
         <v>45147</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37734,7 +37734,7 @@
         <v>45742</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37807,7 +37807,7 @@
         <v>46287</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37880,7 +37880,7 @@
         <v>45575</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37953,7 +37953,7 @@
         <v>46244</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38026,7 +38026,7 @@
         <v>46244</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38099,7 +38099,7 @@
         <v>46244</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38172,7 +38172,7 @@
         <v>46244</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38245,7 +38245,7 @@
         <v>46006</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38318,7 +38318,7 @@
         <v>46244</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38391,7 +38391,7 @@
         <v>46287</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38464,7 +38464,7 @@
         <v>45119</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38537,7 +38537,7 @@
         <v>46244</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38610,7 +38610,7 @@
         <v>46244</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38683,7 +38683,7 @@
         <v>45034</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38756,7 +38756,7 @@
         <v>46244</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>45566</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38902,7 +38902,7 @@
         <v>46245</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38975,7 +38975,7 @@
         <v>46245</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39048,7 +39048,7 @@
         <v>46245</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39121,7 +39121,7 @@
         <v>46245</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39194,7 +39194,7 @@
         <v>44812</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39267,7 +39267,7 @@
         <v>45251</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39340,7 +39340,7 @@
         <v>45141</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39413,7 +39413,7 @@
         <v>45775</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>46289</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39559,7 +39559,7 @@
         <v>46245</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39632,7 +39632,7 @@
         <v>46245</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39705,7 +39705,7 @@
         <v>46245</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39778,7 +39778,7 @@
         <v>46245</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39851,7 +39851,7 @@
         <v>46245</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39924,7 +39924,7 @@
         <v>46245</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39997,7 +39997,7 @@
         <v>46245</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40070,7 +40070,7 @@
         <v>45439</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40143,7 +40143,7 @@
         <v>46266</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40216,7 +40216,7 @@
         <v>46245</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40289,7 +40289,7 @@
         <v>45429</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40362,7 +40362,7 @@
         <v>46245</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40435,7 +40435,7 @@
         <v>46246</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40508,7 +40508,7 @@
         <v>46245</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>44816</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40654,7 +40654,7 @@
         <v>45238</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40727,7 +40727,7 @@
         <v>46293</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40800,7 +40800,7 @@
         <v>44620</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40873,7 +40873,7 @@
         <v>45764</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40946,7 +40946,7 @@
         <v>45764</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41019,7 +41019,7 @@
         <v>45420</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41097,7 +41097,7 @@
         <v>45187</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41170,7 +41170,7 @@
         <v>45763</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41248,7 +41248,7 @@
         <v>46293</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41321,7 +41321,7 @@
         <v>45491</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41394,7 +41394,7 @@
         <v>45140</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>45216</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41550,7 +41550,7 @@
         <v>46295</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41628,7 +41628,7 @@
         <v>45237</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41701,7 +41701,7 @@
         <v>45145</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41779,7 +41779,7 @@
         <v>44531</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41852,7 +41852,7 @@
         <v>45147</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41925,7 +41925,7 @@
         <v>46295</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42003,7 +42003,7 @@
         <v>45676</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42076,7 +42076,7 @@
         <v>46253</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42149,7 +42149,7 @@
         <v>45187</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42222,7 +42222,7 @@
         <v>45187</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42295,7 +42295,7 @@
         <v>46293</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42368,7 +42368,7 @@
         <v>46295</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42446,7 +42446,7 @@
         <v>46254</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42519,7 +42519,7 @@
         <v>46245</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42592,7 +42592,7 @@
         <v>46253</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42665,7 +42665,7 @@
         <v>45772</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42738,7 +42738,7 @@
         <v>45187</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42811,7 +42811,7 @@
         <v>45616</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42884,7 +42884,7 @@
         <v>45665</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42957,7 +42957,7 @@
         <v>46258</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43030,7 +43030,7 @@
         <v>45638</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43103,7 +43103,7 @@
         <v>46258</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43176,7 +43176,7 @@
         <v>45030</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43254,7 +43254,7 @@
         <v>45783</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43327,7 +43327,7 @@
         <v>45783</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43400,7 +43400,7 @@
         <v>46258</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43473,7 +43473,7 @@
         <v>46258</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43546,7 +43546,7 @@
         <v>46258</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43619,7 +43619,7 @@
         <v>46258</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43697,7 +43697,7 @@
         <v>46254</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43770,7 +43770,7 @@
         <v>45603</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
         <v>45261</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
         <v>45789</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43989,7 +43989,7 @@
         <v>45790</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44062,7 +44062,7 @@
         <v>46302</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44135,7 +44135,7 @@
         <v>45790</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44208,7 +44208,7 @@
         <v>45790</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44281,7 +44281,7 @@
         <v>45790</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44354,7 +44354,7 @@
         <v>45036</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44427,7 +44427,7 @@
         <v>46307</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44500,7 +44500,7 @@
         <v>46262</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44578,7 +44578,7 @@
         <v>45796</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44651,7 +44651,7 @@
         <v>45699</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44724,7 +44724,7 @@
         <v>46304</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44797,7 +44797,7 @@
         <v>46262</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44875,7 +44875,7 @@
         <v>46309</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44948,7 +44948,7 @@
         <v>46265</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45021,7 +45021,7 @@
         <v>46308</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45099,7 +45099,7 @@
         <v>46308</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45172,7 +45172,7 @@
         <v>46266</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45245,7 +45245,7 @@
         <v>46309</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45318,7 +45318,7 @@
         <v>45799</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45391,7 +45391,7 @@
         <v>46263</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45464,7 +45464,7 @@
         <v>45238</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45537,7 +45537,7 @@
         <v>46265</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45610,7 +45610,7 @@
         <v>45607</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45683,7 +45683,7 @@
         <v>46265</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45756,7 +45756,7 @@
         <v>45688</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45829,7 +45829,7 @@
         <v>46267</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45902,7 +45902,7 @@
         <v>46267</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45975,7 +45975,7 @@
         <v>45825</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46048,7 +46048,7 @@
         <v>45825</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46121,7 +46121,7 @@
         <v>45825</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46194,7 +46194,7 @@
         <v>45825</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46267,7 +46267,7 @@
         <v>46274</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46340,7 +46340,7 @@
         <v>45825</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46413,7 +46413,7 @@
         <v>46310</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46486,7 +46486,7 @@
         <v>45835</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46559,7 +46559,7 @@
         <v>45838</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46632,7 +46632,7 @@
         <v>45841</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46705,7 +46705,7 @@
         <v>45842</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46783,7 +46783,7 @@
         <v>45846</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46856,7 +46856,7 @@
         <v>45849</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46929,7 +46929,7 @@
         <v>45852</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47002,7 +47002,7 @@
         <v>45470</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47075,7 +47075,7 @@
         <v>45867</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47148,7 +47148,7 @@
         <v>45866</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47221,7 +47221,7 @@
         <v>45775</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47294,7 +47294,7 @@
         <v>45883</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47367,7 +47367,7 @@
         <v>44603</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47445,7 +47445,7 @@
         <v>45567</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47523,7 +47523,7 @@
         <v>44489</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47596,7 +47596,7 @@
         <v>44559</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47674,7 +47674,7 @@
         <v>45667</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47752,7 +47752,7 @@
         <v>44517</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47825,7 +47825,7 @@
         <v>45250</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47903,7 +47903,7 @@
         <v>45638</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47976,7 +47976,7 @@
         <v>45762</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48049,7 +48049,7 @@
         <v>45762</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48122,7 +48122,7 @@
         <v>46071</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48195,7 +48195,7 @@
         <v>46070</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48273,7 +48273,7 @@
         <v>46071</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48346,7 +48346,7 @@
         <v>46071</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48419,7 +48419,7 @@
         <v>46135</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48492,7 +48492,7 @@
         <v>46148</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>

--- a/Översikt NORDMALING.xlsx
+++ b/Översikt NORDMALING.xlsx
@@ -601,7 +601,7 @@
         <v>45283</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45400</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>46205</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45168</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>45183</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>45283</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>45265</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>46139</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>45158</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>45154</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>46044</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>45920</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>45273</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>45219</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>45567</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>44694</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>44859</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>44806</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>44728</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>45873</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>45239</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>44964</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>45574</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>46042</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>46043</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>46295</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>45575</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>44721</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>45077</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>44820</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>44904</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>46032</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>46294</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>45238</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
         <v>46318</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>45265</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>45713</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>44648</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>44802</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>44495</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>44495</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>44859</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         <v>44859</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>44788</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>45618</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>46181</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>45693</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>46205</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>45343</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>45999</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>45999</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>46002</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>46072</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>45824</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>46129</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>44547</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         <v>44908</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>45570</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>45651</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7158,7 +7158,7 @@
         <v>45275</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>45145</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7377,7 +7377,7 @@
         <v>45166</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>45158</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>44519</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7696,7 +7696,7 @@
         <v>46183</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>44858</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>44510</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>44818</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         <v>44859</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>44851</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>44651</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
         <v>44867</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>44867</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>44866</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>44859</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         <v>44744</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>44859</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>44859</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         <v>44833</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>44565</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
         <v>44651</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9019,7 +9019,7 @@
         <v>44657</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         <v>44687</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>44759</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>44859</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>44859</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>44854</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         <v>44832</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>44830</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>44868</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         <v>44620</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         <v>44861</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>44655</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>44621</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>45883</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>45887</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10149,7 +10149,7 @@
         <v>45888</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         <v>44949</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>44816</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         <v>44763</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10446,7 +10446,7 @@
         <v>45772</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10519,7 +10519,7 @@
         <v>45894</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
         <v>45796</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>45891</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10743,7 +10743,7 @@
         <v>44706</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10816,7 +10816,7 @@
         <v>45896</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10889,7 +10889,7 @@
         <v>45247</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>45251</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>45348</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11108,7 +11108,7 @@
         <v>45898</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11181,7 +11181,7 @@
         <v>45343</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>45901</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>45900</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         <v>45378</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>45835</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>45900</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11624,7 +11624,7 @@
         <v>44620</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>45903</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         <v>44812</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>46161</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         <v>46161</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>45034</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>45439</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>45911</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         <v>46160</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>46161</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>46161</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>44881</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>46161</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>45917</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12646,7 +12646,7 @@
         <v>45917</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         <v>46162</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>45917</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12870,7 +12870,7 @@
         <v>45917</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>45691</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>45923</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13089,7 +13089,7 @@
         <v>45923</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13162,7 +13162,7 @@
         <v>45926</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>45126</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13308,7 +13308,7 @@
         <v>45673</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13381,7 +13381,7 @@
         <v>44735</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>45929</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>45929</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>45929</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13673,7 +13673,7 @@
         <v>46171</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>45092</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>45096</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13897,7 +13897,7 @@
         <v>45932</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>45238</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>45936</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         <v>46174</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>44859</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>45742</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>45419</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>45938</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>44886</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>45938</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         <v>45940</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>45940</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14783,7 +14783,7 @@
         <v>45021</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14856,7 +14856,7 @@
         <v>45096</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>46174</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15007,7 +15007,7 @@
         <v>46174</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>45944</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>46176</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>45946</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>45216</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15377,7 +15377,7 @@
         <v>45946</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>44888</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15523,7 +15523,7 @@
         <v>45245</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>45950</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>44972</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15742,7 +15742,7 @@
         <v>45608</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>45950</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>46178</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>45951</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>45951</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16112,7 +16112,7 @@
         <v>45517</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         <v>45953</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16263,7 +16263,7 @@
         <v>45435</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16336,7 +16336,7 @@
         <v>45407</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16409,7 +16409,7 @@
         <v>46185</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>45754</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16555,7 +16555,7 @@
         <v>45960</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16628,7 +16628,7 @@
         <v>45959</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>44909</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>45960</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16852,7 +16852,7 @@
         <v>45962</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>45964</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17003,7 +17003,7 @@
         <v>45964</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17076,7 +17076,7 @@
         <v>45265</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>45961</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17227,7 +17227,7 @@
         <v>45965</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17300,7 +17300,7 @@
         <v>45966</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17373,7 +17373,7 @@
         <v>45965</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17446,7 +17446,7 @@
         <v>46188</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17519,7 +17519,7 @@
         <v>45922</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17592,7 +17592,7 @@
         <v>45188</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>45965</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17743,7 +17743,7 @@
         <v>44788</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17816,7 +17816,7 @@
         <v>45607</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         <v>46195</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17962,7 +17962,7 @@
         <v>45972</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18035,7 +18035,7 @@
         <v>46197</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18108,7 +18108,7 @@
         <v>46197</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18181,7 +18181,7 @@
         <v>45974</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18254,7 +18254,7 @@
         <v>44968</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18327,7 +18327,7 @@
         <v>45078</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>46196</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18473,7 +18473,7 @@
         <v>46199</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18546,7 +18546,7 @@
         <v>45979</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18619,7 +18619,7 @@
         <v>45979</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>45979</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
         <v>45980</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>45665</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>46202</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>45982</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>45981</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>45676</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
         <v>46205</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>46205</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>46205</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>46205</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19505,7 +19505,7 @@
         <v>46205</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>46205</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>45986</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>45713</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19797,7 +19797,7 @@
         <v>45986</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19870,7 +19870,7 @@
         <v>45986</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>45986</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20021,7 +20021,7 @@
         <v>45489</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         <v>45264</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>45241</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20250,7 +20250,7 @@
         <v>45568</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>45568</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>45988</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20469,7 +20469,7 @@
         <v>45993</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>45988</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20615,7 +20615,7 @@
         <v>45994</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20688,7 +20688,7 @@
         <v>45993</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20766,7 +20766,7 @@
         <v>45994</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20839,7 +20839,7 @@
         <v>45988</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20912,7 +20912,7 @@
         <v>46134</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20985,7 +20985,7 @@
         <v>46212</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21058,7 +21058,7 @@
         <v>45664</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>45429</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21209,7 +21209,7 @@
         <v>45764</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21282,7 +21282,7 @@
         <v>45204</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21355,7 +21355,7 @@
         <v>45988</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21428,7 +21428,7 @@
         <v>46136</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21501,7 +21501,7 @@
         <v>46000</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
         <v>46000</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21652,7 +21652,7 @@
         <v>46000</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21730,7 +21730,7 @@
         <v>46003</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>46003</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>46006</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>46006</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22037,7 +22037,7 @@
         <v>45030</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22115,7 +22115,7 @@
         <v>46006</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22188,7 +22188,7 @@
         <v>46006</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22261,7 +22261,7 @@
         <v>46006</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22334,7 +22334,7 @@
         <v>46006</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22407,7 +22407,7 @@
         <v>45936</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>46006</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22553,7 +22553,7 @@
         <v>45783</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22626,7 +22626,7 @@
         <v>45783</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22699,7 +22699,7 @@
         <v>45147</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22772,7 +22772,7 @@
         <v>46009</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         <v>46010</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22918,7 +22918,7 @@
         <v>46010</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22991,7 +22991,7 @@
         <v>45147</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>46010</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23137,7 +23137,7 @@
         <v>45147</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23210,7 +23210,7 @@
         <v>45147</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23283,7 +23283,7 @@
         <v>45147</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>46009</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23429,7 +23429,7 @@
         <v>46009</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23502,7 +23502,7 @@
         <v>45261</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23575,7 +23575,7 @@
         <v>46237</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23648,7 +23648,7 @@
         <v>46279</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23721,7 +23721,7 @@
         <v>46280</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23794,7 +23794,7 @@
         <v>45603</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23867,7 +23867,7 @@
         <v>46239</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23945,7 +23945,7 @@
         <v>45443</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24018,7 +24018,7 @@
         <v>46018</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24091,7 +24091,7 @@
         <v>46018</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24164,7 +24164,7 @@
         <v>46018</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24237,7 +24237,7 @@
         <v>46020</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24310,7 +24310,7 @@
         <v>45790</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24383,7 +24383,7 @@
         <v>45790</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24456,7 +24456,7 @@
         <v>46020</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24529,7 +24529,7 @@
         <v>46022</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24602,7 +24602,7 @@
         <v>45036</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24675,7 +24675,7 @@
         <v>45789</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
         <v>45525</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24821,7 +24821,7 @@
         <v>46028</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24894,7 +24894,7 @@
         <v>45790</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24967,7 +24967,7 @@
         <v>45790</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
         <v>46239</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25118,7 +25118,7 @@
         <v>46029</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25191,7 +25191,7 @@
         <v>46029</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25264,7 +25264,7 @@
         <v>45453</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25342,7 +25342,7 @@
         <v>46032</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         <v>44964</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25493,7 +25493,7 @@
         <v>46037</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25566,7 +25566,7 @@
         <v>46038</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25639,7 +25639,7 @@
         <v>46286</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25712,7 +25712,7 @@
         <v>46042</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25785,7 +25785,7 @@
         <v>46042</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25858,7 +25858,7 @@
         <v>46041</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25931,7 +25931,7 @@
         <v>46245</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>46245</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26077,7 +26077,7 @@
         <v>46245</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26150,7 +26150,7 @@
         <v>45796</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26223,7 +26223,7 @@
         <v>46245</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26296,7 +26296,7 @@
         <v>46244</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26369,7 +26369,7 @@
         <v>46245</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26442,7 +26442,7 @@
         <v>46245</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>45699</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26588,7 +26588,7 @@
         <v>46245</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26661,7 +26661,7 @@
         <v>46245</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26734,7 +26734,7 @@
         <v>46245</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>46245</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>46244</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>46043</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27026,7 +27026,7 @@
         <v>46266</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>46245</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27172,7 +27172,7 @@
         <v>46287</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>46245</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27318,7 +27318,7 @@
         <v>46245</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27391,7 +27391,7 @@
         <v>46244</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27464,7 +27464,7 @@
         <v>46048</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27537,7 +27537,7 @@
         <v>46045</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>46244</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>46244</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27756,7 +27756,7 @@
         <v>46244</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27829,7 +27829,7 @@
         <v>46244</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27902,7 +27902,7 @@
         <v>46245</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>46287</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28048,7 +28048,7 @@
         <v>46006</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28121,7 +28121,7 @@
         <v>46244</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28194,7 +28194,7 @@
         <v>46244</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28267,7 +28267,7 @@
         <v>46287</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28340,7 +28340,7 @@
         <v>46050</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28413,7 +28413,7 @@
         <v>46050</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28486,7 +28486,7 @@
         <v>45799</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28559,7 +28559,7 @@
         <v>45021</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28632,7 +28632,7 @@
         <v>46056</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28710,7 +28710,7 @@
         <v>46246</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28783,7 +28783,7 @@
         <v>46289</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>45238</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>46058</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29002,7 +29002,7 @@
         <v>46058</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29075,7 +29075,7 @@
         <v>46058</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29153,7 +29153,7 @@
         <v>45688</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29226,7 +29226,7 @@
         <v>46293</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29299,7 +29299,7 @@
         <v>45607</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29372,7 +29372,7 @@
         <v>46062</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29445,7 +29445,7 @@
         <v>46293</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29518,7 +29518,7 @@
         <v>46065</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29591,7 +29591,7 @@
         <v>46065</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29664,7 +29664,7 @@
         <v>46066</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>46293</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29810,7 +29810,7 @@
         <v>46072</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29883,7 +29883,7 @@
         <v>46072</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29956,7 +29956,7 @@
         <v>46253</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30029,7 +30029,7 @@
         <v>46076</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30102,7 +30102,7 @@
         <v>46253</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>46295</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30253,7 +30253,7 @@
         <v>46072</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30331,7 +30331,7 @@
         <v>45825</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30404,7 +30404,7 @@
         <v>46295</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30482,7 +30482,7 @@
         <v>45825</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30555,7 +30555,7 @@
         <v>45825</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30628,7 +30628,7 @@
         <v>45825</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30701,7 +30701,7 @@
         <v>45825</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30774,7 +30774,7 @@
         <v>46295</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30852,7 +30852,7 @@
         <v>46254</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30925,7 +30925,7 @@
         <v>46245</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>45838</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31071,7 +31071,7 @@
         <v>45835</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>46094</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31217,7 +31217,7 @@
         <v>46094</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
         <v>46094</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31363,7 +31363,7 @@
         <v>44515</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>45841</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31509,7 +31509,7 @@
         <v>44921</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31582,7 +31582,7 @@
         <v>45842</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31660,7 +31660,7 @@
         <v>45846</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31733,7 +31733,7 @@
         <v>46254</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31806,7 +31806,7 @@
         <v>46258</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31879,7 +31879,7 @@
         <v>46258</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31957,7 +31957,7 @@
         <v>46258</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32030,7 +32030,7 @@
         <v>44922</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32103,7 +32103,7 @@
         <v>46258</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32176,7 +32176,7 @@
         <v>45849</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>45852</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32322,7 +32322,7 @@
         <v>46108</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32400,7 +32400,7 @@
         <v>45482</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32473,7 +32473,7 @@
         <v>46111</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32546,7 +32546,7 @@
         <v>46108</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32619,7 +32619,7 @@
         <v>46302</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32692,7 +32692,7 @@
         <v>44977</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32765,7 +32765,7 @@
         <v>45470</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32838,7 +32838,7 @@
         <v>46258</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32911,7 +32911,7 @@
         <v>46258</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32984,7 +32984,7 @@
         <v>46113</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33057,7 +33057,7 @@
         <v>46113</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33130,7 +33130,7 @@
         <v>45470</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33203,7 +33203,7 @@
         <v>45866</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33276,7 +33276,7 @@
         <v>45867</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33349,7 +33349,7 @@
         <v>46125</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33422,7 +33422,7 @@
         <v>46125</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33495,7 +33495,7 @@
         <v>46127</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33568,7 +33568,7 @@
         <v>46304</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33641,7 +33641,7 @@
         <v>46129</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33714,7 +33714,7 @@
         <v>45327</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33787,7 +33787,7 @@
         <v>46307</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33860,7 +33860,7 @@
         <v>46132</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33933,7 +33933,7 @@
         <v>45775</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34006,7 +34006,7 @@
         <v>46265</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34079,7 +34079,7 @@
         <v>46132</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34152,7 +34152,7 @@
         <v>46262</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34230,7 +34230,7 @@
         <v>46262</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>46308</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34386,7 +34386,7 @@
         <v>46265</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34459,7 +34459,7 @@
         <v>45638</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34537,7 +34537,7 @@
         <v>46265</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34610,7 +34610,7 @@
         <v>45538</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34683,7 +34683,7 @@
         <v>45590</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34756,7 +34756,7 @@
         <v>45589</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34829,7 +34829,7 @@
         <v>45126</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34902,7 +34902,7 @@
         <v>46135</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34975,7 +34975,7 @@
         <v>45800</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35048,7 +35048,7 @@
         <v>45491</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35121,7 +35121,7 @@
         <v>46135</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35199,7 +35199,7 @@
         <v>46309</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35272,7 +35272,7 @@
         <v>46263</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35345,7 +35345,7 @@
         <v>46309</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35418,7 +35418,7 @@
         <v>46310</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35491,7 +35491,7 @@
         <v>45866</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35564,7 +35564,7 @@
         <v>46308</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35637,7 +35637,7 @@
         <v>46266</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35710,7 +35710,7 @@
         <v>45343</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35788,7 +35788,7 @@
         <v>45349</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35861,7 +35861,7 @@
         <v>46050</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35934,7 +35934,7 @@
         <v>45877</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36007,7 +36007,7 @@
         <v>46267</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36080,7 +36080,7 @@
         <v>46267</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36153,7 +36153,7 @@
         <v>45799</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36226,7 +36226,7 @@
         <v>44991</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36304,7 +36304,7 @@
         <v>45926</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36377,7 +36377,7 @@
         <v>46139</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36450,7 +36450,7 @@
         <v>45929</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36523,7 +36523,7 @@
         <v>44609</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36596,7 +36596,7 @@
         <v>45618</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36669,7 +36669,7 @@
         <v>44908</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36747,7 +36747,7 @@
         <v>45552</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36820,7 +36820,7 @@
         <v>46029</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36893,7 +36893,7 @@
         <v>46316</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36971,7 +36971,7 @@
         <v>45965</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37044,7 +37044,7 @@
         <v>45232</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37117,7 +37117,7 @@
         <v>45961</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37190,7 +37190,7 @@
         <v>45890</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37263,7 +37263,7 @@
         <v>46272</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37336,7 +37336,7 @@
         <v>45883</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37409,7 +37409,7 @@
         <v>45996</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37482,7 +37482,7 @@
         <v>45981</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37555,7 +37555,7 @@
         <v>45586</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37628,7 +37628,7 @@
         <v>46275</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37701,7 +37701,7 @@
         <v>46141</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37774,7 +37774,7 @@
         <v>46318</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37852,7 +37852,7 @@
         <v>46318</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37930,7 +37930,7 @@
         <v>46274</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38003,7 +38003,7 @@
         <v>46275</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38076,7 +38076,7 @@
         <v>44905</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38154,7 +38154,7 @@
         <v>46274</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38227,7 +38227,7 @@
         <v>45344</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38300,7 +38300,7 @@
         <v>44977</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38378,7 +38378,7 @@
         <v>45141</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38451,7 +38451,7 @@
         <v>44753</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38529,7 +38529,7 @@
         <v>46151</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38602,7 +38602,7 @@
         <v>45049</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38680,7 +38680,7 @@
         <v>45569</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38753,7 +38753,7 @@
         <v>44722</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38831,7 +38831,7 @@
         <v>46151</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38904,7 +38904,7 @@
         <v>46155</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38977,7 +38977,7 @@
         <v>46155</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39050,7 +39050,7 @@
         <v>46160</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39123,7 +39123,7 @@
         <v>44812</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39196,7 +39196,7 @@
         <v>45034</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39269,7 +39269,7 @@
         <v>45525</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39342,7 +39342,7 @@
         <v>45075</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39415,7 +39415,7 @@
         <v>44977</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39493,7 +39493,7 @@
         <v>45119</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39566,7 +39566,7 @@
         <v>45469</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39639,7 +39639,7 @@
         <v>45187</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39712,7 +39712,7 @@
         <v>45147</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39785,7 +39785,7 @@
         <v>45147</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39858,7 +39858,7 @@
         <v>44742</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39931,7 +39931,7 @@
         <v>45187</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40004,7 +40004,7 @@
         <v>45021</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40077,7 +40077,7 @@
         <v>45763</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40155,7 +40155,7 @@
         <v>45051</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40228,7 +40228,7 @@
         <v>45028</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40301,7 +40301,7 @@
         <v>44907</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40374,7 +40374,7 @@
         <v>45586</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40447,7 +40447,7 @@
         <v>44533</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40520,7 +40520,7 @@
         <v>45173</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40593,7 +40593,7 @@
         <v>45503</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>45524</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40739,7 +40739,7 @@
         <v>45736</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40812,7 +40812,7 @@
         <v>45280</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40890,7 +40890,7 @@
         <v>44943</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40963,7 +40963,7 @@
         <v>44531</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41036,7 +41036,7 @@
         <v>44834</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41114,7 +41114,7 @@
         <v>45102</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41187,7 +41187,7 @@
         <v>45145</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>45343</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41338,7 +41338,7 @@
         <v>45757</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         <v>44812</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41484,7 +41484,7 @@
         <v>45378</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41557,7 +41557,7 @@
         <v>45419</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41630,7 +41630,7 @@
         <v>45096</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41708,7 +41708,7 @@
         <v>44859</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41786,7 +41786,7 @@
         <v>45105</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41864,7 +41864,7 @@
         <v>45491</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41937,7 +41937,7 @@
         <v>45231</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42010,7 +42010,7 @@
         <v>44893</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42088,7 +42088,7 @@
         <v>44949</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42161,7 +42161,7 @@
         <v>45245</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42234,7 +42234,7 @@
         <v>45139</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42312,7 +42312,7 @@
         <v>45187</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42385,7 +42385,7 @@
         <v>45187</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42458,7 +42458,7 @@
         <v>45562</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42531,7 +42531,7 @@
         <v>44896</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42609,7 +42609,7 @@
         <v>45622</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42682,7 +42682,7 @@
         <v>45569</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42755,7 +42755,7 @@
         <v>45575</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42828,7 +42828,7 @@
         <v>45344</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42901,7 +42901,7 @@
         <v>45764</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42974,7 +42974,7 @@
         <v>45447</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43052,7 +43052,7 @@
         <v>44531</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43125,7 +43125,7 @@
         <v>45141</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43198,7 +43198,7 @@
         <v>44540</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43271,7 +43271,7 @@
         <v>45457</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43344,7 +43344,7 @@
         <v>45180</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43422,7 +43422,7 @@
         <v>45673</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43495,7 +43495,7 @@
         <v>45022</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43573,7 +43573,7 @@
         <v>45593</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43646,7 +43646,7 @@
         <v>44981</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43719,7 +43719,7 @@
         <v>45615</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43792,7 +43792,7 @@
         <v>45141</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43865,7 +43865,7 @@
         <v>45587</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43938,7 +43938,7 @@
         <v>45158</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44011,7 +44011,7 @@
         <v>45678</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44084,7 +44084,7 @@
         <v>44993</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44157,7 +44157,7 @@
         <v>45524</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44230,7 +44230,7 @@
         <v>45574</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44303,7 +44303,7 @@
         <v>45330</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44381,7 +44381,7 @@
         <v>45525</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44454,7 +44454,7 @@
         <v>45182</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>45187</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44600,7 +44600,7 @@
         <v>45462</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44673,7 +44673,7 @@
         <v>45462</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44746,7 +44746,7 @@
         <v>45638</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44819,7 +44819,7 @@
         <v>45712</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44892,7 +44892,7 @@
         <v>45420</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44970,7 +44970,7 @@
         <v>45062</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45043,7 +45043,7 @@
         <v>44854</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45116,7 +45116,7 @@
         <v>44859</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45194,7 +45194,7 @@
         <v>45607</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45267,7 +45267,7 @@
         <v>44547</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45340,7 +45340,7 @@
         <v>45638</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45413,7 +45413,7 @@
         <v>44789</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45486,7 +45486,7 @@
         <v>45204</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45559,7 +45559,7 @@
         <v>45140</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45637,7 +45637,7 @@
         <v>45139</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45715,7 +45715,7 @@
         <v>45775</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45788,7 +45788,7 @@
         <v>45775</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45861,7 +45861,7 @@
         <v>45237</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45934,7 +45934,7 @@
         <v>45167</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46012,7 +46012,7 @@
         <v>44687</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>45665</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46158,7 +46158,7 @@
         <v>45239</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46231,7 +46231,7 @@
         <v>45158</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46304,7 +46304,7 @@
         <v>45770</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46377,7 +46377,7 @@
         <v>44756</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46455,7 +46455,7 @@
         <v>45265</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46533,7 +46533,7 @@
         <v>44816</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46606,7 +46606,7 @@
         <v>44902</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46679,7 +46679,7 @@
         <v>44938</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46752,7 +46752,7 @@
         <v>45736</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46825,7 +46825,7 @@
         <v>45566</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46898,7 +46898,7 @@
         <v>45616</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46971,7 +46971,7 @@
         <v>45167</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47044,7 +47044,7 @@
         <v>45707</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47117,7 +47117,7 @@
         <v>45505</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47195,7 +47195,7 @@
         <v>45536</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47268,7 +47268,7 @@
         <v>44922</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47341,7 +47341,7 @@
         <v>45433</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47414,7 +47414,7 @@
         <v>45775</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47487,7 +47487,7 @@
         <v>44916</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47565,7 +47565,7 @@
         <v>44603</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47643,7 +47643,7 @@
         <v>44559</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47721,7 +47721,7 @@
         <v>45567</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47799,7 +47799,7 @@
         <v>45667</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47877,7 +47877,7 @@
         <v>44517</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47950,7 +47950,7 @@
         <v>45250</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48028,7 +48028,7 @@
         <v>45638</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48101,7 +48101,7 @@
         <v>45762</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48174,7 +48174,7 @@
         <v>45762</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48247,7 +48247,7 @@
         <v>46070</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48325,7 +48325,7 @@
         <v>46071</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48398,7 +48398,7 @@
         <v>46071</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48471,7 +48471,7 @@
         <v>46071</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48544,7 +48544,7 @@
         <v>46135</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48617,7 +48617,7 @@
         <v>46148</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>

--- a/Översikt NORDMALING.xlsx
+++ b/Översikt NORDMALING.xlsx
@@ -601,7 +601,7 @@
         <v>45283</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45400</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>46205</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45168</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>45183</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>45283</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>45265</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>46139</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>45158</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>45154</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>46044</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>45920</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>45273</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>45219</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>45567</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>44694</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>44859</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>44806</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>44728</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>45873</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>45239</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>44964</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>45574</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>46042</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>46043</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>46295</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>45575</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>44721</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>45077</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>44820</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>44904</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>46032</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>46294</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>45238</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
         <v>46318</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>45265</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>45713</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>44648</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>44802</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>44495</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>44495</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>44859</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         <v>44859</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>44788</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>45618</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>46181</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>45693</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>46205</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>45343</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>45999</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>45999</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>46002</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>46072</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>45824</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>46129</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>44547</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         <v>44908</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>45570</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>45651</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7158,7 +7158,7 @@
         <v>45275</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>45145</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7377,7 +7377,7 @@
         <v>45166</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>45158</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>44519</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7696,7 +7696,7 @@
         <v>46183</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>44858</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>44510</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>44818</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         <v>44859</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>44851</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>44651</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
         <v>44867</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>44867</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>44866</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>44859</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         <v>44744</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>44859</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>44859</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         <v>44833</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>44565</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
         <v>44651</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9019,7 +9019,7 @@
         <v>44657</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         <v>44687</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>44759</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>44859</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>44859</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>44854</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         <v>44832</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>44830</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>44868</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         <v>44620</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         <v>44861</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>44655</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>44621</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>45883</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>45887</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10149,7 +10149,7 @@
         <v>45888</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         <v>44949</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>44816</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         <v>44763</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10446,7 +10446,7 @@
         <v>45772</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10519,7 +10519,7 @@
         <v>45894</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
         <v>45796</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>45891</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10743,7 +10743,7 @@
         <v>44706</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10816,7 +10816,7 @@
         <v>45896</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10889,7 +10889,7 @@
         <v>45247</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>45251</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>45348</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11108,7 +11108,7 @@
         <v>45898</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11181,7 +11181,7 @@
         <v>45343</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>45901</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>45900</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         <v>45378</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>45835</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>45900</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11624,7 +11624,7 @@
         <v>44620</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>45903</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         <v>44812</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>46161</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         <v>46161</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>45034</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>45439</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>45911</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         <v>46160</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>46161</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>46161</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>44881</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>46161</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>45917</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12646,7 +12646,7 @@
         <v>45917</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         <v>46162</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>45917</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12870,7 +12870,7 @@
         <v>45917</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>45691</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>45923</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13089,7 +13089,7 @@
         <v>45923</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13162,7 +13162,7 @@
         <v>45926</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>45126</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13308,7 +13308,7 @@
         <v>45673</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13381,7 +13381,7 @@
         <v>44735</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>45929</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>45929</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>45929</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13673,7 +13673,7 @@
         <v>46171</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>45092</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>45096</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13897,7 +13897,7 @@
         <v>45932</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>45238</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>45936</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         <v>46174</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>44859</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>45742</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>45419</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>45938</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>44886</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>45938</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         <v>45940</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>45940</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14783,7 +14783,7 @@
         <v>45021</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14856,7 +14856,7 @@
         <v>45096</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>46174</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15007,7 +15007,7 @@
         <v>46174</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>45944</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>46176</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>45946</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>45216</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15377,7 +15377,7 @@
         <v>45946</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>44888</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15523,7 +15523,7 @@
         <v>45245</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>45950</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>44972</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15742,7 +15742,7 @@
         <v>45608</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>45950</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>46178</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>45951</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>45951</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16112,7 +16112,7 @@
         <v>45517</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         <v>45953</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16263,7 +16263,7 @@
         <v>45435</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16336,7 +16336,7 @@
         <v>45407</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16409,7 +16409,7 @@
         <v>46185</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>45754</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16555,7 +16555,7 @@
         <v>45960</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16628,7 +16628,7 @@
         <v>45959</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>44909</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>45960</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16852,7 +16852,7 @@
         <v>45962</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>45964</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17003,7 +17003,7 @@
         <v>45964</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17076,7 +17076,7 @@
         <v>45265</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>45961</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17227,7 +17227,7 @@
         <v>45965</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17300,7 +17300,7 @@
         <v>45966</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17373,7 +17373,7 @@
         <v>45965</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17446,7 +17446,7 @@
         <v>46188</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17519,7 +17519,7 @@
         <v>45922</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17592,7 +17592,7 @@
         <v>45188</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>45965</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17743,7 +17743,7 @@
         <v>44788</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17816,7 +17816,7 @@
         <v>45607</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         <v>46195</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17962,7 +17962,7 @@
         <v>45972</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18035,7 +18035,7 @@
         <v>46197</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18108,7 +18108,7 @@
         <v>46197</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18181,7 +18181,7 @@
         <v>45974</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18254,7 +18254,7 @@
         <v>44968</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18327,7 +18327,7 @@
         <v>45078</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>46196</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18473,7 +18473,7 @@
         <v>46199</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18546,7 +18546,7 @@
         <v>45979</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18619,7 +18619,7 @@
         <v>45979</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>45979</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
         <v>45980</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>45665</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>46202</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>45982</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>45981</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>45676</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
         <v>46205</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>46205</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>46205</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>46205</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19505,7 +19505,7 @@
         <v>46205</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>46205</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>45986</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>45713</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19797,7 +19797,7 @@
         <v>45986</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19870,7 +19870,7 @@
         <v>45986</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>45986</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20021,7 +20021,7 @@
         <v>45489</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         <v>45264</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>45241</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20250,7 +20250,7 @@
         <v>45568</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>45568</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>45988</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20469,7 +20469,7 @@
         <v>45993</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>45988</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20615,7 +20615,7 @@
         <v>45994</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20688,7 +20688,7 @@
         <v>45993</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20766,7 +20766,7 @@
         <v>45994</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20839,7 +20839,7 @@
         <v>45988</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20912,7 +20912,7 @@
         <v>46134</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20985,7 +20985,7 @@
         <v>46212</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21058,7 +21058,7 @@
         <v>45664</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>45429</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21209,7 +21209,7 @@
         <v>45764</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21282,7 +21282,7 @@
         <v>45204</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21355,7 +21355,7 @@
         <v>45988</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21428,7 +21428,7 @@
         <v>46136</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21501,7 +21501,7 @@
         <v>46000</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
         <v>46000</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21652,7 +21652,7 @@
         <v>46000</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21730,7 +21730,7 @@
         <v>46003</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>46003</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>46006</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>46006</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22037,7 +22037,7 @@
         <v>45030</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22115,7 +22115,7 @@
         <v>46006</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22188,7 +22188,7 @@
         <v>46006</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22261,7 +22261,7 @@
         <v>46006</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22334,7 +22334,7 @@
         <v>46006</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22407,7 +22407,7 @@
         <v>45936</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>46006</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22553,7 +22553,7 @@
         <v>45783</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22626,7 +22626,7 @@
         <v>45783</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22699,7 +22699,7 @@
         <v>45147</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22772,7 +22772,7 @@
         <v>46009</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         <v>46010</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22918,7 +22918,7 @@
         <v>46010</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22991,7 +22991,7 @@
         <v>45147</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>46010</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23137,7 +23137,7 @@
         <v>45147</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23210,7 +23210,7 @@
         <v>45147</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23283,7 +23283,7 @@
         <v>45147</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>46009</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23429,7 +23429,7 @@
         <v>46009</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23502,7 +23502,7 @@
         <v>45261</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23575,7 +23575,7 @@
         <v>46237</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23648,7 +23648,7 @@
         <v>46279</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23721,7 +23721,7 @@
         <v>46280</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23794,7 +23794,7 @@
         <v>45603</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23867,7 +23867,7 @@
         <v>46239</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23945,7 +23945,7 @@
         <v>45443</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24018,7 +24018,7 @@
         <v>46018</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24091,7 +24091,7 @@
         <v>46018</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24164,7 +24164,7 @@
         <v>46018</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24237,7 +24237,7 @@
         <v>46020</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24310,7 +24310,7 @@
         <v>45790</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24383,7 +24383,7 @@
         <v>45790</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24456,7 +24456,7 @@
         <v>46020</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24529,7 +24529,7 @@
         <v>46022</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24602,7 +24602,7 @@
         <v>45036</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24675,7 +24675,7 @@
         <v>45789</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
         <v>45525</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24821,7 +24821,7 @@
         <v>46028</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24894,7 +24894,7 @@
         <v>45790</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24967,7 +24967,7 @@
         <v>45790</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
         <v>46239</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25118,7 +25118,7 @@
         <v>46029</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25191,7 +25191,7 @@
         <v>46029</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25264,7 +25264,7 @@
         <v>45453</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25342,7 +25342,7 @@
         <v>46032</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         <v>44964</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25493,7 +25493,7 @@
         <v>46037</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25566,7 +25566,7 @@
         <v>46038</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25639,7 +25639,7 @@
         <v>46286</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25712,7 +25712,7 @@
         <v>46042</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25785,7 +25785,7 @@
         <v>46042</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25858,7 +25858,7 @@
         <v>46041</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25931,7 +25931,7 @@
         <v>46245</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>46245</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26077,7 +26077,7 @@
         <v>46245</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26150,7 +26150,7 @@
         <v>45796</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26223,7 +26223,7 @@
         <v>46245</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26296,7 +26296,7 @@
         <v>46244</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26369,7 +26369,7 @@
         <v>46245</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26442,7 +26442,7 @@
         <v>46245</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>45699</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26588,7 +26588,7 @@
         <v>46245</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26661,7 +26661,7 @@
         <v>46245</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26734,7 +26734,7 @@
         <v>46245</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>46245</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>46244</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>46043</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27026,7 +27026,7 @@
         <v>46266</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>46245</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27172,7 +27172,7 @@
         <v>46287</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>46245</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27318,7 +27318,7 @@
         <v>46245</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27391,7 +27391,7 @@
         <v>46244</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27464,7 +27464,7 @@
         <v>46048</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27537,7 +27537,7 @@
         <v>46045</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>46244</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>46244</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27756,7 +27756,7 @@
         <v>46244</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27829,7 +27829,7 @@
         <v>46244</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27902,7 +27902,7 @@
         <v>46245</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>46287</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28048,7 +28048,7 @@
         <v>46006</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28121,7 +28121,7 @@
         <v>46244</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28194,7 +28194,7 @@
         <v>46244</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28267,7 +28267,7 @@
         <v>46287</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28340,7 +28340,7 @@
         <v>46050</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28413,7 +28413,7 @@
         <v>46050</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28486,7 +28486,7 @@
         <v>45799</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28559,7 +28559,7 @@
         <v>45021</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28632,7 +28632,7 @@
         <v>46056</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28710,7 +28710,7 @@
         <v>46246</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28783,7 +28783,7 @@
         <v>46289</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>45238</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>46058</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29002,7 +29002,7 @@
         <v>46058</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29075,7 +29075,7 @@
         <v>46058</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29153,7 +29153,7 @@
         <v>45688</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29226,7 +29226,7 @@
         <v>46293</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29299,7 +29299,7 @@
         <v>45607</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29372,7 +29372,7 @@
         <v>46062</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29445,7 +29445,7 @@
         <v>46293</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29518,7 +29518,7 @@
         <v>46065</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29591,7 +29591,7 @@
         <v>46065</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29664,7 +29664,7 @@
         <v>46066</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>46293</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29810,7 +29810,7 @@
         <v>46072</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29883,7 +29883,7 @@
         <v>46072</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29956,7 +29956,7 @@
         <v>46253</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30029,7 +30029,7 @@
         <v>46076</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30102,7 +30102,7 @@
         <v>46253</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>46295</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30253,7 +30253,7 @@
         <v>46072</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30331,7 +30331,7 @@
         <v>45825</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30404,7 +30404,7 @@
         <v>46295</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30482,7 +30482,7 @@
         <v>45825</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30555,7 +30555,7 @@
         <v>45825</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30628,7 +30628,7 @@
         <v>45825</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30701,7 +30701,7 @@
         <v>45825</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30774,7 +30774,7 @@
         <v>46295</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30852,7 +30852,7 @@
         <v>46254</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30925,7 +30925,7 @@
         <v>46245</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>45838</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31071,7 +31071,7 @@
         <v>45835</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>46094</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31217,7 +31217,7 @@
         <v>46094</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
         <v>46094</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31363,7 +31363,7 @@
         <v>44515</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>45841</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31509,7 +31509,7 @@
         <v>44921</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31582,7 +31582,7 @@
         <v>45842</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31660,7 +31660,7 @@
         <v>45846</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31733,7 +31733,7 @@
         <v>46254</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31806,7 +31806,7 @@
         <v>46258</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31879,7 +31879,7 @@
         <v>46258</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31957,7 +31957,7 @@
         <v>46258</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32030,7 +32030,7 @@
         <v>44922</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32103,7 +32103,7 @@
         <v>46258</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32176,7 +32176,7 @@
         <v>45849</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>45852</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32322,7 +32322,7 @@
         <v>46108</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32400,7 +32400,7 @@
         <v>45482</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32473,7 +32473,7 @@
         <v>46111</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32546,7 +32546,7 @@
         <v>46108</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32619,7 +32619,7 @@
         <v>46302</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32692,7 +32692,7 @@
         <v>44977</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32765,7 +32765,7 @@
         <v>45470</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32838,7 +32838,7 @@
         <v>46258</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32911,7 +32911,7 @@
         <v>46258</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32984,7 +32984,7 @@
         <v>46113</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33057,7 +33057,7 @@
         <v>46113</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33130,7 +33130,7 @@
         <v>45470</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33203,7 +33203,7 @@
         <v>45866</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33276,7 +33276,7 @@
         <v>45867</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33349,7 +33349,7 @@
         <v>46125</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33422,7 +33422,7 @@
         <v>46125</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33495,7 +33495,7 @@
         <v>46127</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33568,7 +33568,7 @@
         <v>46304</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33641,7 +33641,7 @@
         <v>46129</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33714,7 +33714,7 @@
         <v>45327</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33787,7 +33787,7 @@
         <v>46307</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33860,7 +33860,7 @@
         <v>46132</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33933,7 +33933,7 @@
         <v>45775</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34006,7 +34006,7 @@
         <v>46265</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34079,7 +34079,7 @@
         <v>46132</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34152,7 +34152,7 @@
         <v>46262</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34230,7 +34230,7 @@
         <v>46262</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>46308</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34386,7 +34386,7 @@
         <v>46265</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34459,7 +34459,7 @@
         <v>45638</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34537,7 +34537,7 @@
         <v>46265</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34610,7 +34610,7 @@
         <v>45538</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34683,7 +34683,7 @@
         <v>45590</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34756,7 +34756,7 @@
         <v>45589</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34829,7 +34829,7 @@
         <v>45126</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34902,7 +34902,7 @@
         <v>46135</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34975,7 +34975,7 @@
         <v>45800</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35048,7 +35048,7 @@
         <v>45491</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35121,7 +35121,7 @@
         <v>46135</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35199,7 +35199,7 @@
         <v>46309</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35272,7 +35272,7 @@
         <v>46263</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35345,7 +35345,7 @@
         <v>46309</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35418,7 +35418,7 @@
         <v>46310</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35491,7 +35491,7 @@
         <v>45866</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35564,7 +35564,7 @@
         <v>46308</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35637,7 +35637,7 @@
         <v>46266</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35710,7 +35710,7 @@
         <v>45343</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35788,7 +35788,7 @@
         <v>45349</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35861,7 +35861,7 @@
         <v>46050</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35934,7 +35934,7 @@
         <v>45877</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36007,7 +36007,7 @@
         <v>46267</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36080,7 +36080,7 @@
         <v>46267</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36153,7 +36153,7 @@
         <v>45799</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36226,7 +36226,7 @@
         <v>44991</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36304,7 +36304,7 @@
         <v>45926</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36377,7 +36377,7 @@
         <v>46139</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36450,7 +36450,7 @@
         <v>45929</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36523,7 +36523,7 @@
         <v>44609</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36596,7 +36596,7 @@
         <v>45618</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36669,7 +36669,7 @@
         <v>44908</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36747,7 +36747,7 @@
         <v>45552</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36820,7 +36820,7 @@
         <v>46029</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36893,7 +36893,7 @@
         <v>46316</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36971,7 +36971,7 @@
         <v>45965</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37044,7 +37044,7 @@
         <v>45232</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37117,7 +37117,7 @@
         <v>45961</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37190,7 +37190,7 @@
         <v>45890</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37263,7 +37263,7 @@
         <v>46272</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37336,7 +37336,7 @@
         <v>45883</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37409,7 +37409,7 @@
         <v>45996</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37482,7 +37482,7 @@
         <v>45981</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37555,7 +37555,7 @@
         <v>45586</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37628,7 +37628,7 @@
         <v>46275</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37701,7 +37701,7 @@
         <v>46141</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37774,7 +37774,7 @@
         <v>46318</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37852,7 +37852,7 @@
         <v>46318</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37930,7 +37930,7 @@
         <v>46274</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38003,7 +38003,7 @@
         <v>46275</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38076,7 +38076,7 @@
         <v>44905</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38154,7 +38154,7 @@
         <v>46274</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38227,7 +38227,7 @@
         <v>45344</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38300,7 +38300,7 @@
         <v>44977</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38378,7 +38378,7 @@
         <v>45141</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38451,7 +38451,7 @@
         <v>44753</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38529,7 +38529,7 @@
         <v>46151</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38602,7 +38602,7 @@
         <v>45049</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38680,7 +38680,7 @@
         <v>45569</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38753,7 +38753,7 @@
         <v>44722</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38831,7 +38831,7 @@
         <v>46151</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38904,7 +38904,7 @@
         <v>46155</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38977,7 +38977,7 @@
         <v>46155</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39050,7 +39050,7 @@
         <v>46160</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39123,7 +39123,7 @@
         <v>44812</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39196,7 +39196,7 @@
         <v>45034</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39269,7 +39269,7 @@
         <v>45525</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39342,7 +39342,7 @@
         <v>45075</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39415,7 +39415,7 @@
         <v>44977</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39493,7 +39493,7 @@
         <v>45119</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39566,7 +39566,7 @@
         <v>45469</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39639,7 +39639,7 @@
         <v>45187</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39712,7 +39712,7 @@
         <v>45147</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39785,7 +39785,7 @@
         <v>45147</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39858,7 +39858,7 @@
         <v>44742</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39931,7 +39931,7 @@
         <v>45187</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40004,7 +40004,7 @@
         <v>45021</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40077,7 +40077,7 @@
         <v>45763</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40155,7 +40155,7 @@
         <v>45051</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40228,7 +40228,7 @@
         <v>45028</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40301,7 +40301,7 @@
         <v>44907</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40374,7 +40374,7 @@
         <v>45586</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40447,7 +40447,7 @@
         <v>44533</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40520,7 +40520,7 @@
         <v>45173</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40593,7 +40593,7 @@
         <v>45503</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>45524</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40739,7 +40739,7 @@
         <v>45736</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40812,7 +40812,7 @@
         <v>45280</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40890,7 +40890,7 @@
         <v>44943</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40963,7 +40963,7 @@
         <v>44531</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41036,7 +41036,7 @@
         <v>44834</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41114,7 +41114,7 @@
         <v>45102</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41187,7 +41187,7 @@
         <v>45145</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>45343</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41338,7 +41338,7 @@
         <v>45757</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         <v>44812</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41484,7 +41484,7 @@
         <v>45378</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41557,7 +41557,7 @@
         <v>45419</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41630,7 +41630,7 @@
         <v>45096</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41708,7 +41708,7 @@
         <v>44859</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41786,7 +41786,7 @@
         <v>45105</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41864,7 +41864,7 @@
         <v>45491</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41937,7 +41937,7 @@
         <v>45231</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42010,7 +42010,7 @@
         <v>44893</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42088,7 +42088,7 @@
         <v>44949</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42161,7 +42161,7 @@
         <v>45245</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42234,7 +42234,7 @@
         <v>45139</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42312,7 +42312,7 @@
         <v>45187</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42385,7 +42385,7 @@
         <v>45187</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42458,7 +42458,7 @@
         <v>45562</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42531,7 +42531,7 @@
         <v>44896</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42609,7 +42609,7 @@
         <v>45622</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42682,7 +42682,7 @@
         <v>45569</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42755,7 +42755,7 @@
         <v>45575</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42828,7 +42828,7 @@
         <v>45344</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42901,7 +42901,7 @@
         <v>45764</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42974,7 +42974,7 @@
         <v>45447</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43052,7 +43052,7 @@
         <v>44531</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43125,7 +43125,7 @@
         <v>45141</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43198,7 +43198,7 @@
         <v>44540</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43271,7 +43271,7 @@
         <v>45457</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43344,7 +43344,7 @@
         <v>45180</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43422,7 +43422,7 @@
         <v>45673</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43495,7 +43495,7 @@
         <v>45022</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43573,7 +43573,7 @@
         <v>45593</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43646,7 +43646,7 @@
         <v>44981</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43719,7 +43719,7 @@
         <v>45615</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43792,7 +43792,7 @@
         <v>45141</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43865,7 +43865,7 @@
         <v>45587</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43938,7 +43938,7 @@
         <v>45158</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44011,7 +44011,7 @@
         <v>45678</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44084,7 +44084,7 @@
         <v>44993</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44157,7 +44157,7 @@
         <v>45524</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44230,7 +44230,7 @@
         <v>45574</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44303,7 +44303,7 @@
         <v>45330</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44381,7 +44381,7 @@
         <v>45525</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44454,7 +44454,7 @@
         <v>45182</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>45187</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44600,7 +44600,7 @@
         <v>45462</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44673,7 +44673,7 @@
         <v>45462</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44746,7 +44746,7 @@
         <v>45638</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44819,7 +44819,7 @@
         <v>45712</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44892,7 +44892,7 @@
         <v>45420</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44970,7 +44970,7 @@
         <v>45062</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45043,7 +45043,7 @@
         <v>44854</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45116,7 +45116,7 @@
         <v>44859</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45194,7 +45194,7 @@
         <v>45607</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45267,7 +45267,7 @@
         <v>44547</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45340,7 +45340,7 @@
         <v>45638</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45413,7 +45413,7 @@
         <v>44789</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45486,7 +45486,7 @@
         <v>45204</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45559,7 +45559,7 @@
         <v>45140</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45637,7 +45637,7 @@
         <v>45139</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45715,7 +45715,7 @@
         <v>45775</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45788,7 +45788,7 @@
         <v>45775</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45861,7 +45861,7 @@
         <v>45237</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45934,7 +45934,7 @@
         <v>45167</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46012,7 +46012,7 @@
         <v>44687</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>45665</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46158,7 +46158,7 @@
         <v>45239</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46231,7 +46231,7 @@
         <v>45158</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46304,7 +46304,7 @@
         <v>45770</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46377,7 +46377,7 @@
         <v>44756</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46455,7 +46455,7 @@
         <v>45265</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46533,7 +46533,7 @@
         <v>44816</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46606,7 +46606,7 @@
         <v>44902</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46679,7 +46679,7 @@
         <v>44938</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46752,7 +46752,7 @@
         <v>45736</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46825,7 +46825,7 @@
         <v>45566</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46898,7 +46898,7 @@
         <v>45616</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46971,7 +46971,7 @@
         <v>45167</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47044,7 +47044,7 @@
         <v>45707</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47117,7 +47117,7 @@
         <v>45505</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47195,7 +47195,7 @@
         <v>45536</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47268,7 +47268,7 @@
         <v>44922</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47341,7 +47341,7 @@
         <v>45433</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47414,7 +47414,7 @@
         <v>45775</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47487,7 +47487,7 @@
         <v>44916</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47565,7 +47565,7 @@
         <v>44603</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47643,7 +47643,7 @@
         <v>44559</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47721,7 +47721,7 @@
         <v>45567</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47799,7 +47799,7 @@
         <v>45667</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47877,7 +47877,7 @@
         <v>44517</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47950,7 +47950,7 @@
         <v>45250</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48028,7 +48028,7 @@
         <v>45638</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48101,7 +48101,7 @@
         <v>45762</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48174,7 +48174,7 @@
         <v>45762</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48247,7 +48247,7 @@
         <v>46070</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48325,7 +48325,7 @@
         <v>46071</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48398,7 +48398,7 @@
         <v>46071</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48471,7 +48471,7 @@
         <v>46071</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48544,7 +48544,7 @@
         <v>46135</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48617,7 +48617,7 @@
         <v>46148</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
